--- a/base/list-points.xlsx
+++ b/base/list-points.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:XFD78"/>
+  <dimension ref="A1:XFD90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" customWidth="1" style="70" min="1" max="1"/>
@@ -1721,17 +1721,17 @@
     <row r="11" ht="18" customHeight="1" s="70">
       <c r="A11" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B11" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.74</t>
+          <t>10.67.28.77</t>
         </is>
       </c>
       <c r="C11" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B1:92</t>
+          <t>F8:CC:6E:00:B4:DD</t>
         </is>
       </c>
       <c r="D11" s="75" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F11" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="J11" s="75" t="inlineStr">
         <is>
-          <t>002096</t>
+          <t>comp-pentium-gold-002096</t>
         </is>
       </c>
       <c r="K11" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>hp402</t>
         </is>
       </c>
       <c r="L11" s="75" t="inlineStr">
         <is>
-          <t>регистратура 4 окно</t>
+          <t>регистратура 2 окно</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1786,24 +1786,24 @@
       </c>
       <c r="N11" s="75" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>78535</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20.1" customHeight="1" s="70">
       <c r="A12" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B12" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.57</t>
+          <t>10.67.28.59</t>
         </is>
       </c>
       <c r="C12" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:A2:9E</t>
+          <t>F8:CC:6E:00:B1:CF</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="G12" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>KINGSTON_SA400S37240G</t>
         </is>
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>SSD 120Gb</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I12" s="75" t="inlineStr">
@@ -1838,17 +1838,17 @@
       </c>
       <c r="J12" s="75" t="inlineStr">
         <is>
-          <t>002096</t>
+          <t>comp-pentium-gold-002096</t>
         </is>
       </c>
       <c r="K12" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>M428</t>
         </is>
       </c>
       <c r="L12" s="75" t="inlineStr">
         <is>
-          <t>регистратура 5 окно</t>
+          <t>регистратура 3 окно</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
@@ -1858,97 +1858,101 @@
       </c>
       <c r="N12" s="75" t="inlineStr">
         <is>
-          <t>88536</t>
+          <t>88546</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20.1" customHeight="1" s="70">
       <c r="A13" s="72" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B13" s="73" t="inlineStr">
         <is>
-          <t>10.67.40.22</t>
+          <t>10.67.28.61</t>
         </is>
       </c>
       <c r="C13" s="74" t="inlineStr">
         <is>
-          <t>70-85-C2-0F-89-20</t>
+          <t>F8:CC:6E:00:A5:45</t>
         </is>
       </c>
       <c r="D13" s="75" t="inlineStr">
         <is>
-          <t>ASRock H81M-VG4 R3.0</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E13" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-4160 3.60GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F13" s="75" t="inlineStr">
         <is>
-          <t>4Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G13" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H13" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I13" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J13" s="75" t="inlineStr">
         <is>
-          <t>WS-040-022</t>
+          <t>comp-pentium-gold-002096</t>
         </is>
       </c>
       <c r="K13" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet MFP M129-M134 PCLmS</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L13" s="75" t="inlineStr">
         <is>
-          <t>заведующая</t>
+          <t>регистратура 1 окно</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
         <is>
-          <t>туберкулёз</t>
-        </is>
-      </c>
-      <c r="N13" s="75" t="inlineStr"/>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N13" s="75" t="inlineStr">
+        <is>
+          <t>88541</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20.1" customHeight="1" s="70">
       <c r="A14" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B14" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.145</t>
+          <t>10.67.14.141</t>
         </is>
       </c>
       <c r="C14" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-EA</t>
+          <t>2C-F0-5D-9E-B2-74</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star A320M-A PRO (MS-7C51)</t>
+          <t>Micro-Star International Co., Ltd.  A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E14" s="75" t="inlineStr">
@@ -1978,7 +1982,7 @@
       </c>
       <c r="J14" s="75" t="inlineStr">
         <is>
-          <t>WS-014-145</t>
+          <t>WS-14-141</t>
         </is>
       </c>
       <c r="K14" s="75" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="L14" s="75" t="inlineStr">
         <is>
-          <t>регистратура - 6 окно</t>
+          <t>регистратура 2 окно</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
@@ -1998,29 +2002,29 @@
       </c>
       <c r="N14" s="75" t="inlineStr">
         <is>
-          <t>88749</t>
+          <t>88746</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20.1" customHeight="1" s="70">
       <c r="A15" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B15" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.146</t>
+          <t>10.67.14.130</t>
         </is>
       </c>
       <c r="C15" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-5D</t>
+          <t>04-D9-F5-81-FB-36</t>
         </is>
       </c>
       <c r="D15" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star  A320M-A PRO (MS-7C51)</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E15" s="75" t="inlineStr">
@@ -2035,12 +2039,12 @@
       </c>
       <c r="G15" s="75" t="inlineStr">
         <is>
-          <t>Smartbuy SSD 256GB</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H15" s="75" t="inlineStr">
         <is>
-          <t>SSD-256Gb</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I15" s="75" t="inlineStr">
@@ -2050,7 +2054,7 @@
       </c>
       <c r="J15" s="75" t="inlineStr">
         <is>
-          <t>WS-014-146</t>
+          <t>DESKTOP-MQADVRK</t>
         </is>
       </c>
       <c r="K15" s="75" t="inlineStr">
@@ -2060,7 +2064,7 @@
       </c>
       <c r="L15" s="75" t="inlineStr">
         <is>
-          <t>регистратура 5 окно</t>
+          <t>регистратура 3 окно</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
@@ -2070,49 +2074,49 @@
       </c>
       <c r="N15" s="75" t="inlineStr">
         <is>
-          <t>88745</t>
+          <t>114130</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20.1" customHeight="1" s="70">
       <c r="A16" s="72" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B16" s="73" t="inlineStr">
         <is>
-          <t>10.67.40.24</t>
+          <t>10.67.14.132 / 192.168.56.1</t>
         </is>
       </c>
       <c r="C16" s="74" t="inlineStr">
         <is>
-          <t>10-FF-E0-28-EC-18</t>
+          <t>04-D9-F5-81-FB-2A / 0A-00-27-00-00-07</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E16" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F16" s="75" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G16" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I16" s="75" t="inlineStr">
@@ -2122,157 +2126,161 @@
       </c>
       <c r="J16" s="75" t="inlineStr">
         <is>
-          <t>WS-040-024</t>
+          <t>WS-014-132</t>
         </is>
       </c>
       <c r="K16" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Professional M1214nfh MFP</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L16" s="75" t="inlineStr">
         <is>
-          <t>9 заведующая</t>
+          <t>регистратура 1 окно</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
         <is>
-          <t>туберкулёз</t>
-        </is>
-      </c>
-      <c r="N16" s="75" t="inlineStr"/>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N16" s="75" t="inlineStr">
+        <is>
+          <t>114132</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20.1" customHeight="1" s="70">
       <c r="A17" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B17" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.133</t>
+          <t>10.67.38.49</t>
         </is>
       </c>
       <c r="C17" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-2B</t>
+          <t>00:58:3F:12:1D:31</t>
         </is>
       </c>
       <c r="D17" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME A320M-A</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E17" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F17" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G17" s="75" t="inlineStr">
         <is>
-          <t>ST1000DM010-2EP102</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H17" s="75" t="inlineStr">
         <is>
-          <t>HDD-1Tb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I17" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J17" s="75" t="inlineStr">
         <is>
-          <t>WS-014-133</t>
+          <t>comp-core-i7-8700t-1051a2</t>
         </is>
       </c>
       <c r="K17" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP_LaserJet_MFP_M28-M31</t>
         </is>
       </c>
       <c r="L17" s="75" t="inlineStr">
         <is>
-          <t>регитратура 4 окно</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="N17" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89591</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="70">
       <c r="A18" s="72" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B18" s="73" t="inlineStr">
         <is>
-          <t>192.168.56.1</t>
+          <t>10.67.64.26</t>
         </is>
       </c>
       <c r="C18" s="74" t="inlineStr">
         <is>
-          <t>04-42-1A-0F-29-A3</t>
+          <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME H510M-R</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E18" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G18" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I18" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J18" s="75" t="inlineStr">
         <is>
-          <t>WS-014-0198</t>
+          <t>1051a2</t>
         </is>
       </c>
       <c r="K18" s="75" t="inlineStr">
         <is>
-          <t>HP Color LaserJet Pro MFP 4303</t>
+          <t>Samsung-SCX-483x-5x3x-Series</t>
         </is>
       </c>
       <c r="L18" s="75" t="inlineStr">
         <is>
-          <t>Кирилл Николаевич приемная</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
@@ -2280,22 +2288,26 @@
           <t>pol1</t>
         </is>
       </c>
-      <c r="N18" s="75" t="inlineStr"/>
+      <c r="N18" s="75" t="inlineStr">
+        <is>
+          <t>91036</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20.1" customHeight="1" s="70">
       <c r="A19" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B19" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.87</t>
+          <t>10.67.64.88</t>
         </is>
       </c>
       <c r="C19" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:72:20</t>
+          <t>00:58:3F:17:72:F0</t>
         </is>
       </c>
       <c r="D19" s="75" t="inlineStr">
@@ -2310,7 +2322,7 @@
       </c>
       <c r="F19" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G19" s="75" t="inlineStr">
@@ -2335,12 +2347,12 @@
       </c>
       <c r="K19" s="75" t="inlineStr">
         <is>
-          <t>M428</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L19" s="75" t="inlineStr">
         <is>
-          <t>регистратура - 6 окно</t>
+          <t>542</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
@@ -2350,24 +2362,24 @@
       </c>
       <c r="N19" s="75" t="inlineStr">
         <is>
-          <t>89636</t>
+          <t>89588</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="70">
       <c r="A20" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B20" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>10.67.64.66</t>
         </is>
       </c>
       <c r="C20" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>00:58:3F:17:64:28</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -2407,12 +2419,12 @@
       </c>
       <c r="K20" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>Samsung-SCX-3400-Series</t>
         </is>
       </c>
       <c r="L20" s="75" t="inlineStr">
         <is>
-          <t>регистратура - расписание</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
@@ -2422,29 +2434,29 @@
       </c>
       <c r="N20" s="75" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>89722</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="70">
       <c r="A21" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B21" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.103</t>
+          <t>10.67.64.82</t>
         </is>
       </c>
       <c r="C21" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:10</t>
+          <t>00:58:3F:0F:3F:87</t>
         </is>
       </c>
       <c r="D21" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E21" s="75" t="inlineStr">
@@ -2454,12 +2466,12 @@
       </c>
       <c r="F21" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G21" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5 DataTraveler_3.0</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H21" s="75" t="inlineStr">
@@ -2479,17 +2491,17 @@
       </c>
       <c r="K21" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>HP_LaserJet_Professional_P1102</t>
         </is>
       </c>
       <c r="L21" s="75" t="inlineStr">
         <is>
-          <t>ординаторская</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
         <is>
-          <t>хирургия онкология 3 этаж</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N21" s="75" t="inlineStr">
@@ -2501,22 +2513,22 @@
     <row r="22" ht="20.1" customHeight="1" s="70">
       <c r="A22" s="72" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B22" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.73</t>
+          <t>10.67.11.32</t>
         </is>
       </c>
       <c r="C22" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:5A:FA</t>
+          <t>00:58:3F:0D:24:AD</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>ASUSTeK PRIME B365M-C</t>
         </is>
       </c>
       <c r="E22" s="75" t="inlineStr">
@@ -2526,45 +2538,49 @@
       </c>
       <c r="F22" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G22" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>FOXLINE FLSSD256X5</t>
         </is>
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>SSD 256Gb</t>
         </is>
       </c>
       <c r="I22" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>ALT Workstation 10.4</t>
         </is>
       </c>
       <c r="J22" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>dpk5324</t>
         </is>
       </c>
       <c r="K22" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet 1320</t>
+          <t>POScentre</t>
         </is>
       </c>
       <c r="L22" s="75" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>312-3211</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
-        </is>
-      </c>
-      <c r="N22" s="75" t="inlineStr"/>
+          <t>uprav</t>
+        </is>
+      </c>
+      <c r="N22" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="70">
       <c r="A23" s="72" t="inlineStr">
@@ -2574,22 +2590,22 @@
       </c>
       <c r="B23" s="73" t="inlineStr">
         <is>
-          <t>10.67.12.77</t>
+          <t>10.67.28.74</t>
         </is>
       </c>
       <c r="C23" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:16:55:32</t>
+          <t>F8:CC:6E:00:B1:92</t>
         </is>
       </c>
       <c r="D23" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E23" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel(R) i3-9100 3.60GHz</t>
         </is>
       </c>
       <c r="F23" s="75" t="inlineStr">
@@ -2599,3645 +2615,4493 @@
       </c>
       <c r="G23" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H23" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I23" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J23" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K23" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L23" s="75" t="inlineStr">
         <is>
-          <t>ординаторская</t>
+          <t>регистратура 4 окно</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
         <is>
-          <t>жирургия онкология 3 этаж</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N23" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>88520</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="70">
       <c r="A24" s="72" t="inlineStr">
         <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B24" s="73" t="inlineStr">
+        <is>
+          <t>10.67.28.57</t>
+        </is>
+      </c>
+      <c r="C24" s="74" t="inlineStr">
+        <is>
+          <t>F8:CC:6E:00:A2:9E</t>
+        </is>
+      </c>
+      <c r="D24" s="75" t="inlineStr">
+        <is>
+          <t>DEPO Computers DPH110S</t>
+        </is>
+      </c>
+      <c r="E24" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
+        </is>
+      </c>
+      <c r="F24" s="75" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G24" s="75" t="inlineStr">
+        <is>
+          <t>QUMO_SSD</t>
+        </is>
+      </c>
+      <c r="H24" s="75" t="inlineStr">
+        <is>
+          <t>SSD 120Gb</t>
+        </is>
+      </c>
+      <c r="I24" s="75" t="inlineStr">
+        <is>
+          <t>ALT 8 SP Workstation (cliff)</t>
+        </is>
+      </c>
+      <c r="J24" s="75" t="inlineStr">
+        <is>
+          <t>002096</t>
+        </is>
+      </c>
+      <c r="K24" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro M428fdw</t>
+        </is>
+      </c>
+      <c r="L24" s="75" t="inlineStr">
+        <is>
+          <t>регистратура 5 окно</t>
+        </is>
+      </c>
+      <c r="M24" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N24" s="75" t="inlineStr">
+        <is>
+          <t>88536</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" s="70">
+      <c r="A25" s="72" t="inlineStr">
+        <is>
+          <t>01.09.2026</t>
+        </is>
+      </c>
+      <c r="B25" s="73" t="inlineStr">
+        <is>
+          <t>10.67.40.22</t>
+        </is>
+      </c>
+      <c r="C25" s="74" t="inlineStr">
+        <is>
+          <t>70-85-C2-0F-89-20</t>
+        </is>
+      </c>
+      <c r="D25" s="75" t="inlineStr">
+        <is>
+          <t>ASRock H81M-VG4 R3.0</t>
+        </is>
+      </c>
+      <c r="E25" s="75" t="inlineStr">
+        <is>
+          <t>Intel i3-4160 3.60GHz</t>
+        </is>
+      </c>
+      <c r="F25" s="75" t="inlineStr">
+        <is>
+          <t>4Gb</t>
+        </is>
+      </c>
+      <c r="G25" s="75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H25" s="75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I25" s="75" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J25" s="75" t="inlineStr">
+        <is>
+          <t>WS-040-022</t>
+        </is>
+      </c>
+      <c r="K25" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet MFP M129-M134 PCLmS</t>
+        </is>
+      </c>
+      <c r="L25" s="75" t="inlineStr">
+        <is>
+          <t>заведующая</t>
+        </is>
+      </c>
+      <c r="M25" s="75" t="inlineStr">
+        <is>
+          <t>туберкулёз</t>
+        </is>
+      </c>
+      <c r="N25" s="75" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="70">
+      <c r="A26" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B26" s="73" t="inlineStr">
+        <is>
+          <t>10.67.14.145</t>
+        </is>
+      </c>
+      <c r="C26" s="74" t="inlineStr">
+        <is>
+          <t>2C-F0-5D-9E-B2-EA</t>
+        </is>
+      </c>
+      <c r="D26" s="75" t="inlineStr">
+        <is>
+          <t>Micro-Star A320M-A PRO (MS-7C51)</t>
+        </is>
+      </c>
+      <c r="E26" s="75" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+        </is>
+      </c>
+      <c r="F26" s="75" t="inlineStr">
+        <is>
+          <t>6Gb</t>
+        </is>
+      </c>
+      <c r="G26" s="75" t="inlineStr">
+        <is>
+          <t>Smartbuy SSD 256GB</t>
+        </is>
+      </c>
+      <c r="H26" s="75" t="inlineStr">
+        <is>
+          <t>SSD-256Gb</t>
+        </is>
+      </c>
+      <c r="I26" s="75" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J26" s="75" t="inlineStr">
+        <is>
+          <t>WS-014-145</t>
+        </is>
+      </c>
+      <c r="K26" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro M428fdw</t>
+        </is>
+      </c>
+      <c r="L26" s="75" t="inlineStr">
+        <is>
+          <t>регистратура - 6 окно</t>
+        </is>
+      </c>
+      <c r="M26" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N26" s="75" t="inlineStr">
+        <is>
+          <t>88749</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="70">
+      <c r="A27" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B27" s="73" t="inlineStr">
+        <is>
+          <t>10.67.14.146</t>
+        </is>
+      </c>
+      <c r="C27" s="74" t="inlineStr">
+        <is>
+          <t>2C-F0-5D-9E-B2-5D</t>
+        </is>
+      </c>
+      <c r="D27" s="75" t="inlineStr">
+        <is>
+          <t>Micro-Star  A320M-A PRO (MS-7C51)</t>
+        </is>
+      </c>
+      <c r="E27" s="75" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+        </is>
+      </c>
+      <c r="F27" s="75" t="inlineStr">
+        <is>
+          <t>6Gb</t>
+        </is>
+      </c>
+      <c r="G27" s="75" t="inlineStr">
+        <is>
+          <t>Smartbuy SSD 256GB</t>
+        </is>
+      </c>
+      <c r="H27" s="75" t="inlineStr">
+        <is>
+          <t>SSD-256Gb</t>
+        </is>
+      </c>
+      <c r="I27" s="75" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J27" s="75" t="inlineStr">
+        <is>
+          <t>WS-014-146</t>
+        </is>
+      </c>
+      <c r="K27" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro M428fdw</t>
+        </is>
+      </c>
+      <c r="L27" s="75" t="inlineStr">
+        <is>
+          <t>регистратура 5 окно</t>
+        </is>
+      </c>
+      <c r="M27" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N27" s="75" t="inlineStr">
+        <is>
+          <t>88745</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" s="70">
+      <c r="A28" s="72" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="B28" s="73" t="inlineStr">
+        <is>
+          <t>10.67.40.24</t>
+        </is>
+      </c>
+      <c r="C28" s="74" t="inlineStr">
+        <is>
+          <t>10-FF-E0-28-EC-18</t>
+        </is>
+      </c>
+      <c r="D28" s="75" t="inlineStr">
+        <is>
+          <t>Gigabyte H410M K</t>
+        </is>
+      </c>
+      <c r="E28" s="75" t="inlineStr">
+        <is>
+          <t>Intel i3-10100 3.60GHz</t>
+        </is>
+      </c>
+      <c r="F28" s="75" t="inlineStr">
+        <is>
+          <t>16Gb</t>
+        </is>
+      </c>
+      <c r="G28" s="75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H28" s="75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I28" s="75" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J28" s="75" t="inlineStr">
+        <is>
+          <t>WS-040-024</t>
+        </is>
+      </c>
+      <c r="K28" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Professional M1214nfh MFP</t>
+        </is>
+      </c>
+      <c r="L28" s="75" t="inlineStr">
+        <is>
+          <t>9 заведующая</t>
+        </is>
+      </c>
+      <c r="M28" s="75" t="inlineStr">
+        <is>
+          <t>туберкулёз</t>
+        </is>
+      </c>
+      <c r="N28" s="75" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" s="70">
+      <c r="A29" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B29" s="73" t="inlineStr">
+        <is>
+          <t>10.67.14.133</t>
+        </is>
+      </c>
+      <c r="C29" s="74" t="inlineStr">
+        <is>
+          <t>04-D9-F5-81-FB-2B</t>
+        </is>
+      </c>
+      <c r="D29" s="75" t="inlineStr">
+        <is>
+          <t>ASUSTeK PRIME A320M-A</t>
+        </is>
+      </c>
+      <c r="E29" s="75" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+        </is>
+      </c>
+      <c r="F29" s="75" t="inlineStr">
+        <is>
+          <t>6Gb</t>
+        </is>
+      </c>
+      <c r="G29" s="75" t="inlineStr">
+        <is>
+          <t>ST1000DM010-2EP102</t>
+        </is>
+      </c>
+      <c r="H29" s="75" t="inlineStr">
+        <is>
+          <t>HDD-1Tb</t>
+        </is>
+      </c>
+      <c r="I29" s="75" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J29" s="75" t="inlineStr">
+        <is>
+          <t>WS-014-133</t>
+        </is>
+      </c>
+      <c r="K29" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro M428fdw</t>
+        </is>
+      </c>
+      <c r="L29" s="75" t="inlineStr">
+        <is>
+          <t>регитратура 4 окно</t>
+        </is>
+      </c>
+      <c r="M29" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N29" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" s="70">
+      <c r="A30" s="72" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="B30" s="73" t="inlineStr">
+        <is>
+          <t>192.168.56.1</t>
+        </is>
+      </c>
+      <c r="C30" s="74" t="inlineStr">
+        <is>
+          <t>04-42-1A-0F-29-A3</t>
+        </is>
+      </c>
+      <c r="D30" s="75" t="inlineStr">
+        <is>
+          <t>ASUSTeK PRIME H510M-R</t>
+        </is>
+      </c>
+      <c r="E30" s="75" t="inlineStr">
+        <is>
+          <t>Intel i3-10100 3.60GHz</t>
+        </is>
+      </c>
+      <c r="F30" s="75" t="inlineStr">
+        <is>
+          <t>16Gb</t>
+        </is>
+      </c>
+      <c r="G30" s="75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H30" s="75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I30" s="75" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J30" s="75" t="inlineStr">
+        <is>
+          <t>WS-014-0198</t>
+        </is>
+      </c>
+      <c r="K30" s="75" t="inlineStr">
+        <is>
+          <t>HP Color LaserJet Pro MFP 4303</t>
+        </is>
+      </c>
+      <c r="L30" s="75" t="inlineStr">
+        <is>
+          <t>Кирилл Николаевич приемная</t>
+        </is>
+      </c>
+      <c r="M30" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N30" s="75" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" s="70">
+      <c r="A31" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B31" s="73" t="inlineStr">
+        <is>
+          <t>10.67.64.87</t>
+        </is>
+      </c>
+      <c r="C31" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:72:20</t>
+        </is>
+      </c>
+      <c r="D31" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F31" s="75" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G31" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H31" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I31" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J31" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K31" s="75" t="inlineStr">
+        <is>
+          <t>M428</t>
+        </is>
+      </c>
+      <c r="L31" s="75" t="inlineStr">
+        <is>
+          <t>регистратура - 6 окно</t>
+        </is>
+      </c>
+      <c r="M31" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N31" s="75" t="inlineStr">
+        <is>
+          <t>89636</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" s="70">
+      <c r="A32" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="inlineStr">
+        <is>
+          <t>10.67.64.98</t>
+        </is>
+      </c>
+      <c r="C32" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:6A:B2</t>
+        </is>
+      </c>
+      <c r="D32" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E32" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F32" s="75" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G32" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H32" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I32" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J32" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K32" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro M428fdw</t>
+        </is>
+      </c>
+      <c r="L32" s="75" t="inlineStr">
+        <is>
+          <t>регистратура - расписание</t>
+        </is>
+      </c>
+      <c r="M32" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N32" s="75" t="inlineStr">
+        <is>
+          <t>89681</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" s="70">
+      <c r="A33" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B33" s="73" t="inlineStr">
+        <is>
+          <t>10.67.64.103</t>
+        </is>
+      </c>
+      <c r="C33" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:6A:10</t>
+        </is>
+      </c>
+      <c r="D33" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E33" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F33" s="75" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G33" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5 DataTraveler_3.0</t>
+        </is>
+      </c>
+      <c r="H33" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I33" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J33" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K33" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro MFP 4103</t>
+        </is>
+      </c>
+      <c r="L33" s="75" t="inlineStr">
+        <is>
+          <t>ординаторская</t>
+        </is>
+      </c>
+      <c r="M33" s="75" t="inlineStr">
+        <is>
+          <t>хирургия онкология 3 этаж</t>
+        </is>
+      </c>
+      <c r="N33" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" s="70">
+      <c r="A34" s="72" t="inlineStr">
+        <is>
           <t>24.08.2026</t>
         </is>
       </c>
-      <c r="B24" s="73" t="inlineStr">
+      <c r="B34" s="73" t="inlineStr">
         <is>
           <t>10.67.64.73</t>
         </is>
       </c>
-      <c r="C24" s="74" t="inlineStr">
+      <c r="C34" s="74" t="inlineStr">
         <is>
           <t>00:58:3F:17:5A:FA</t>
         </is>
       </c>
-      <c r="D24" s="75" t="inlineStr">
+      <c r="D34" s="75" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E24" s="75" t="inlineStr">
+      <c r="E34" s="75" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F34" s="75" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G34" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H34" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I34" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J34" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K34" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet 1320</t>
+        </is>
+      </c>
+      <c r="L34" s="75" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="M34" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N34" s="75" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" s="70">
+      <c r="A35" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B35" s="73" t="inlineStr">
+        <is>
+          <t>10.67.12.77</t>
+        </is>
+      </c>
+      <c r="C35" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:16:55:32</t>
+        </is>
+      </c>
+      <c r="D35" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQB365MC</t>
+        </is>
+      </c>
+      <c r="E35" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F35" s="75" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G35" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H35" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I35" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J35" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K35" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro MFP 4103</t>
+        </is>
+      </c>
+      <c r="L35" s="75" t="inlineStr">
+        <is>
+          <t>ординаторская</t>
+        </is>
+      </c>
+      <c r="M35" s="75" t="inlineStr">
+        <is>
+          <t>жирургия онкология 3 этаж</t>
+        </is>
+      </c>
+      <c r="N35" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" s="70">
+      <c r="A36" s="72" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>10.67.64.73</t>
+        </is>
+      </c>
+      <c r="C36" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:5A:FA</t>
+        </is>
+      </c>
+      <c r="D36" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E36" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F36" s="75" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G24" s="75" t="inlineStr">
+      <c r="G36" s="75" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H24" s="75" t="inlineStr">
+      <c r="H36" s="75" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I24" s="75" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J24" s="75" t="inlineStr">
+      <c r="J36" s="75" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K24" s="75" t="inlineStr">
+      <c r="K36" s="75" t="inlineStr">
         <is>
           <t>HP LaserJet 1320</t>
         </is>
       </c>
-      <c r="L24" s="75" t="inlineStr">
+      <c r="L36" s="75" t="inlineStr">
         <is>
           <t>828</t>
         </is>
       </c>
-      <c r="M24" s="75" t="inlineStr">
+      <c r="M36" s="75" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" s="70">
-      <c r="A25" s="66" t="inlineStr">
+    <row r="37" ht="20.1" customHeight="1" s="70">
+      <c r="A37" s="66" t="inlineStr">
         <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B25" s="63" t="inlineStr">
+      <c r="B37" s="63" t="inlineStr">
         <is>
           <t>10.67.14.168</t>
         </is>
       </c>
-      <c r="C25" s="64" t="inlineStr">
+      <c r="C37" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:AF:29</t>
         </is>
       </c>
-      <c r="D25" s="65" t="inlineStr">
+      <c r="D37" s="65" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E25" s="65" t="inlineStr">
+      <c r="E37" s="65" t="inlineStr">
         <is>
           <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F25" s="65" t="inlineStr">
+      <c r="F37" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G25" s="65" t="inlineStr">
+      <c r="G37" s="65" t="inlineStr">
         <is>
           <t>QUMO_SSD ProductCode</t>
         </is>
       </c>
-      <c r="H25" s="65" t="inlineStr">
+      <c r="H37" s="65" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I25" s="65" t="inlineStr">
+      <c r="I37" s="65" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J25" s="65" t="inlineStr">
+      <c r="J37" s="65" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K25" s="65" t="inlineStr">
+      <c r="K37" s="65" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L25" s="65" t="inlineStr">
+      <c r="L37" s="65" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="M25" s="65" t="inlineStr">
+      <c r="M37" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1" s="70">
-      <c r="A26" s="66" t="inlineStr">
+    <row r="38" ht="20.1" customHeight="1" s="70">
+      <c r="A38" s="66" t="inlineStr">
         <is>
           <t>04.08.2026</t>
         </is>
       </c>
-      <c r="B26" s="63" t="inlineStr">
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>10.67.28.72</t>
         </is>
       </c>
-      <c r="C26" s="64" t="inlineStr">
+      <c r="C38" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:5B:1A</t>
         </is>
       </c>
-      <c r="D26" s="65" t="inlineStr">
+      <c r="D38" s="65" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E26" s="65" t="inlineStr">
+      <c r="E38" s="65" t="inlineStr">
         <is>
           <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F26" s="65" t="inlineStr">
+      <c r="F38" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G26" s="65" t="inlineStr">
+      <c r="G38" s="65" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H26" s="65" t="inlineStr">
+      <c r="H38" s="65" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I26" s="65" t="inlineStr">
+      <c r="I38" s="65" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J26" s="65" t="inlineStr">
+      <c r="J38" s="65" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K26" s="65" t="inlineStr">
+      <c r="K38" s="65" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L26" s="65" t="inlineStr">
+      <c r="L38" s="65" t="inlineStr">
         <is>
           <t>ord</t>
         </is>
       </c>
-      <c r="M26" s="65" t="inlineStr">
+      <c r="M38" s="65" t="inlineStr">
         <is>
           <t>rod-3</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20.1" customHeight="1" s="70">
-      <c r="A27" s="66" t="inlineStr">
+    <row r="39" ht="20.1" customHeight="1" s="70">
+      <c r="A39" s="66" t="inlineStr">
         <is>
           <t>03.08.2026</t>
         </is>
       </c>
-      <c r="B27" s="63" t="inlineStr">
+      <c r="B39" s="63" t="inlineStr">
         <is>
           <t>10.67.28.69</t>
         </is>
       </c>
-      <c r="C27" s="64" t="inlineStr">
+      <c r="C39" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:4F:13</t>
         </is>
       </c>
-      <c r="D27" s="65" t="inlineStr">
+      <c r="D39" s="65" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E27" s="65" t="inlineStr">
+      <c r="E39" s="65" t="inlineStr">
         <is>
           <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F27" s="65" t="inlineStr">
+      <c r="F39" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G27" s="65" t="inlineStr">
+      <c r="G39" s="65" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H27" s="65" t="inlineStr">
+      <c r="H39" s="65" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I27" s="65" t="inlineStr">
+      <c r="I39" s="65" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J27" s="65" t="inlineStr">
+      <c r="J39" s="65" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K27" s="65" t="inlineStr">
+      <c r="K39" s="65" t="inlineStr">
         <is>
           <t>Samsung SCX-4833FD</t>
         </is>
       </c>
-      <c r="L27" s="65" t="inlineStr">
+      <c r="L39" s="65" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="M27" s="65" t="inlineStr">
+      <c r="M39" s="65" t="inlineStr">
         <is>
           <t>det.pol</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20.1" customHeight="1" s="70">
-      <c r="A28" s="66" t="inlineStr">
+    <row r="40" ht="20.1" customHeight="1" s="70">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>30.07.2026</t>
         </is>
       </c>
-      <c r="B28" s="63" t="inlineStr">
+      <c r="B40" s="63" t="inlineStr">
         <is>
           <t>127.0.0.1</t>
         </is>
       </c>
-      <c r="C28" s="64" t="inlineStr">
+      <c r="C40" s="64" t="inlineStr">
         <is>
           <t>10:FF:E0:63:F1:98</t>
         </is>
       </c>
-      <c r="D28" s="65" t="inlineStr">
+      <c r="D40" s="65" t="inlineStr">
         <is>
           <t>Gigabyte H410M K</t>
         </is>
       </c>
-      <c r="E28" s="65" t="inlineStr">
+      <c r="E40" s="65" t="inlineStr">
         <is>
           <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F28" s="65" t="inlineStr">
+      <c r="F40" s="65" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G28" s="65" t="inlineStr">
+      <c r="G40" s="65" t="inlineStr">
         <is>
           <t>SSD</t>
         </is>
       </c>
-      <c r="H28" s="65" t="inlineStr">
+      <c r="H40" s="65" t="inlineStr">
         <is>
           <t>SSD 440Gb</t>
         </is>
       </c>
-      <c r="I28" s="65" t="inlineStr">
+      <c r="I40" s="65" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J28" s="65" t="inlineStr">
+      <c r="J40" s="65" t="inlineStr">
         <is>
           <t>WS-016-052</t>
         </is>
       </c>
-      <c r="K28" s="65" t="inlineStr">
+      <c r="K40" s="65" t="inlineStr">
         <is>
           <t>HP LaserJet Pro MFP 4103</t>
         </is>
       </c>
-      <c r="L28" s="65" t="inlineStr">
+      <c r="L40" s="65" t="inlineStr">
         <is>
           <t>zav</t>
         </is>
       </c>
-      <c r="M28" s="65" t="inlineStr">
+      <c r="M40" s="65" t="inlineStr">
         <is>
           <t>pblock</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20.1" customHeight="1" s="70">
-      <c r="A29" s="66" t="inlineStr">
+    <row r="41" ht="20.1" customHeight="1" s="70">
+      <c r="A41" s="66" t="inlineStr">
         <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B29" s="63" t="inlineStr">
+      <c r="B41" s="63" t="inlineStr">
         <is>
           <t>10.67.64.98</t>
         </is>
       </c>
-      <c r="C29" s="64" t="inlineStr">
+      <c r="C41" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
-      <c r="D29" s="65" t="inlineStr">
+      <c r="D41" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E29" s="65" t="inlineStr">
+      <c r="E41" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F29" s="65" t="inlineStr">
+      <c r="F41" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G29" s="65" t="inlineStr">
+      <c r="G41" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H29" s="65" t="inlineStr">
+      <c r="H41" s="65" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I29" s="65" t="inlineStr">
+      <c r="I41" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J29" s="65" t="inlineStr">
+      <c r="J41" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K29" s="65" t="inlineStr">
+      <c r="K41" s="65" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M426fdn</t>
         </is>
       </c>
-      <c r="L29" s="65" t="inlineStr">
+      <c r="L41" s="65" t="inlineStr">
         <is>
           <t>reg.raspis</t>
         </is>
       </c>
-      <c r="M29" s="65" t="inlineStr">
+      <c r="M41" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20.1" customHeight="1" s="70">
-      <c r="A30" s="66" t="inlineStr">
+    <row r="42" ht="20.1" customHeight="1" s="70">
+      <c r="A42" s="66" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="B30" s="63" t="inlineStr">
+      <c r="B42" s="63" t="inlineStr">
         <is>
           <t>10.67.64.77</t>
         </is>
       </c>
-      <c r="C30" s="64" t="inlineStr">
+      <c r="C42" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:00</t>
         </is>
       </c>
-      <c r="D30" s="65" t="inlineStr">
+      <c r="D42" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E30" s="65" t="inlineStr">
+      <c r="E42" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F30" s="65" t="inlineStr">
+      <c r="F42" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G30" s="65" t="inlineStr">
+      <c r="G42" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H30" s="65" t="inlineStr">
+      <c r="H42" s="65" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I30" s="65" t="inlineStr">
+      <c r="I42" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J30" s="65" t="inlineStr">
+      <c r="J42" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K30" s="65" t="inlineStr">
+      <c r="K42" s="65" t="inlineStr">
         <is>
           <t>Samsung SCX-4833</t>
         </is>
       </c>
-      <c r="L30" s="65" t="inlineStr">
+      <c r="L42" s="65" t="inlineStr">
         <is>
           <t>423</t>
         </is>
       </c>
-      <c r="M30" s="65" t="inlineStr">
+      <c r="M42" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1" s="70">
-      <c r="A31" s="66" t="inlineStr">
+    <row r="43" ht="20.1" customHeight="1" s="70">
+      <c r="A43" s="66" t="inlineStr">
         <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B31" s="63" t="inlineStr">
+      <c r="B43" s="63" t="inlineStr">
         <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C31" s="64" t="inlineStr">
+      <c r="C43" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D31" s="65" t="inlineStr">
+      <c r="D43" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E31" s="65" t="inlineStr">
+      <c r="E43" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F31" s="65" t="inlineStr">
+      <c r="F43" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G31" s="65" t="inlineStr">
+      <c r="G43" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H31" s="65" t="inlineStr">
+      <c r="H43" s="65" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I31" s="65" t="inlineStr">
+      <c r="I43" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J31" s="65" t="inlineStr">
+      <c r="J43" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K31" s="65" t="inlineStr">
+      <c r="K43" s="65" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L31" s="65" t="inlineStr">
+      <c r="L43" s="65" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M31" s="65" t="inlineStr">
+      <c r="M43" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1" s="70">
-      <c r="A32" s="66" t="inlineStr">
+    <row r="44" ht="20.1" customHeight="1" s="70">
+      <c r="A44" s="66" t="inlineStr">
         <is>
           <t>06.08.2026</t>
         </is>
       </c>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t>10.67.64.67</t>
         </is>
       </c>
-      <c r="C32" s="64" t="inlineStr">
+      <c r="C44" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:F8</t>
         </is>
       </c>
-      <c r="D32" s="65" t="inlineStr">
+      <c r="D44" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E32" s="65" t="inlineStr">
+      <c r="E44" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F32" s="65" t="inlineStr">
+      <c r="F44" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G32" s="65" t="inlineStr">
+      <c r="G44" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H32" s="65" t="inlineStr">
+      <c r="H44" s="65" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I32" s="65" t="inlineStr">
+      <c r="I44" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J32" s="65" t="inlineStr">
+      <c r="J44" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K32" s="65" t="inlineStr">
+      <c r="K44" s="65" t="inlineStr">
         <is>
           <t>HP_LaserJet_Professional_P1102</t>
         </is>
       </c>
-      <c r="L32" s="65" t="inlineStr">
+      <c r="L44" s="65" t="inlineStr">
         <is>
           <t>522</t>
         </is>
       </c>
-      <c r="M32" s="65" t="inlineStr">
+      <c r="M44" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" s="70">
-      <c r="A33" s="66" t="inlineStr">
+    <row r="45" ht="20.1" customHeight="1" s="70">
+      <c r="A45" s="66" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="B33" s="63" t="inlineStr">
+      <c r="B45" s="63" t="inlineStr">
         <is>
           <t>10.67.64.56</t>
         </is>
       </c>
-      <c r="C33" s="64" t="inlineStr">
+      <c r="C45" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:6A</t>
         </is>
       </c>
-      <c r="D33" s="65" t="inlineStr">
+      <c r="D45" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E33" s="65" t="inlineStr">
+      <c r="E45" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F33" s="65" t="inlineStr">
+      <c r="F45" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G33" s="65" t="inlineStr">
+      <c r="G45" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H33" s="65" t="inlineStr">
+      <c r="H45" s="65" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I33" s="65" t="inlineStr">
+      <c r="I45" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J33" s="65" t="inlineStr">
+      <c r="J45" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K33" s="65" t="inlineStr">
+      <c r="K45" s="65" t="inlineStr">
         <is>
           <t>HP_LaserJet_P2055d</t>
         </is>
       </c>
-      <c r="L33" s="65" t="inlineStr">
+      <c r="L45" s="65" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="M33" s="65" t="inlineStr">
+      <c r="M45" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" s="70">
-      <c r="A34" s="62" t="inlineStr">
+    <row r="46" ht="20.1" customHeight="1" s="70">
+      <c r="A46" s="62" t="inlineStr">
         <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B34" s="63" t="inlineStr">
+      <c r="B46" s="63" t="inlineStr">
         <is>
           <t>10.67.14.168</t>
         </is>
       </c>
-      <c r="C34" s="64" t="inlineStr">
+      <c r="C46" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:AF:29</t>
         </is>
       </c>
-      <c r="D34" s="61" t="inlineStr">
+      <c r="D46" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E34" s="61" t="inlineStr">
+      <c r="E46" s="61" t="inlineStr">
         <is>
           <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F34" s="61" t="inlineStr">
+      <c r="F46" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G34" s="61" t="inlineStr">
+      <c r="G46" s="61" t="inlineStr">
         <is>
           <t>QUMO_SSD ProductCode</t>
         </is>
       </c>
-      <c r="H34" s="61" t="inlineStr">
+      <c r="H46" s="61" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I34" s="61" t="inlineStr">
+      <c r="I46" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J34" s="61" t="inlineStr">
+      <c r="J46" s="61" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K34" s="61" t="inlineStr">
+      <c r="K46" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L34" s="61" t="inlineStr">
+      <c r="L46" s="61" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="M34" s="61" t="inlineStr">
+      <c r="M46" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" s="70">
-      <c r="A35" s="62" t="inlineStr">
+    <row r="47" ht="20.1" customHeight="1" s="70">
+      <c r="A47" s="62" t="inlineStr">
         <is>
           <t>04.08.2026</t>
         </is>
       </c>
-      <c r="B35" s="63" t="inlineStr">
+      <c r="B47" s="63" t="inlineStr">
         <is>
           <t>10.67.28.72</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
+      <c r="C47" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:5B:1A</t>
         </is>
       </c>
-      <c r="D35" s="61" t="inlineStr">
+      <c r="D47" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E35" s="61" t="inlineStr">
+      <c r="E47" s="61" t="inlineStr">
         <is>
           <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F35" s="61" t="inlineStr">
+      <c r="F47" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G35" s="61" t="inlineStr">
+      <c r="G47" s="61" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H35" s="61" t="inlineStr">
+      <c r="H47" s="61" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I35" s="61" t="inlineStr">
+      <c r="I47" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J35" s="61" t="inlineStr">
+      <c r="J47" s="61" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K35" s="61" t="inlineStr">
+      <c r="K47" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L35" s="61" t="inlineStr">
+      <c r="L47" s="61" t="inlineStr">
         <is>
           <t>ord</t>
         </is>
       </c>
-      <c r="M35" s="61" t="inlineStr">
+      <c r="M47" s="61" t="inlineStr">
         <is>
           <t>rod3</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" s="70">
-      <c r="A36" s="62" t="inlineStr">
+    <row r="48" ht="20.1" customHeight="1" s="70">
+      <c r="A48" s="62" t="inlineStr">
         <is>
           <t>03.08.2026</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B48" s="63" t="inlineStr">
         <is>
           <t>10.67.28.69</t>
         </is>
       </c>
-      <c r="C36" s="64" t="inlineStr">
+      <c r="C48" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:4F:13</t>
         </is>
       </c>
-      <c r="D36" s="61" t="inlineStr">
+      <c r="D48" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E36" s="61" t="inlineStr">
+      <c r="E48" s="61" t="inlineStr">
         <is>
           <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F36" s="61" t="inlineStr">
+      <c r="F48" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G36" s="61" t="inlineStr">
+      <c r="G48" s="61" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H36" s="61" t="inlineStr">
+      <c r="H48" s="61" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I36" s="61" t="inlineStr">
+      <c r="I48" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J36" s="61" t="inlineStr">
+      <c r="J48" s="61" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K36" s="61" t="inlineStr">
+      <c r="K48" s="61" t="inlineStr">
         <is>
           <t>samsung4833</t>
         </is>
       </c>
-      <c r="L36" s="61" t="inlineStr">
+      <c r="L48" s="61" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="M36" s="61" t="inlineStr">
+      <c r="M48" s="61" t="inlineStr">
         <is>
           <t>det.pol</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" s="70">
-      <c r="A37" s="62" t="inlineStr">
+    <row r="49" ht="20.1" customHeight="1" s="70">
+      <c r="A49" s="62" t="inlineStr">
         <is>
           <t>30.07.2026</t>
         </is>
       </c>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="B49" s="63" t="inlineStr">
         <is>
           <t>127.0.0.1</t>
         </is>
       </c>
-      <c r="C37" s="64" t="inlineStr">
+      <c r="C49" s="64" t="inlineStr">
         <is>
           <t>10:FF:E0:63:F1:98</t>
         </is>
       </c>
-      <c r="D37" s="61" t="inlineStr">
+      <c r="D49" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M K</t>
         </is>
       </c>
-      <c r="E37" s="61" t="inlineStr">
+      <c r="E49" s="61" t="inlineStr">
         <is>
           <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F37" s="61" t="inlineStr">
+      <c r="F49" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G37" s="61" t="inlineStr">
+      <c r="G49" s="61" t="inlineStr">
         <is>
           <t>SSD</t>
         </is>
       </c>
-      <c r="H37" s="61" t="inlineStr">
+      <c r="H49" s="61" t="inlineStr">
         <is>
           <t>SSD 440Gb</t>
         </is>
       </c>
-      <c r="I37" s="61" t="inlineStr">
+      <c r="I49" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J37" s="61" t="inlineStr">
+      <c r="J49" s="61" t="inlineStr">
         <is>
           <t>WS-016-052</t>
         </is>
       </c>
-      <c r="K37" s="61" t="inlineStr">
+      <c r="K49" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro MFP 4103</t>
         </is>
       </c>
-      <c r="L37" s="61" t="inlineStr">
+      <c r="L49" s="61" t="inlineStr">
         <is>
           <t>zav</t>
         </is>
       </c>
-      <c r="M37" s="61" t="inlineStr">
+      <c r="M49" s="61" t="inlineStr">
         <is>
           <t>pblock</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" s="70">
-      <c r="A38" s="62" t="inlineStr">
+    <row r="50" ht="20.1" customHeight="1" s="70">
+      <c r="A50" s="62" t="inlineStr">
         <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B38" s="63" t="inlineStr">
+      <c r="B50" s="63" t="inlineStr">
         <is>
           <t>10.67.64.98</t>
         </is>
       </c>
-      <c r="C38" s="64" t="inlineStr">
+      <c r="C50" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
-      <c r="D38" s="61" t="inlineStr">
+      <c r="D50" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E38" s="61" t="inlineStr">
+      <c r="E50" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F38" s="61" t="inlineStr">
+      <c r="F50" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G38" s="61" t="inlineStr">
+      <c r="G50" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H38" s="61" t="inlineStr">
+      <c r="H50" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I38" s="61" t="inlineStr">
+      <c r="I50" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J38" s="61" t="inlineStr">
+      <c r="J50" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K38" s="61" t="inlineStr">
+      <c r="K50" s="61" t="inlineStr">
         <is>
           <t>M428f</t>
         </is>
       </c>
-      <c r="L38" s="61" t="inlineStr">
+      <c r="L50" s="61" t="inlineStr">
         <is>
           <t>reg.raspis</t>
         </is>
       </c>
-      <c r="M38" s="61" t="inlineStr">
+      <c r="M50" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20.1" customHeight="1" s="70">
-      <c r="A39" s="62" t="inlineStr">
+    <row r="51" ht="20.1" customHeight="1" s="70">
+      <c r="A51" s="62" t="inlineStr">
         <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B39" s="63" t="inlineStr">
+      <c r="B51" s="63" t="inlineStr">
         <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C39" s="64" t="inlineStr">
+      <c r="C51" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D39" s="61" t="inlineStr">
+      <c r="D51" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E39" s="61" t="inlineStr">
+      <c r="E51" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F39" s="61" t="inlineStr">
+      <c r="F51" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G39" s="61" t="inlineStr">
+      <c r="G51" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H39" s="61" t="inlineStr">
+      <c r="H51" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I39" s="61" t="inlineStr">
+      <c r="I51" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J39" s="61" t="inlineStr">
+      <c r="J51" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K39" s="61" t="inlineStr">
+      <c r="K51" s="61" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L39" s="61" t="inlineStr">
+      <c r="L51" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M39" s="61" t="inlineStr">
+      <c r="M51" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20.1" customHeight="1" s="70">
-      <c r="A40" s="59" t="n">
+    <row r="52" ht="20.1" customHeight="1" s="70">
+      <c r="A52" s="59" t="n">
         <v>46231</v>
       </c>
-      <c r="B40" s="63" t="inlineStr">
+      <c r="B52" s="63" t="inlineStr">
         <is>
           <t>10.67.2.33</t>
         </is>
       </c>
-      <c r="C40" s="64" t="inlineStr">
+      <c r="C52" s="64" t="inlineStr">
         <is>
           <t>F0-B4-D2-2C-6D-1D</t>
         </is>
       </c>
-      <c r="D40" s="61" t="inlineStr">
+      <c r="D52" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H510M H</t>
         </is>
       </c>
-      <c r="E40" s="61" t="inlineStr">
+      <c r="E52" s="61" t="inlineStr">
         <is>
           <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F40" s="61" t="inlineStr">
+      <c r="F52" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G40" s="61" t="inlineStr">
+      <c r="G52" s="61" t="inlineStr">
         <is>
           <t>KINGSTON SA400S37480G</t>
         </is>
       </c>
-      <c r="H40" s="61" t="inlineStr">
+      <c r="H52" s="61" t="inlineStr">
         <is>
           <t>SSD 480Gb</t>
         </is>
       </c>
-      <c r="I40" s="61" t="inlineStr">
+      <c r="I52" s="61" t="inlineStr">
         <is>
           <t>Windows 10 IoT Enterprise LTSC</t>
         </is>
       </c>
-      <c r="J40" s="61" t="inlineStr">
+      <c r="J52" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K40" s="61" t="inlineStr">
+      <c r="K52" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
-      <c r="L40" s="61" t="inlineStr">
+      <c r="L52" s="61" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="M40" s="61" t="inlineStr">
+      <c r="M52" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20.1" customHeight="1" s="70">
-      <c r="A41" s="58" t="n">
+    <row r="53" ht="20.1" customHeight="1" s="70">
+      <c r="A53" s="58" t="n">
         <v>46232</v>
       </c>
-      <c r="B41" s="63" t="inlineStr">
+      <c r="B53" s="63" t="inlineStr">
         <is>
           <t>10.67.14.88</t>
         </is>
       </c>
-      <c r="C41" s="64" t="inlineStr">
+      <c r="C53" s="64" t="inlineStr">
         <is>
           <t>D0-27-88-9A-7C-7C</t>
         </is>
       </c>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="D53" s="61" t="inlineStr">
         <is>
           <t>Foxconn H61S</t>
         </is>
       </c>
-      <c r="E41" s="61" t="inlineStr">
+      <c r="E53" s="61" t="inlineStr">
         <is>
           <t>Intel Celeron CPU G530 2.40GHz</t>
         </is>
       </c>
-      <c r="F41" s="61" t="inlineStr">
+      <c r="F53" s="61" t="inlineStr">
         <is>
           <t>12Gb</t>
         </is>
       </c>
-      <c r="G41" s="61" t="inlineStr">
+      <c r="G53" s="61" t="inlineStr">
         <is>
           <t>WD Green</t>
         </is>
       </c>
-      <c r="H41" s="61" t="inlineStr">
+      <c r="H53" s="61" t="inlineStr">
         <is>
           <t>SSD 500Gb</t>
         </is>
       </c>
-      <c r="I41" s="61" t="inlineStr">
+      <c r="I53" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J41" s="61" t="inlineStr">
+      <c r="J53" s="61" t="inlineStr">
         <is>
           <t>WS-014-088</t>
         </is>
       </c>
-      <c r="K41" s="61" t="inlineStr">
+      <c r="K53" s="61" t="inlineStr">
         <is>
           <t>Samsung SCX-483x 5x3x Series</t>
         </is>
       </c>
-      <c r="L41" s="61" t="inlineStr">
+      <c r="L53" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M41" s="61" t="inlineStr">
+      <c r="M53" s="61" t="inlineStr">
         <is>
           <t>pol1 khl</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20.1" customHeight="1" s="70">
-      <c r="A42" s="57" t="n">
+    <row r="54" ht="20.1" customHeight="1" s="70">
+      <c r="A54" s="57" t="n">
         <v>46232</v>
       </c>
-      <c r="B42" s="63" t="inlineStr">
+      <c r="B54" s="63" t="inlineStr">
         <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C42" s="64" t="inlineStr">
+      <c r="C54" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr">
+      <c r="D54" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E42" s="61" t="inlineStr">
+      <c r="E54" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F42" s="61" t="inlineStr">
+      <c r="F54" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G42" s="61" t="inlineStr">
+      <c r="G54" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H42" s="61" t="inlineStr">
+      <c r="H54" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I42" s="61" t="inlineStr">
+      <c r="I54" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J42" s="61" t="inlineStr">
+      <c r="J54" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K42" s="61" t="inlineStr">
+      <c r="K54" s="61" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L42" s="61" t="inlineStr">
+      <c r="L54" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M42" s="61" t="inlineStr">
+      <c r="M54" s="61" t="inlineStr">
         <is>
           <t>pol1 khl</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20.1" customHeight="1" s="70">
-      <c r="A43" s="56" t="n">
+    <row r="55" ht="15.75" customHeight="1" s="70">
+      <c r="A55" s="56" t="n">
         <v>46231</v>
       </c>
-      <c r="B43" s="63" t="inlineStr">
+      <c r="B55" s="63" t="inlineStr">
         <is>
           <t>10.67.24.12</t>
         </is>
       </c>
-      <c r="C43" s="64" t="inlineStr">
+      <c r="C55" s="64" t="inlineStr">
         <is>
           <t>04-D9-F5-81-FB-29</t>
         </is>
       </c>
-      <c r="D43" s="61" t="inlineStr">
+      <c r="D55" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
-      <c r="E43" s="61" t="inlineStr">
+      <c r="E55" s="61" t="inlineStr">
         <is>
           <t>AMD Ryzen 5 3400G</t>
         </is>
       </c>
-      <c r="F43" s="61" t="inlineStr">
+      <c r="F55" s="61" t="inlineStr">
         <is>
           <t>6GiB</t>
         </is>
       </c>
-      <c r="G43" s="61" t="inlineStr">
+      <c r="G55" s="61" t="inlineStr">
         <is>
           <t>WDC WD5003ABYX-01WERA1</t>
         </is>
       </c>
-      <c r="H43" s="61" t="inlineStr">
+      <c r="H55" s="61" t="inlineStr">
         <is>
           <t>500Gb</t>
         </is>
       </c>
-      <c r="I43" s="61" t="inlineStr">
+      <c r="I55" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J43" s="61" t="inlineStr">
+      <c r="J55" s="61" t="inlineStr">
         <is>
           <t>WS-024-012</t>
         </is>
       </c>
-      <c r="K43" s="61" t="inlineStr">
+      <c r="K55" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M404dn</t>
         </is>
       </c>
-      <c r="L43" s="61" t="inlineStr">
+      <c r="L55" s="61" t="inlineStr">
         <is>
           <t>disp</t>
         </is>
       </c>
-      <c r="M43" s="61" t="inlineStr">
+      <c r="M55" s="61" t="inlineStr">
         <is>
           <t>skp</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20.1" customHeight="1" s="70">
-      <c r="A44" s="55" t="n">
+    <row r="56" ht="15.75" customHeight="1" s="70">
+      <c r="A56" s="55" t="n">
         <v>46230</v>
       </c>
-      <c r="B44" s="63" t="inlineStr">
+      <c r="B56" s="63" t="inlineStr">
         <is>
           <t>10.67.28.59</t>
         </is>
       </c>
-      <c r="C44" s="64" t="inlineStr">
+      <c r="C56" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:B1:CF</t>
         </is>
       </c>
-      <c r="D44" s="61" t="inlineStr">
+      <c r="D56" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E44" s="61" t="inlineStr">
+      <c r="E56" s="61" t="inlineStr">
         <is>
           <t>Intel(R) G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F44" s="61" t="inlineStr">
+      <c r="F56" s="61" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="G44" s="61" t="inlineStr">
+      <c r="G56" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">KINGSTON_SA400S37240G </t>
         </is>
       </c>
-      <c r="H44" s="61" t="inlineStr">
+      <c r="H56" s="61" t="inlineStr">
         <is>
           <t>SSD 240Gb</t>
         </is>
       </c>
-      <c r="I44" s="61" t="inlineStr">
+      <c r="I56" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J44" s="61" t="n">
+      <c r="J56" s="61" t="n">
         <v>2096</v>
       </c>
-      <c r="K44" s="61" t="inlineStr">
+      <c r="K56" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428f-M429f</t>
         </is>
       </c>
-      <c r="L44" s="61" t="inlineStr">
+      <c r="L56" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M44" s="61" t="inlineStr">
+      <c r="M56" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20.1" customHeight="1" s="70">
-      <c r="A45" s="47" t="n">
+    <row r="57" ht="15.75" customHeight="1" s="70">
+      <c r="A57" s="47" t="n">
         <v>46225</v>
       </c>
-      <c r="B45" s="63" t="inlineStr">
+      <c r="B57" s="63" t="inlineStr">
         <is>
           <t>10.67.64.107</t>
         </is>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C57" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:4C:F7</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr">
+      <c r="D57" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E45" s="61" t="inlineStr">
+      <c r="E57" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F45" s="61" t="inlineStr">
+      <c r="F57" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G45" s="61" t="inlineStr">
+      <c r="G57" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H45" s="61" t="inlineStr">
+      <c r="H57" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I45" s="61" t="inlineStr">
+      <c r="I57" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J45" s="61" t="inlineStr">
+      <c r="J57" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K45" s="61" t="inlineStr">
+      <c r="K57" s="61" t="inlineStr">
         <is>
           <t>Pantum BP5100DN</t>
         </is>
       </c>
-      <c r="L45" s="61" t="inlineStr">
+      <c r="L57" s="61" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="M45" s="61" t="inlineStr">
+      <c r="M57" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20.1" customHeight="1" s="70">
-      <c r="A46" s="46" t="n">
+    <row r="58" ht="15.75" customHeight="1" s="70">
+      <c r="A58" s="46" t="n">
         <v>46225</v>
       </c>
-      <c r="B46" s="63" t="inlineStr">
+      <c r="B58" s="63" t="inlineStr">
         <is>
           <t>10.67.64.5</t>
         </is>
       </c>
-      <c r="C46" s="64" t="inlineStr">
+      <c r="C58" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:58:0C</t>
         </is>
       </c>
-      <c r="D46" s="61" t="inlineStr">
+      <c r="D58" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E46" s="61" t="inlineStr">
+      <c r="E58" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F46" s="61" t="inlineStr">
+      <c r="F58" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G46" s="61" t="inlineStr">
+      <c r="G58" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H46" s="61" t="inlineStr">
+      <c r="H58" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I46" s="61" t="inlineStr">
+      <c r="I58" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J46" s="61" t="inlineStr">
+      <c r="J58" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K46" s="61" t="inlineStr">
+      <c r="K58" s="61" t="inlineStr">
         <is>
           <t>HP M428</t>
         </is>
       </c>
-      <c r="L46" s="61" t="inlineStr">
+      <c r="L58" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M46" s="61" t="inlineStr">
+      <c r="M58" s="61" t="inlineStr">
         <is>
           <t>pol1-3level</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20.1" customHeight="1" s="70">
-      <c r="A47" s="45" t="n">
+    <row r="59" ht="15.75" customHeight="1" s="70">
+      <c r="A59" s="45" t="n">
         <v>46226</v>
       </c>
-      <c r="B47" s="63" t="inlineStr">
+      <c r="B59" s="63" t="inlineStr">
         <is>
           <t>10.67.64.26</t>
         </is>
       </c>
-      <c r="C47" s="64" t="inlineStr">
+      <c r="C59" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
-      <c r="D47" s="61" t="inlineStr">
+      <c r="D59" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E47" s="61" t="inlineStr">
+      <c r="E59" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F47" s="61" t="inlineStr">
+      <c r="F59" s="61" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="G47" s="61" t="inlineStr">
+      <c r="G59" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H47" s="61" t="inlineStr">
+      <c r="H59" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I47" s="61" t="inlineStr">
+      <c r="I59" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J47" s="61" t="inlineStr">
+      <c r="J59" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K47" s="61" t="inlineStr">
+      <c r="K59" s="61" t="inlineStr">
         <is>
           <t>Samsung-SCX-483x-5x3x-Series</t>
         </is>
       </c>
-      <c r="L47" s="61" t="inlineStr">
+      <c r="L59" s="61" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="M47" s="61" t="inlineStr">
+      <c r="M59" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20.1" customHeight="1" s="70">
-      <c r="A48" s="44" t="n">
+    <row r="60" ht="15.75" customHeight="1" s="70">
+      <c r="A60" s="44" t="n">
         <v>46225</v>
       </c>
-      <c r="B48" s="63" t="inlineStr">
+      <c r="B60" s="63" t="inlineStr">
         <is>
           <t>10.67.64.2</t>
         </is>
       </c>
-      <c r="C48" s="64" t="inlineStr">
+      <c r="C60" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:20</t>
         </is>
       </c>
-      <c r="D48" s="61" t="inlineStr">
+      <c r="D60" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E48" s="61" t="inlineStr">
+      <c r="E60" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F48" s="61" t="inlineStr">
+      <c r="F60" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G48" s="61" t="inlineStr">
+      <c r="G60" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H48" s="61" t="inlineStr">
+      <c r="H60" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I48" s="61" t="inlineStr">
+      <c r="I60" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J48" s="61" t="inlineStr">
+      <c r="J60" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K48" s="61" t="inlineStr">
+      <c r="K60" s="61" t="inlineStr">
         <is>
           <t>HP M428</t>
         </is>
       </c>
-      <c r="L48" s="61" t="inlineStr">
+      <c r="L60" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M48" s="61" t="inlineStr">
+      <c r="M60" s="61" t="inlineStr">
         <is>
           <t>pol1-3level</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20.1" customHeight="1" s="70">
-      <c r="A49" s="43" t="n">
+    <row r="61" ht="15.75" customHeight="1" s="70">
+      <c r="A61" s="43" t="n">
         <v>46227</v>
       </c>
-      <c r="B49" s="63" t="inlineStr">
+      <c r="B61" s="63" t="inlineStr">
         <is>
           <t>10.67.28.73</t>
         </is>
       </c>
-      <c r="C49" s="64" t="inlineStr">
+      <c r="C61" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:AF:9E</t>
         </is>
       </c>
-      <c r="D49" s="61" t="inlineStr">
+      <c r="D61" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E49" s="61" t="inlineStr">
+      <c r="E61" s="61" t="inlineStr">
         <is>
           <t>Intel(R) G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F49" s="61" t="inlineStr">
+      <c r="F61" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G49" s="61" t="inlineStr">
+      <c r="G61" s="61" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H49" s="61" t="inlineStr">
+      <c r="H61" s="61" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I49" s="61" t="inlineStr">
+      <c r="I61" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J49" s="61" t="inlineStr">
+      <c r="J61" s="61" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K49" s="61" t="inlineStr">
+      <c r="K61" s="61" t="inlineStr">
         <is>
           <t>HP Laserjet M14-M17</t>
         </is>
       </c>
-      <c r="L49" s="61" t="inlineStr">
+      <c r="L61" s="61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M49" s="61" t="inlineStr">
+      <c r="M61" s="61" t="inlineStr">
         <is>
           <t>pat.anatom.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20.1" customHeight="1" s="70">
-      <c r="A50" s="40" t="n">
+    <row r="62" ht="15.75" customHeight="1" s="70">
+      <c r="A62" s="40" t="n">
         <v>46220</v>
       </c>
-      <c r="B50" s="63" t="inlineStr">
+      <c r="B62" s="63" t="inlineStr">
         <is>
           <t>10.67.12.70</t>
         </is>
       </c>
-      <c r="C50" s="64" t="inlineStr">
+      <c r="C62" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:16:57:0A</t>
         </is>
       </c>
-      <c r="D50" s="61" t="inlineStr">
+      <c r="D62" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E50" s="61" t="inlineStr">
+      <c r="E62" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F50" s="61" t="inlineStr">
+      <c r="F62" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G50" s="61" t="inlineStr">
+      <c r="G62" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H50" s="61" t="inlineStr">
+      <c r="H62" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I50" s="61" t="inlineStr">
+      <c r="I62" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J50" s="61" t="inlineStr">
+      <c r="J62" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K50" s="61" t="inlineStr">
+      <c r="K62" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L50" s="61" t="inlineStr">
+      <c r="L62" s="61" t="inlineStr">
         <is>
           <t>st.ses</t>
         </is>
       </c>
-      <c r="M50" s="61" t="inlineStr">
+      <c r="M62" s="61" t="inlineStr">
         <is>
           <t>h5</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20.1" customHeight="1" s="70">
-      <c r="A51" s="39" t="n">
+    <row r="63" ht="15.75" customHeight="1" s="70">
+      <c r="A63" s="39" t="n">
         <v>46218</v>
       </c>
-      <c r="B51" s="63" t="inlineStr">
+      <c r="B63" s="63" t="inlineStr">
         <is>
           <t>10.67.12.49</t>
         </is>
       </c>
-      <c r="C51" s="64" t="inlineStr">
+      <c r="C63" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:47:D7</t>
         </is>
       </c>
-      <c r="D51" s="61" t="inlineStr">
+      <c r="D63" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E51" s="61" t="inlineStr">
+      <c r="E63" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F51" s="61" t="inlineStr">
+      <c r="F63" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G51" s="61" t="inlineStr">
+      <c r="G63" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H51" s="61" t="inlineStr">
+      <c r="H63" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I51" s="61" t="inlineStr">
+      <c r="I63" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J51" s="61" t="inlineStr">
+      <c r="J63" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K51" s="61" t="inlineStr">
+      <c r="K63" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L51" s="61" t="inlineStr">
+      <c r="L63" s="61" t="inlineStr">
         <is>
           <t>sts</t>
         </is>
       </c>
-      <c r="M51" s="61" t="inlineStr">
+      <c r="M63" s="61" t="inlineStr">
         <is>
           <t>h2</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20.1" customHeight="1" s="70">
-      <c r="A52" s="38" t="n">
+    <row r="64" ht="15.75" customHeight="1" s="70">
+      <c r="A64" s="38" t="n">
         <v>46218</v>
       </c>
-      <c r="B52" s="63" t="inlineStr">
+      <c r="B64" s="63" t="inlineStr">
         <is>
           <t>10.67.64.82</t>
         </is>
       </c>
-      <c r="C52" s="64" t="inlineStr">
+      <c r="C64" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:3F:87</t>
         </is>
       </c>
-      <c r="D52" s="61" t="inlineStr">
+      <c r="D64" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E52" s="61" t="inlineStr">
+      <c r="E64" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F52" s="61" t="inlineStr">
+      <c r="F64" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G52" s="61" t="inlineStr">
+      <c r="G64" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H52" s="61" t="inlineStr">
+      <c r="H64" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I52" s="61" t="inlineStr">
+      <c r="I64" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J52" s="61" t="inlineStr">
+      <c r="J64" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K52" s="61" t="inlineStr">
+      <c r="K64" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L52" s="61" t="inlineStr">
+      <c r="L64" s="61" t="inlineStr">
         <is>
           <t>433</t>
         </is>
       </c>
-      <c r="M52" s="61" t="inlineStr">
+      <c r="M64" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20.1" customHeight="1" s="70">
-      <c r="A53" s="37" t="n">
+    <row r="65">
+      <c r="A65" s="37" t="n">
         <v>46218</v>
       </c>
-      <c r="B53" s="63" t="inlineStr">
+      <c r="B65" s="63" t="inlineStr">
         <is>
           <t>10.67.64.52</t>
         </is>
       </c>
-      <c r="C53" s="64" t="inlineStr">
+      <c r="C65" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:59:52</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D65" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E65" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F53" s="61" t="inlineStr">
+      <c r="F65" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G53" s="61" t="inlineStr">
+      <c r="G65" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H53" s="61" t="inlineStr">
+      <c r="H65" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I53" s="61" t="inlineStr">
+      <c r="I65" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J53" s="61" t="inlineStr">
+      <c r="J65" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K53" s="61" t="inlineStr">
+      <c r="K65" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L53" s="61" t="inlineStr">
+      <c r="L65" s="61" t="inlineStr">
         <is>
           <t>824</t>
         </is>
       </c>
-      <c r="M53" s="61" t="inlineStr">
+      <c r="M65" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" s="70">
-      <c r="A54" s="36" t="n">
+    <row r="66">
+      <c r="A66" s="36" t="n">
         <v>46218</v>
       </c>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="B66" s="63" t="inlineStr">
         <is>
           <t>10.67.64.9</t>
         </is>
       </c>
-      <c r="C54" s="64" t="inlineStr">
+      <c r="C66" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:52</t>
         </is>
       </c>
-      <c r="D54" s="61" t="inlineStr">
+      <c r="D66" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="E66" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F54" s="61" t="inlineStr">
+      <c r="F66" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G54" s="61" t="inlineStr">
+      <c r="G66" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H54" s="61" t="inlineStr">
+      <c r="H66" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I54" s="61" t="inlineStr">
+      <c r="I66" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J54" s="61" t="inlineStr">
+      <c r="J66" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K54" s="61" t="inlineStr">
+      <c r="K66" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L54" s="61" t="inlineStr">
+      <c r="L66" s="61" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M54" s="61" t="inlineStr">
+      <c r="M66" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="70">
-      <c r="A55" s="35" t="n">
+    <row r="67">
+      <c r="A67" s="35" t="n">
         <v>46218</v>
       </c>
-      <c r="B55" s="63" t="inlineStr">
+      <c r="B67" s="63" t="inlineStr">
         <is>
           <t>10.67.64.26</t>
         </is>
       </c>
-      <c r="C55" s="64" t="inlineStr">
+      <c r="C67" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
-      <c r="D55" s="61" t="inlineStr">
+      <c r="D67" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E55" s="61" t="inlineStr">
+      <c r="E67" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F55" s="61" t="inlineStr">
+      <c r="F67" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G55" s="61" t="inlineStr">
+      <c r="G67" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H55" s="61" t="inlineStr">
+      <c r="H67" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I55" s="61" t="inlineStr">
+      <c r="I67" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J55" s="61" t="inlineStr">
+      <c r="J67" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K55" s="61" t="inlineStr">
+      <c r="K67" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L55" s="61" t="inlineStr">
+      <c r="L67" s="61" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="M55" s="61" t="inlineStr">
+      <c r="M67" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="70">
-      <c r="A56" s="34" t="n">
+    <row r="68">
+      <c r="A68" s="34" t="n">
         <v>46217</v>
       </c>
-      <c r="B56" s="63" t="inlineStr">
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>10.67.22.66</t>
         </is>
       </c>
-      <c r="C56" s="64" t="inlineStr">
+      <c r="C68" s="64" t="inlineStr">
         <is>
           <t>2C-F0-5D-9E-B2-56</t>
         </is>
       </c>
-      <c r="D56" s="61" t="inlineStr">
+      <c r="D68" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">MSI A320M-A PRO </t>
         </is>
       </c>
-      <c r="E56" s="61" t="inlineStr">
+      <c r="E68" s="61" t="inlineStr">
         <is>
           <t>AMD Ryzen 5 3400G</t>
         </is>
       </c>
-      <c r="F56" s="61" t="inlineStr">
+      <c r="F68" s="61" t="inlineStr">
         <is>
           <t>6GiB</t>
         </is>
       </c>
-      <c r="G56" s="61" t="inlineStr">
+      <c r="G68" s="61" t="inlineStr">
         <is>
           <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
-      <c r="H56" s="61" t="inlineStr">
+      <c r="H68" s="61" t="inlineStr">
         <is>
           <t>256Gb</t>
         </is>
       </c>
-      <c r="I56" s="61" t="inlineStr">
+      <c r="I68" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J56" s="61" t="inlineStr">
+      <c r="J68" s="61" t="inlineStr">
         <is>
           <t>WS-022-066</t>
         </is>
       </c>
-      <c r="K56" s="61" t="inlineStr">
+      <c r="K68" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428f-M429f</t>
         </is>
       </c>
-      <c r="L56" s="61" t="inlineStr">
+      <c r="L68" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M56" s="61" t="inlineStr">
+      <c r="M68" s="61" t="inlineStr">
         <is>
           <t>detstvo</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="70">
-      <c r="A57" s="33" t="n">
+    <row r="69">
+      <c r="A69" s="33" t="n">
         <v>46211</v>
       </c>
-      <c r="B57" s="63" t="inlineStr">
+      <c r="B69" s="63" t="inlineStr">
         <is>
           <t>10.67.64.88</t>
         </is>
       </c>
-      <c r="C57" s="64" t="inlineStr">
+      <c r="C69" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:72:F0</t>
         </is>
       </c>
-      <c r="D57" s="61" t="inlineStr">
+      <c r="D69" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E57" s="61" t="inlineStr">
+      <c r="E69" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F57" s="61" t="inlineStr">
+      <c r="F69" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G57" s="61" t="inlineStr">
+      <c r="G69" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H57" s="61" t="inlineStr">
+      <c r="H69" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I57" s="61" t="inlineStr">
+      <c r="I69" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J57" s="61" t="inlineStr">
+      <c r="J69" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K57" s="61" t="inlineStr">
+      <c r="K69" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L57" s="61" t="inlineStr">
+      <c r="L69" s="61" t="inlineStr">
         <is>
           <t>542</t>
         </is>
       </c>
-      <c r="M57" s="61" t="inlineStr">
+      <c r="M69" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="70">
-      <c r="A58" s="32" t="n">
+    <row r="70">
+      <c r="A70" s="32" t="n">
         <v>46202</v>
       </c>
-      <c r="B58" s="63" t="inlineStr">
+      <c r="B70" s="63" t="inlineStr">
         <is>
           <t>10.67.64.40</t>
         </is>
       </c>
-      <c r="C58" s="64" t="inlineStr">
+      <c r="C70" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:54:E6</t>
         </is>
       </c>
-      <c r="D58" s="61" t="inlineStr">
+      <c r="D70" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E58" s="61" t="inlineStr">
+      <c r="E70" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F58" s="61" t="inlineStr">
+      <c r="F70" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G58" s="61" t="inlineStr">
+      <c r="G70" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H58" s="61" t="inlineStr">
+      <c r="H70" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I58" s="61" t="inlineStr">
+      <c r="I70" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J58" s="61" t="inlineStr">
+      <c r="J70" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K58" s="61" t="inlineStr">
+      <c r="K70" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L58" s="61" t="inlineStr">
+      <c r="L70" s="61" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="M58" s="61" t="inlineStr">
+      <c r="M70" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1" s="70">
-      <c r="A59" s="31" t="n">
+    <row r="71">
+      <c r="A71" s="31" t="n">
         <v>46199</v>
       </c>
-      <c r="B59" s="63" t="inlineStr">
+      <c r="B71" s="63" t="inlineStr">
         <is>
           <t>10.67.64.8</t>
         </is>
       </c>
-      <c r="C59" s="64" t="inlineStr">
+      <c r="C71" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:D6</t>
         </is>
       </c>
-      <c r="D59" s="61" t="inlineStr">
+      <c r="D71" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E59" s="61" t="inlineStr">
+      <c r="E71" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F59" s="61" t="inlineStr">
+      <c r="F71" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G59" s="61" t="inlineStr">
+      <c r="G71" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H59" s="61" t="inlineStr">
+      <c r="H71" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I59" s="61" t="inlineStr">
+      <c r="I71" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J59" s="61" t="inlineStr">
+      <c r="J71" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K59" s="61" t="inlineStr">
+      <c r="K71" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L59" s="61" t="inlineStr">
+      <c r="L71" s="61" t="inlineStr">
         <is>
           <t>~</t>
         </is>
       </c>
-      <c r="M59" s="61" t="inlineStr">
+      <c r="M71" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="70">
-      <c r="A60" s="30" t="n">
+    <row r="72">
+      <c r="A72" s="30" t="n">
         <v>46198</v>
       </c>
-      <c r="B60" s="63" t="inlineStr">
+      <c r="B72" s="63" t="inlineStr">
         <is>
           <t>10.67.22.105</t>
         </is>
       </c>
-      <c r="C60" s="64" t="inlineStr">
+      <c r="C72" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:36:6D</t>
         </is>
       </c>
-      <c r="D60" s="61" t="inlineStr">
+      <c r="D72" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E60" s="61" t="inlineStr">
+      <c r="E72" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F60" s="61" t="inlineStr">
+      <c r="F72" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G60" s="61" t="inlineStr">
+      <c r="G72" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H60" s="61" t="inlineStr">
+      <c r="H72" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I60" s="61" t="inlineStr">
+      <c r="I72" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J60" s="61" t="inlineStr">
+      <c r="J72" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K60" s="61" t="inlineStr">
+      <c r="K72" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L60" s="61" t="inlineStr">
+      <c r="L72" s="61" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="M60" s="61" t="inlineStr">
+      <c r="M72" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="70">
-      <c r="A61" s="29" t="n">
+    <row r="73">
+      <c r="A73" s="29" t="n">
         <v>46196</v>
       </c>
-      <c r="B61" s="63" t="inlineStr">
+      <c r="B73" s="63" t="inlineStr">
         <is>
           <t>192.168.36.31</t>
         </is>
       </c>
-      <c r="C61" s="64" t="inlineStr">
+      <c r="C73" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:1D:48</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D73" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E73" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F73" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G61" s="61" t="inlineStr">
+      <c r="G73" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H61" s="61" t="inlineStr">
+      <c r="H73" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I61" s="61" t="inlineStr">
+      <c r="I73" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J61" s="61" t="inlineStr">
+      <c r="J73" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K61" s="61" t="inlineStr">
+      <c r="K73" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L61" s="61" t="inlineStr">
+      <c r="L73" s="61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M61" s="61" t="inlineStr">
+      <c r="M73" s="61" t="inlineStr">
         <is>
           <t>stomat</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="70">
-      <c r="A62" s="28" t="n">
+    <row r="74">
+      <c r="A74" s="28" t="n">
         <v>46196</v>
       </c>
-      <c r="B62" s="63" t="inlineStr">
+      <c r="B74" s="63" t="inlineStr">
         <is>
           <t>192.168.36.25</t>
         </is>
       </c>
-      <c r="C62" s="64" t="inlineStr">
+      <c r="C74" s="64" t="inlineStr">
         <is>
           <t>18-C0-4D-CD-F6-5E</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr">
+      <c r="D74" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M H V3</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E74" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10105 3.70GHz</t>
         </is>
       </c>
-      <c r="F62" s="61" t="inlineStr">
+      <c r="F74" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr">
+      <c r="G74" s="61" t="inlineStr">
         <is>
           <t>Samsung SSD 870 EVO 500GB</t>
         </is>
       </c>
-      <c r="H62" s="61" t="inlineStr">
+      <c r="H74" s="61" t="inlineStr">
         <is>
           <t>465Gb</t>
         </is>
       </c>
-      <c r="I62" s="61" t="inlineStr">
+      <c r="I74" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J62" s="61" t="inlineStr">
+      <c r="J74" s="61" t="inlineStr">
         <is>
           <t>WS-036-025</t>
         </is>
       </c>
-      <c r="K62" s="61" t="inlineStr">
+      <c r="K74" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L62" s="61" t="inlineStr">
+      <c r="L74" s="61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M62" s="61" t="inlineStr">
+      <c r="M74" s="61" t="inlineStr">
         <is>
           <t>stomat</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1" s="70">
-      <c r="A63" s="27" t="n">
+    <row r="75">
+      <c r="A75" s="27" t="n">
         <v>46192</v>
       </c>
-      <c r="B63" s="63" t="inlineStr">
+      <c r="B75" s="63" t="inlineStr">
         <is>
           <t>10.67.38.58</t>
         </is>
       </c>
-      <c r="C63" s="64" t="inlineStr">
+      <c r="C75" s="64" t="inlineStr">
         <is>
           <t>10-FF-E0-63-ED-A8</t>
         </is>
       </c>
-      <c r="D63" s="61" t="inlineStr">
+      <c r="D75" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M K</t>
         </is>
       </c>
-      <c r="E63" s="61" t="inlineStr">
+      <c r="E75" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F63" s="61" t="inlineStr">
+      <c r="F75" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G63" s="61" t="inlineStr">
+      <c r="G75" s="61" t="inlineStr">
         <is>
           <t>WD Blue SN5000 500GB</t>
         </is>
       </c>
-      <c r="H63" s="61" t="inlineStr">
+      <c r="H75" s="61" t="inlineStr">
         <is>
           <t>HDD 465Gb</t>
         </is>
       </c>
-      <c r="I63" s="61" t="inlineStr">
+      <c r="I75" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J63" s="61" t="inlineStr">
+      <c r="J75" s="61" t="inlineStr">
         <is>
           <t>WS-038-058</t>
         </is>
       </c>
-      <c r="K63" s="61" t="inlineStr">
+      <c r="K75" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L63" s="61" t="inlineStr">
+      <c r="L75" s="61" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="M63" s="61" t="inlineStr">
+      <c r="M75" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="70">
-      <c r="A64" s="26" t="n">
+    <row r="76">
+      <c r="A76" s="26" t="n">
         <v>46191</v>
       </c>
-      <c r="B64" s="63" t="inlineStr">
+      <c r="B76" s="63" t="inlineStr">
         <is>
           <t>10.67.64.98</t>
         </is>
       </c>
-      <c r="C64" s="64" t="inlineStr">
+      <c r="C76" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
-      <c r="D64" s="61" t="inlineStr">
+      <c r="D76" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E64" s="61" t="inlineStr">
+      <c r="E76" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F64" s="61" t="inlineStr">
+      <c r="F76" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G64" s="61" t="inlineStr">
+      <c r="G76" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H64" s="61" t="inlineStr">
+      <c r="H76" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I64" s="61" t="inlineStr">
+      <c r="I76" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J64" s="61" t="inlineStr">
+      <c r="J76" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K64" s="61" t="inlineStr">
+      <c r="K76" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L64" s="61" t="inlineStr">
+      <c r="L76" s="61" t="inlineStr">
         <is>
           <t>registratura</t>
         </is>
       </c>
-      <c r="M64" s="61" t="inlineStr">
+      <c r="M76" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="25" t="n">
+    <row r="77">
+      <c r="A77" s="25" t="n">
         <v>46183</v>
       </c>
-      <c r="B65" s="63" t="inlineStr">
+      <c r="B77" s="63" t="inlineStr">
         <is>
           <t>10.67.64.92</t>
         </is>
       </c>
-      <c r="C65" s="64" t="inlineStr">
+      <c r="C77" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:63:82</t>
         </is>
       </c>
-      <c r="D65" s="61" t="inlineStr">
+      <c r="D77" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E65" s="61" t="inlineStr">
+      <c r="E77" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F65" s="61" t="inlineStr">
+      <c r="F77" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G65" s="61" t="inlineStr">
+      <c r="G77" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5 OnlyDisk</t>
         </is>
       </c>
-      <c r="H65" s="61" t="inlineStr">
+      <c r="H77" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I65" s="61" t="inlineStr">
+      <c r="I77" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J65" s="61" t="inlineStr">
+      <c r="J77" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K65" s="61" t="inlineStr">
+      <c r="K77" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L65" s="61" t="inlineStr">
+      <c r="L77" s="61" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="M65" s="61" t="inlineStr">
+      <c r="M77" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="24" t="n">
+    <row r="78">
+      <c r="A78" s="24" t="n">
         <v>46183</v>
       </c>
-      <c r="B66" s="63" t="inlineStr">
+      <c r="B78" s="63" t="inlineStr">
         <is>
           <t>10.67.64.38</t>
         </is>
       </c>
-      <c r="C66" s="64" t="inlineStr">
+      <c r="C78" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:54:A4</t>
         </is>
       </c>
-      <c r="D66" s="61" t="inlineStr">
+      <c r="D78" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E66" s="61" t="inlineStr">
+      <c r="E78" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F66" s="61" t="inlineStr">
+      <c r="F78" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G66" s="61" t="inlineStr">
+      <c r="G78" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H66" s="61" t="inlineStr">
+      <c r="H78" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I66" s="61" t="inlineStr">
+      <c r="I78" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J66" s="61" t="inlineStr">
+      <c r="J78" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K66" s="61" t="inlineStr">
+      <c r="K78" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L66" s="61" t="inlineStr">
+      <c r="L78" s="61" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="M66" s="61" t="inlineStr">
+      <c r="M78" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="23" t="n">
+    <row r="79">
+      <c r="A79" s="23" t="n">
         <v>46183</v>
       </c>
-      <c r="B67" s="63" t="inlineStr">
+      <c r="B79" s="63" t="inlineStr">
         <is>
           <t>10.67.64.96</t>
         </is>
       </c>
-      <c r="C67" s="64" t="inlineStr">
+      <c r="C79" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:42:79</t>
         </is>
       </c>
-      <c r="D67" s="61" t="inlineStr">
+      <c r="D79" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E67" s="61" t="inlineStr">
+      <c r="E79" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F67" s="61" t="inlineStr">
+      <c r="F79" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G67" s="61" t="inlineStr">
+      <c r="G79" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H67" s="61" t="inlineStr">
+      <c r="H79" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I67" s="61" t="inlineStr">
+      <c r="I79" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J67" s="61" t="inlineStr">
+      <c r="J79" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K67" s="61" t="inlineStr">
+      <c r="K79" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L67" s="61" t="inlineStr">
+      <c r="L79" s="61" t="inlineStr">
         <is>
           <t>417</t>
         </is>
       </c>
-      <c r="M67" s="61" t="inlineStr">
+      <c r="M79" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="22" t="n">
+    <row r="80">
+      <c r="A80" s="22" t="n">
         <v>46181</v>
       </c>
-      <c r="B68" s="63" t="inlineStr">
+      <c r="B80" s="63" t="inlineStr">
         <is>
           <t>10.67.64.3</t>
         </is>
       </c>
-      <c r="C68" s="64" t="inlineStr">
+      <c r="C80" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:62:CA</t>
         </is>
       </c>
-      <c r="D68" s="61" t="inlineStr">
+      <c r="D80" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E68" s="61" t="inlineStr">
+      <c r="E80" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F68" s="61" t="inlineStr">
+      <c r="F80" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G68" s="61" t="inlineStr">
+      <c r="G80" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H68" s="61" t="inlineStr">
+      <c r="H80" s="61" t="inlineStr">
         <is>
           <t>238Gb</t>
         </is>
       </c>
-      <c r="I68" s="61" t="inlineStr">
+      <c r="I80" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J68" s="61" t="inlineStr">
+      <c r="J80" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K68" s="61" t="inlineStr">
+      <c r="K80" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L68" s="61" t="inlineStr">
+      <c r="L80" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M68" s="61" t="inlineStr">
+      <c r="M80" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="21" t="n">
+    <row r="81">
+      <c r="A81" s="21" t="n">
         <v>46181</v>
       </c>
-      <c r="B69" s="63" t="inlineStr">
+      <c r="B81" s="63" t="inlineStr">
         <is>
           <t>192.168.0.129</t>
         </is>
       </c>
-      <c r="C69" s="64" t="inlineStr">
+      <c r="C81" s="64" t="inlineStr">
         <is>
           <t>38-D5-47-E1-3E-C6</t>
         </is>
       </c>
-      <c r="D69" s="61" t="inlineStr">
+      <c r="D81" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK Z170-K</t>
         </is>
       </c>
-      <c r="E69" s="61" t="inlineStr">
+      <c r="E81" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i7-6700K 4.00GHz</t>
         </is>
       </c>
-      <c r="F69" s="61" t="inlineStr">
+      <c r="F81" s="61" t="inlineStr">
         <is>
           <t>32Gb</t>
         </is>
       </c>
-      <c r="G69" s="61" t="inlineStr">
+      <c r="G81" s="61" t="inlineStr">
         <is>
           <t>TOSHIBA DT01ACA100</t>
         </is>
       </c>
-      <c r="H69" s="61" t="inlineStr">
+      <c r="H81" s="61" t="inlineStr">
         <is>
           <t>931Gb</t>
         </is>
       </c>
-      <c r="I69" s="61" t="inlineStr">
+      <c r="I81" s="61" t="inlineStr">
         <is>
           <t>Windows 10 IoT Enterprise</t>
         </is>
       </c>
-      <c r="J69" s="61" t="inlineStr">
+      <c r="J81" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K69" s="61" t="inlineStr">
+      <c r="K81" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L69" s="61" t="inlineStr">
+      <c r="L81" s="61" t="inlineStr">
         <is>
           <t>my</t>
         </is>
       </c>
-      <c r="M69" s="61" t="inlineStr">
+      <c r="M81" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="n">
+    <row r="82">
+      <c r="A82" s="20" t="n">
         <v>46178</v>
       </c>
-      <c r="B70" s="63" t="inlineStr">
+      <c r="B82" s="63" t="inlineStr">
         <is>
           <t>10.67.2.8</t>
         </is>
       </c>
-      <c r="C70" s="64" t="inlineStr">
+      <c r="C82" s="64" t="inlineStr">
         <is>
           <t>58-11-22-07-4E-DF</t>
         </is>
       </c>
-      <c r="D70" s="61" t="inlineStr">
+      <c r="D82" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME H510M-K</t>
         </is>
       </c>
-      <c r="E70" s="61" t="inlineStr">
+      <c r="E82" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-10400 2.90GHz</t>
         </is>
       </c>
-      <c r="F70" s="61" t="inlineStr">
+      <c r="F82" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G70" s="61" t="inlineStr">
+      <c r="G82" s="61" t="inlineStr">
         <is>
           <t>ST500NM0011</t>
         </is>
       </c>
-      <c r="H70" s="61" t="inlineStr">
+      <c r="H82" s="61" t="inlineStr">
         <is>
           <t>SSD 465 Gb</t>
         </is>
       </c>
-      <c r="I70" s="61" t="inlineStr">
+      <c r="I82" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J70" s="61" t="inlineStr">
+      <c r="J82" s="61" t="inlineStr">
         <is>
           <t>WS-002-008</t>
         </is>
       </c>
-      <c r="K70" s="61" t="inlineStr">
+      <c r="K82" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L70" s="61" t="inlineStr">
+      <c r="L82" s="61" t="inlineStr">
         <is>
           <t>312 IGOR</t>
         </is>
       </c>
-      <c r="M70" s="61" t="inlineStr">
+      <c r="M82" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="19" t="n">
+    <row r="83">
+      <c r="A83" s="19" t="n">
         <v>46177</v>
       </c>
-      <c r="B71" s="63" t="inlineStr">
+      <c r="B83" s="63" t="inlineStr">
         <is>
           <t>10.67.2.33</t>
         </is>
       </c>
-      <c r="C71" s="64" t="inlineStr">
+      <c r="C83" s="64" t="inlineStr">
         <is>
           <t>18-C0-4D-D7-67-0E</t>
         </is>
       </c>
-      <c r="D71" s="61" t="inlineStr">
+      <c r="D83" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H510M H</t>
         </is>
       </c>
-      <c r="E71" s="61" t="inlineStr">
+      <c r="E83" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F71" s="61" t="inlineStr">
+      <c r="F83" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G71" s="61" t="inlineStr">
+      <c r="G83" s="61" t="inlineStr">
         <is>
           <t>KINGSTON SA400S37480G</t>
         </is>
       </c>
-      <c r="H71" s="61" t="inlineStr">
+      <c r="H83" s="61" t="inlineStr">
         <is>
           <t>SSD 447 Gb</t>
         </is>
       </c>
-      <c r="I71" s="61" t="inlineStr">
+      <c r="I83" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Windows 10 IoT Enterprise LTSC </t>
         </is>
       </c>
-      <c r="J71" s="61" t="inlineStr">
+      <c r="J83" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K71" s="61" t="inlineStr">
+      <c r="K83" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L71" s="61" t="inlineStr">
+      <c r="L83" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M71" s="61" t="inlineStr">
+      <c r="M83" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="18" t="n">
+    <row r="84">
+      <c r="A84" s="18" t="n">
         <v>46178</v>
       </c>
-      <c r="B72" s="63" t="inlineStr">
+      <c r="B84" s="63" t="inlineStr">
         <is>
           <t>192.168.36.34</t>
         </is>
       </c>
-      <c r="C72" s="64" t="inlineStr">
+      <c r="C84" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:37:A7</t>
         </is>
       </c>
-      <c r="D72" s="61" t="inlineStr">
+      <c r="D84" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E72" s="61" t="inlineStr">
+      <c r="E84" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) i5-9400 2.90GHz </t>
         </is>
       </c>
-      <c r="F72" s="61" t="inlineStr">
+      <c r="F84" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G72" s="61" t="inlineStr">
+      <c r="G84" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H72" s="61" t="inlineStr">
+      <c r="H84" s="61" t="inlineStr">
         <is>
           <t>SSD 256</t>
         </is>
       </c>
-      <c r="I72" s="61" t="inlineStr">
+      <c r="I84" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J72" s="61" t="inlineStr">
+      <c r="J84" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K72" s="61" t="inlineStr">
+      <c r="K84" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L72" s="61" t="inlineStr">
+      <c r="L84" s="61" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M72" s="61" t="inlineStr">
+      <c r="M84" s="61" t="inlineStr">
         <is>
           <t>stomatology</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="17" t="n">
+    <row r="85">
+      <c r="A85" s="17" t="n">
         <v>46178</v>
       </c>
-      <c r="B73" s="63" t="inlineStr">
+      <c r="B85" s="63" t="inlineStr">
         <is>
           <t>10.67.11.32</t>
         </is>
       </c>
-      <c r="C73" s="64" t="inlineStr">
+      <c r="C85" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0D:24:AD</t>
         </is>
       </c>
-      <c r="D73" s="61" t="inlineStr">
+      <c r="D85" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME B365M-C</t>
         </is>
       </c>
-      <c r="E73" s="61" t="inlineStr">
+      <c r="E85" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) i5-9400 2.90GHz </t>
         </is>
       </c>
-      <c r="F73" s="61" t="inlineStr">
+      <c r="F85" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G73" s="61" t="inlineStr">
+      <c r="G85" s="61" t="inlineStr">
         <is>
           <t>FOXLINE FLSSD256X5</t>
         </is>
       </c>
-      <c r="H73" s="61" t="inlineStr">
+      <c r="H85" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I73" s="61" t="inlineStr">
+      <c r="I85" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 10.4</t>
         </is>
       </c>
-      <c r="J73" s="61" t="inlineStr">
+      <c r="J85" s="61" t="inlineStr">
         <is>
           <t>dpk5324</t>
         </is>
       </c>
-      <c r="K73" s="61" t="inlineStr">
+      <c r="K85" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L73" s="61" t="inlineStr">
+      <c r="L85" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M73" s="61" t="inlineStr">
+      <c r="M85" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="n">
+    <row r="86">
+      <c r="A86" s="16" t="n">
         <v>46177</v>
       </c>
-      <c r="B74" s="63" t="inlineStr">
+      <c r="B86" s="63" t="inlineStr">
         <is>
           <t>192.168.0.172</t>
         </is>
       </c>
-      <c r="C74" s="64" t="inlineStr">
+      <c r="C86" s="64" t="inlineStr">
         <is>
           <t>2C:56:DC:DB:90:05</t>
         </is>
       </c>
-      <c r="D74" s="61" t="inlineStr">
+      <c r="D86" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK A68HM-K</t>
         </is>
       </c>
-      <c r="E74" s="61" t="inlineStr">
+      <c r="E86" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">AMD Athlon(tm) X2 340 </t>
         </is>
       </c>
-      <c r="F74" s="61" t="inlineStr">
+      <c r="F86" s="61" t="inlineStr">
         <is>
           <t>6Gb</t>
         </is>
       </c>
-      <c r="G74" s="61" t="inlineStr">
+      <c r="G86" s="61" t="inlineStr">
         <is>
           <t>TOSHIBA DT01ACA100</t>
         </is>
       </c>
-      <c r="H74" s="61" t="inlineStr">
+      <c r="H86" s="61" t="inlineStr">
         <is>
           <t>HDD 1000Gb</t>
         </is>
       </c>
-      <c r="I74" s="61" t="inlineStr">
+      <c r="I86" s="61" t="inlineStr">
         <is>
           <t>CentOS Stream 9</t>
         </is>
       </c>
-      <c r="J74" s="61" t="inlineStr">
+      <c r="J86" s="61" t="inlineStr">
         <is>
           <t>localhost</t>
         </is>
       </c>
-      <c r="K74" s="61" t="inlineStr">
+      <c r="K86" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L74" s="61" t="inlineStr">
+      <c r="L86" s="61" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="M74" s="61" t="inlineStr">
+      <c r="M86" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="15" t="n">
+    <row r="87">
+      <c r="A87" s="15" t="n">
         <v>46164</v>
       </c>
-      <c r="B75" s="63" t="inlineStr">
+      <c r="B87" s="63" t="inlineStr">
         <is>
           <t>10.67.40.20</t>
         </is>
       </c>
-      <c r="C75" s="64" t="inlineStr">
+      <c r="C87" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:12:36:42</t>
         </is>
       </c>
-      <c r="D75" s="61" t="inlineStr">
+      <c r="D87" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E75" s="61" t="inlineStr">
+      <c r="E87" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F75" s="61" t="inlineStr">
+      <c r="F87" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G75" s="61" t="inlineStr">
+      <c r="G87" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H75" s="61" t="inlineStr">
+      <c r="H87" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I75" s="61" t="inlineStr">
+      <c r="I87" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J75" s="61" t="inlineStr">
+      <c r="J87" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K75" s="61" t="inlineStr">
+      <c r="K87" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L75" s="61" t="inlineStr">
+      <c r="L87" s="61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M75" s="61" t="inlineStr">
+      <c r="M87" s="61" t="inlineStr">
         <is>
           <t>tuber</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="14" t="n">
+    <row r="88">
+      <c r="A88" s="14" t="n">
         <v>46164</v>
       </c>
-      <c r="B76" s="63" t="inlineStr">
+      <c r="B88" s="63" t="inlineStr">
         <is>
           <t>10.67.40.17</t>
         </is>
       </c>
-      <c r="C76" s="64" t="inlineStr">
+      <c r="C88" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:12:36:49</t>
         </is>
       </c>
-      <c r="D76" s="61" t="inlineStr">
+      <c r="D88" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E76" s="61" t="inlineStr">
+      <c r="E88" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F76" s="61" t="inlineStr">
+      <c r="F88" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G76" s="61" t="inlineStr">
+      <c r="G88" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H76" s="61" t="inlineStr">
+      <c r="H88" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I76" s="61" t="inlineStr">
+      <c r="I88" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J76" s="61" t="inlineStr">
+      <c r="J88" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K76" s="61" t="inlineStr">
+      <c r="K88" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L76" s="61" t="inlineStr">
+      <c r="L88" s="61" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M76" s="61" t="inlineStr">
+      <c r="M88" s="61" t="inlineStr">
         <is>
           <t>tuber</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
+    <row r="89">
+      <c r="A89" s="7" t="n">
         <v>46150</v>
       </c>
-      <c r="B77" s="63" t="inlineStr">
+      <c r="B89" s="63" t="inlineStr">
         <is>
           <t>10.67.64.62</t>
         </is>
       </c>
-      <c r="C77" s="64" t="inlineStr">
+      <c r="C89" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:17:59:a3</t>
         </is>
       </c>
-      <c r="D77" s="61" t="inlineStr">
+      <c r="D89" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E77" s="61" t="inlineStr">
+      <c r="E89" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F77" s="61" t="inlineStr">
+      <c r="F89" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G77" s="61" t="inlineStr">
+      <c r="G89" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H77" s="61" t="inlineStr">
+      <c r="H89" s="61" t="inlineStr">
         <is>
           <t>256 GB/238 GiB</t>
         </is>
       </c>
-      <c r="I77" s="61" t="inlineStr">
+      <c r="I89" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J77" s="61" t="inlineStr">
+      <c r="J89" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K77" s="61" t="inlineStr">
+      <c r="K89" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L77" s="61" t="inlineStr">
+      <c r="L89" s="61" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="M77" s="61" t="inlineStr">
+      <c r="M89" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="7" t="n">
+    <row r="90">
+      <c r="A90" s="7" t="n">
         <v>46148</v>
       </c>
-      <c r="B78" s="63" t="inlineStr">
+      <c r="B90" s="63" t="inlineStr">
         <is>
           <t>192.168.0.139</t>
         </is>
       </c>
-      <c r="C78" s="64" t="inlineStr">
+      <c r="C90" s="64" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="D78" s="61" t="inlineStr">
+      <c r="D90" s="61" t="inlineStr">
         <is>
           <t>ASRock J3355M</t>
         </is>
       </c>
-      <c r="E78" s="61" t="inlineStr">
+      <c r="E90" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) J3355 2.00GHz </t>
         </is>
       </c>
-      <c r="F78" s="61" t="inlineStr">
+      <c r="F90" s="61" t="inlineStr">
         <is>
           <t>6Gb</t>
         </is>
       </c>
-      <c r="G78" s="61" t="inlineStr">
+      <c r="G90" s="61" t="inlineStr">
         <is>
           <t>WDC WD5000BPVT-2</t>
         </is>
       </c>
-      <c r="H78" s="61" t="inlineStr">
+      <c r="H90" s="61" t="inlineStr">
         <is>
           <t>500 GB/466 GiB</t>
         </is>
       </c>
-      <c r="I78" s="61" t="inlineStr">
+      <c r="I90" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 8.2</t>
         </is>
       </c>
-      <c r="J78" s="61" t="inlineStr">
+      <c r="J90" s="61" t="inlineStr">
         <is>
           <t>home-comp</t>
         </is>
       </c>
-      <c r="K78" s="61" t="inlineStr">
+      <c r="K90" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L78" s="61" t="inlineStr">
+      <c r="L90" s="61" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="M78" s="61" t="inlineStr">
+      <c r="M90" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>

--- a/base/list-points.xlsx
+++ b/base/list-points.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:XFD90"/>
+  <dimension ref="A1:XFD92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" customWidth="1" style="70" min="1" max="1"/>
@@ -1721,62 +1721,62 @@
     <row r="11" ht="18" customHeight="1" s="70">
       <c r="A11" s="72" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B11" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.77</t>
+          <t>10.67.14.161</t>
         </is>
       </c>
       <c r="C11" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B4:DD</t>
+          <t>18-C0-4D-CD-F2-E9</t>
         </is>
       </c>
       <c r="D11" s="75" t="inlineStr">
         <is>
-          <t>DEPO Computers DPH110S</t>
+          <t>Gigabyte H410M H V3</t>
         </is>
       </c>
       <c r="E11" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i3-9100 3.60GHz</t>
+          <t>Intel Core i3-10105 CPU 3.70GHz</t>
         </is>
       </c>
       <c r="F11" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>Samsung SSD 870 EVO 500GB</t>
         </is>
       </c>
       <c r="H11" s="75" t="inlineStr">
         <is>
-          <t>SSD 240Gb</t>
+          <t>SSD-500Gb</t>
         </is>
       </c>
       <c r="I11" s="75" t="inlineStr">
         <is>
-          <t>ALT 8 SP Workstation (cliff)</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J11" s="75" t="inlineStr">
         <is>
-          <t>comp-pentium-gold-002096</t>
+          <t>WS-014-161</t>
         </is>
       </c>
       <c r="K11" s="75" t="inlineStr">
         <is>
-          <t>hp402</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L11" s="75" t="inlineStr">
         <is>
-          <t>регистратура 2 окно</t>
+          <t>510</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
@@ -1786,34 +1786,34 @@
       </c>
       <c r="N11" s="75" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20.1" customHeight="1" s="70">
       <c r="A12" s="72" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B12" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.59</t>
+          <t>10.67.64.6</t>
         </is>
       </c>
       <c r="C12" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B1:CF</t>
+          <t>00:58:3F:17:59:32</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
         <is>
-          <t>DEPO Computers DPH110S</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E12" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F12" s="75" t="inlineStr">
@@ -1823,32 +1823,32 @@
       </c>
       <c r="G12" s="75" t="inlineStr">
         <is>
-          <t>KINGSTON_SA400S37240G</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>SSD 240Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I12" s="75" t="inlineStr">
         <is>
-          <t>ALT 8 SP Workstation (cliff)</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J12" s="75" t="inlineStr">
         <is>
-          <t>comp-pentium-gold-002096</t>
+          <t>comp-core-i7-8700t-1051a2</t>
         </is>
       </c>
       <c r="K12" s="75" t="inlineStr">
         <is>
-          <t>M428</t>
+          <t>HP LaserJet Pro M404dn</t>
         </is>
       </c>
       <c r="L12" s="75" t="inlineStr">
         <is>
-          <t>регистратура 3 окно</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="N12" s="75" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B13" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.61</t>
+          <t>10.67.28.77</t>
         </is>
       </c>
       <c r="C13" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:A5:45</t>
+          <t>F8:CC:6E:00:B4:DD</t>
         </is>
       </c>
       <c r="D13" s="75" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E13" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
+          <t>Intel(R) i3-9100 3.60GHz</t>
         </is>
       </c>
       <c r="F13" s="75" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H13" s="75" t="inlineStr">
         <is>
-          <t>SSD 120Gb</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I13" s="75" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="K13" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>hp402</t>
         </is>
       </c>
       <c r="L13" s="75" t="inlineStr">
         <is>
-          <t>регистратура 1 окно</t>
+          <t>регистратура 2 окно</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="N13" s="75" t="inlineStr">
         <is>
-          <t>88541</t>
+          <t>78535</t>
         </is>
       </c>
     </row>
@@ -1942,57 +1942,57 @@
       </c>
       <c r="B14" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.141</t>
+          <t>10.67.28.59</t>
         </is>
       </c>
       <c r="C14" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-74</t>
+          <t>F8:CC:6E:00:B1:CF</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star International Co., Ltd.  A320M-A PRO (MS-7C51)</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E14" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F14" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G14" s="75" t="inlineStr">
         <is>
-          <t>Smartbuy SSD 256GB</t>
+          <t>KINGSTON_SA400S37240G</t>
         </is>
       </c>
       <c r="H14" s="75" t="inlineStr">
         <is>
-          <t>SSD-256Gb</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I14" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J14" s="75" t="inlineStr">
         <is>
-          <t>WS-14-141</t>
+          <t>comp-pentium-gold-002096</t>
         </is>
       </c>
       <c r="K14" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>M428</t>
         </is>
       </c>
       <c r="L14" s="75" t="inlineStr">
         <is>
-          <t>регистратура 2 окно</t>
+          <t>регистратура 3 окно</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="N14" s="75" t="inlineStr">
         <is>
-          <t>88746</t>
+          <t>88546</t>
         </is>
       </c>
     </row>
@@ -2014,47 +2014,47 @@
       </c>
       <c r="B15" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.130</t>
+          <t>10.67.28.61</t>
         </is>
       </c>
       <c r="C15" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-36</t>
+          <t>F8:CC:6E:00:A5:45</t>
         </is>
       </c>
       <c r="D15" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME A320M-A</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E15" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F15" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G15" s="75" t="inlineStr">
         <is>
-          <t>ST1000DM010-2EP102</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H15" s="75" t="inlineStr">
         <is>
-          <t>HDD-1Tb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I15" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J15" s="75" t="inlineStr">
         <is>
-          <t>DESKTOP-MQADVRK</t>
+          <t>comp-pentium-gold-002096</t>
         </is>
       </c>
       <c r="K15" s="75" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="L15" s="75" t="inlineStr">
         <is>
-          <t>регистратура 3 окно</t>
+          <t>регистратура 1 окно</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="N15" s="75" t="inlineStr">
         <is>
-          <t>114130</t>
+          <t>88541</t>
         </is>
       </c>
     </row>
@@ -2086,17 +2086,17 @@
       </c>
       <c r="B16" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.132 / 192.168.56.1</t>
+          <t>10.67.14.141</t>
         </is>
       </c>
       <c r="C16" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-2A / 0A-00-27-00-00-07</t>
+          <t>2C-F0-5D-9E-B2-74</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME A320M-A</t>
+          <t>Micro-Star International Co., Ltd.  A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E16" s="75" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="G16" s="75" t="inlineStr">
         <is>
-          <t>ST1000DM010-2EP102</t>
+          <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>HDD-1Tb</t>
+          <t>SSD-256Gb</t>
         </is>
       </c>
       <c r="I16" s="75" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="J16" s="75" t="inlineStr">
         <is>
-          <t>WS-014-132</t>
+          <t>WS-14-141</t>
         </is>
       </c>
       <c r="K16" s="75" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="L16" s="75" t="inlineStr">
         <is>
-          <t>регистратура 1 окно</t>
+          <t>регистратура 2 окно</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="N16" s="75" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>88746</t>
         </is>
       </c>
     </row>
@@ -2158,129 +2158,129 @@
       </c>
       <c r="B17" s="73" t="inlineStr">
         <is>
-          <t>10.67.38.49</t>
+          <t>10.67.14.130</t>
         </is>
       </c>
       <c r="C17" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:12:1D:31</t>
+          <t>04-D9-F5-81-FB-36</t>
         </is>
       </c>
       <c r="D17" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E17" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F17" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G17" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H17" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I17" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J17" s="75" t="inlineStr">
         <is>
-          <t>comp-core-i7-8700t-1051a2</t>
+          <t>DESKTOP-MQADVRK</t>
         </is>
       </c>
       <c r="K17" s="75" t="inlineStr">
         <is>
-          <t>HP_LaserJet_MFP_M28-M31</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L17" s="75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>регистратура 3 окно</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N17" s="75" t="inlineStr">
         <is>
-          <t>89591</t>
+          <t>114130</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="70">
       <c r="A18" s="72" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B18" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.26</t>
+          <t>10.67.14.132 / 192.168.56.1</t>
         </is>
       </c>
       <c r="C18" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:76:0C</t>
+          <t>04-D9-F5-81-FB-2A / 0A-00-27-00-00-07</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E18" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F18" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G18" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H18" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I18" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J18" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-014-132</t>
         </is>
       </c>
       <c r="K18" s="75" t="inlineStr">
         <is>
-          <t>Samsung-SCX-483x-5x3x-Series</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L18" s="75" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>регистратура 1 окно</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="N18" s="75" t="inlineStr">
         <is>
-          <t>91036</t>
+          <t>114132</t>
         </is>
       </c>
     </row>
@@ -2302,17 +2302,17 @@
       </c>
       <c r="B19" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.88</t>
+          <t>10.67.38.49</t>
         </is>
       </c>
       <c r="C19" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:72:F0</t>
+          <t>00:58:3F:12:1D:31</t>
         </is>
       </c>
       <c r="D19" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E19" s="75" t="inlineStr">
@@ -2342,44 +2342,44 @@
       </c>
       <c r="J19" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>comp-core-i7-8700t-1051a2</t>
         </is>
       </c>
       <c r="K19" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP_LaserJet_MFP_M28-M31</t>
         </is>
       </c>
       <c r="L19" s="75" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="N19" s="75" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>89591</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="70">
       <c r="A20" s="72" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B20" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.66</t>
+          <t>10.67.64.26</t>
         </is>
       </c>
       <c r="C20" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:64:28</t>
+          <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="K20" s="75" t="inlineStr">
         <is>
-          <t>Samsung-SCX-3400-Series</t>
+          <t>Samsung-SCX-483x-5x3x-Series</t>
         </is>
       </c>
       <c r="L20" s="75" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
@@ -2434,29 +2434,29 @@
       </c>
       <c r="N20" s="75" t="inlineStr">
         <is>
-          <t>89722</t>
+          <t>91036</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="70">
       <c r="A21" s="72" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B21" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.82</t>
+          <t>10.67.64.88</t>
         </is>
       </c>
       <c r="C21" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:0F:3F:87</t>
+          <t>00:58:3F:17:72:F0</t>
         </is>
       </c>
       <c r="D21" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E21" s="75" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="K21" s="75" t="inlineStr">
         <is>
-          <t>HP_LaserJet_Professional_P1102</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L21" s="75" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>542</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
@@ -2506,29 +2506,29 @@
       </c>
       <c r="N21" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89588</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20.1" customHeight="1" s="70">
       <c r="A22" s="72" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B22" s="73" t="inlineStr">
         <is>
-          <t>10.67.11.32</t>
+          <t>10.67.64.66</t>
         </is>
       </c>
       <c r="C22" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:0D:24:AD</t>
+          <t>00:58:3F:17:64:28</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME B365M-C</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E22" s="75" t="inlineStr">
@@ -2543,104 +2543,104 @@
       </c>
       <c r="G22" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE FLSSD256X5</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H22" s="75" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I22" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 10.4</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J22" s="75" t="inlineStr">
         <is>
-          <t>dpk5324</t>
+          <t>1051a2</t>
         </is>
       </c>
       <c r="K22" s="75" t="inlineStr">
         <is>
-          <t>POScentre</t>
+          <t>Samsung-SCX-3400-Series</t>
         </is>
       </c>
       <c r="L22" s="75" t="inlineStr">
         <is>
-          <t>312-3211</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
         <is>
-          <t>uprav</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N22" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89722</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="70">
       <c r="A23" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B23" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.74</t>
+          <t>10.67.64.82</t>
         </is>
       </c>
       <c r="C23" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B1:92</t>
+          <t>00:58:3F:0F:3F:87</t>
         </is>
       </c>
       <c r="D23" s="75" t="inlineStr">
         <is>
-          <t>DEPO Computers DPH110S</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E23" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i3-9100 3.60GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F23" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G23" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H23" s="75" t="inlineStr">
         <is>
-          <t>SSD 240Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I23" s="75" t="inlineStr">
         <is>
-          <t>ALT 8 SP Workstation (cliff)</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J23" s="75" t="inlineStr">
         <is>
-          <t>002096</t>
+          <t>1051a2</t>
         </is>
       </c>
       <c r="K23" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP_LaserJet_Professional_P1102</t>
         </is>
       </c>
       <c r="L23" s="75" t="inlineStr">
         <is>
-          <t>регистратура 4 окно</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
@@ -2650,34 +2650,34 @@
       </c>
       <c r="N23" s="75" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="70">
       <c r="A24" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B24" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.57</t>
+          <t>10.67.11.32</t>
         </is>
       </c>
       <c r="C24" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:A2:9E</t>
+          <t>00:58:3F:0D:24:AD</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
         <is>
-          <t>DEPO Computers DPH110S</t>
+          <t>ASUSTeK PRIME B365M-C</t>
         </is>
       </c>
       <c r="E24" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F24" s="75" t="inlineStr">
@@ -2687,112 +2687,116 @@
       </c>
       <c r="G24" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>FOXLINE FLSSD256X5</t>
         </is>
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>SSD 120Gb</t>
+          <t>SSD 256Gb</t>
         </is>
       </c>
       <c r="I24" s="75" t="inlineStr">
         <is>
-          <t>ALT 8 SP Workstation (cliff)</t>
+          <t>ALT Workstation 10.4</t>
         </is>
       </c>
       <c r="J24" s="75" t="inlineStr">
         <is>
-          <t>002096</t>
+          <t>dpk5324</t>
         </is>
       </c>
       <c r="K24" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>POScentre</t>
         </is>
       </c>
       <c r="L24" s="75" t="inlineStr">
         <is>
-          <t>регистратура 5 окно</t>
+          <t>312-3211</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>uprav</t>
         </is>
       </c>
       <c r="N24" s="75" t="inlineStr">
         <is>
-          <t>88536</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20.1" customHeight="1" s="70">
       <c r="A25" s="72" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B25" s="73" t="inlineStr">
         <is>
-          <t>10.67.40.22</t>
+          <t>10.67.28.74</t>
         </is>
       </c>
       <c r="C25" s="74" t="inlineStr">
         <is>
-          <t>70-85-C2-0F-89-20</t>
+          <t>F8:CC:6E:00:B1:92</t>
         </is>
       </c>
       <c r="D25" s="75" t="inlineStr">
         <is>
-          <t>ASRock H81M-VG4 R3.0</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E25" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-4160 3.60GHz</t>
+          <t>Intel(R) i3-9100 3.60GHz</t>
         </is>
       </c>
       <c r="F25" s="75" t="inlineStr">
         <is>
-          <t>4Gb</t>
+          <t>8Gb</t>
         </is>
       </c>
       <c r="G25" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H25" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I25" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J25" s="75" t="inlineStr">
         <is>
-          <t>WS-040-022</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K25" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet MFP M129-M134 PCLmS</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L25" s="75" t="inlineStr">
         <is>
-          <t>заведующая</t>
+          <t>регистратура 4 окно</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
         <is>
-          <t>туберкулёз</t>
-        </is>
-      </c>
-      <c r="N25" s="75" t="inlineStr"/>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N25" s="75" t="inlineStr">
+        <is>
+          <t>88520</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20.1" customHeight="1" s="70">
       <c r="A26" s="72" t="inlineStr">
@@ -2802,47 +2806,47 @@
       </c>
       <c r="B26" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.145</t>
+          <t>10.67.28.57</t>
         </is>
       </c>
       <c r="C26" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-EA</t>
+          <t>F8:CC:6E:00:A2:9E</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star A320M-A PRO (MS-7C51)</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E26" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F26" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G26" s="75" t="inlineStr">
         <is>
-          <t>Smartbuy SSD 256GB</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>SSD-256Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I26" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J26" s="75" t="inlineStr">
         <is>
-          <t>WS-014-145</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K26" s="75" t="inlineStr">
@@ -2852,7 +2856,7 @@
       </c>
       <c r="L26" s="75" t="inlineStr">
         <is>
-          <t>регистратура - 6 окно</t>
+          <t>регистратура 5 окно</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
@@ -2862,49 +2866,49 @@
       </c>
       <c r="N26" s="75" t="inlineStr">
         <is>
-          <t>88749</t>
+          <t>88536</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20.1" customHeight="1" s="70">
       <c r="A27" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B27" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.146</t>
+          <t>10.67.40.22</t>
         </is>
       </c>
       <c r="C27" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-5D</t>
+          <t>70-85-C2-0F-89-20</t>
         </is>
       </c>
       <c r="D27" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star  A320M-A PRO (MS-7C51)</t>
+          <t>ASRock H81M-VG4 R3.0</t>
         </is>
       </c>
       <c r="E27" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel i3-4160 3.60GHz</t>
         </is>
       </c>
       <c r="F27" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>4Gb</t>
         </is>
       </c>
       <c r="G27" s="75" t="inlineStr">
         <is>
-          <t>Smartbuy SSD 256GB</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H27" s="75" t="inlineStr">
         <is>
-          <t>SSD-256Gb</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I27" s="75" t="inlineStr">
@@ -2914,69 +2918,65 @@
       </c>
       <c r="J27" s="75" t="inlineStr">
         <is>
-          <t>WS-014-146</t>
+          <t>WS-040-022</t>
         </is>
       </c>
       <c r="K27" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP LaserJet MFP M129-M134 PCLmS</t>
         </is>
       </c>
       <c r="L27" s="75" t="inlineStr">
         <is>
-          <t>регистратура 5 окно</t>
+          <t>заведующая</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
-        </is>
-      </c>
-      <c r="N27" s="75" t="inlineStr">
-        <is>
-          <t>88745</t>
-        </is>
-      </c>
+          <t>туберкулёз</t>
+        </is>
+      </c>
+      <c r="N27" s="75" t="inlineStr"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="70">
       <c r="A28" s="72" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B28" s="73" t="inlineStr">
         <is>
-          <t>10.67.40.24</t>
+          <t>10.67.14.145</t>
         </is>
       </c>
       <c r="C28" s="74" t="inlineStr">
         <is>
-          <t>10-FF-E0-28-EC-18</t>
+          <t>2C-F0-5D-9E-B2-EA</t>
         </is>
       </c>
       <c r="D28" s="75" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>Micro-Star A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E28" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F28" s="75" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G28" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SSD-256Gb</t>
         </is>
       </c>
       <c r="I28" s="75" t="inlineStr">
@@ -2986,25 +2986,29 @@
       </c>
       <c r="J28" s="75" t="inlineStr">
         <is>
-          <t>WS-040-024</t>
+          <t>WS-014-145</t>
         </is>
       </c>
       <c r="K28" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Professional M1214nfh MFP</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L28" s="75" t="inlineStr">
         <is>
-          <t>9 заведующая</t>
+          <t>регистратура - 6 окно</t>
         </is>
       </c>
       <c r="M28" s="75" t="inlineStr">
         <is>
-          <t>туберкулёз</t>
-        </is>
-      </c>
-      <c r="N28" s="75" t="inlineStr"/>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N28" s="75" t="inlineStr">
+        <is>
+          <t>88749</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20.1" customHeight="1" s="70">
       <c r="A29" s="72" t="inlineStr">
@@ -3014,17 +3018,17 @@
       </c>
       <c r="B29" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.133</t>
+          <t>10.67.14.146</t>
         </is>
       </c>
       <c r="C29" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-2B</t>
+          <t>2C-F0-5D-9E-B2-5D</t>
         </is>
       </c>
       <c r="D29" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME A320M-A</t>
+          <t>Micro-Star  A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E29" s="75" t="inlineStr">
@@ -3039,12 +3043,12 @@
       </c>
       <c r="G29" s="75" t="inlineStr">
         <is>
-          <t>ST1000DM010-2EP102</t>
+          <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
       <c r="H29" s="75" t="inlineStr">
         <is>
-          <t>HDD-1Tb</t>
+          <t>SSD-256Gb</t>
         </is>
       </c>
       <c r="I29" s="75" t="inlineStr">
@@ -3054,7 +3058,7 @@
       </c>
       <c r="J29" s="75" t="inlineStr">
         <is>
-          <t>WS-014-133</t>
+          <t>WS-014-146</t>
         </is>
       </c>
       <c r="K29" s="75" t="inlineStr">
@@ -3064,7 +3068,7 @@
       </c>
       <c r="L29" s="75" t="inlineStr">
         <is>
-          <t>регитратура 4 окно</t>
+          <t>регистратура 5 окно</t>
         </is>
       </c>
       <c r="M29" s="75" t="inlineStr">
@@ -3074,29 +3078,29 @@
       </c>
       <c r="N29" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>88745</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20.1" customHeight="1" s="70">
       <c r="A30" s="72" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B30" s="73" t="inlineStr">
         <is>
-          <t>192.168.56.1</t>
+          <t>10.67.40.24</t>
         </is>
       </c>
       <c r="C30" s="74" t="inlineStr">
         <is>
-          <t>04-42-1A-0F-29-A3</t>
+          <t>10-FF-E0-28-EC-18</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME H510M-R</t>
+          <t>Gigabyte H410M K</t>
         </is>
       </c>
       <c r="E30" s="75" t="inlineStr">
@@ -3126,22 +3130,22 @@
       </c>
       <c r="J30" s="75" t="inlineStr">
         <is>
-          <t>WS-014-0198</t>
+          <t>WS-040-024</t>
         </is>
       </c>
       <c r="K30" s="75" t="inlineStr">
         <is>
-          <t>HP Color LaserJet Pro MFP 4303</t>
+          <t>HP LaserJet Professional M1214nfh MFP</t>
         </is>
       </c>
       <c r="L30" s="75" t="inlineStr">
         <is>
-          <t>Кирилл Николаевич приемная</t>
+          <t>9 заведующая</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>туберкулёз</t>
         </is>
       </c>
       <c r="N30" s="75" t="inlineStr"/>
@@ -3154,57 +3158,57 @@
       </c>
       <c r="B31" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.87</t>
+          <t>10.67.14.133</t>
         </is>
       </c>
       <c r="C31" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:72:20</t>
+          <t>04-D9-F5-81-FB-2B</t>
         </is>
       </c>
       <c r="D31" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E31" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F31" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G31" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H31" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I31" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J31" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-014-133</t>
         </is>
       </c>
       <c r="K31" s="75" t="inlineStr">
         <is>
-          <t>M428</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L31" s="75" t="inlineStr">
         <is>
-          <t>регистратура - 6 окно</t>
+          <t>регитратура 4 окно</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
@@ -3214,69 +3218,69 @@
       </c>
       <c r="N31" s="75" t="inlineStr">
         <is>
-          <t>89636</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20.1" customHeight="1" s="70">
       <c r="A32" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B32" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>192.168.56.1</t>
         </is>
       </c>
       <c r="C32" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>04-42-1A-0F-29-A3</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>ASUSTeK PRIME H510M-R</t>
         </is>
       </c>
       <c r="E32" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
       <c r="F32" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G32" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H32" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I32" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J32" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-014-0198</t>
         </is>
       </c>
       <c r="K32" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP Color LaserJet Pro MFP 4303</t>
         </is>
       </c>
       <c r="L32" s="75" t="inlineStr">
         <is>
-          <t>регистратура - расписание</t>
+          <t>Кирилл Николаевич приемная</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
@@ -3284,11 +3288,7 @@
           <t>pol1</t>
         </is>
       </c>
-      <c r="N32" s="75" t="inlineStr">
-        <is>
-          <t>89681</t>
-        </is>
-      </c>
+      <c r="N32" s="75" t="inlineStr"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="70">
       <c r="A33" s="72" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B33" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.103</t>
+          <t>10.67.64.87</t>
         </is>
       </c>
       <c r="C33" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:10</t>
+          <t>00:58:3F:17:72:20</t>
         </is>
       </c>
       <c r="D33" s="75" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G33" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5 DataTraveler_3.0</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H33" s="75" t="inlineStr">
@@ -3343,39 +3343,39 @@
       </c>
       <c r="K33" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>M428</t>
         </is>
       </c>
       <c r="L33" s="75" t="inlineStr">
         <is>
-          <t>ординаторская</t>
+          <t>регистратура - 6 окно</t>
         </is>
       </c>
       <c r="M33" s="75" t="inlineStr">
         <is>
-          <t>хирургия онкология 3 этаж</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N33" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89636</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20.1" customHeight="1" s="70">
       <c r="A34" s="72" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B34" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.73</t>
+          <t>10.67.64.98</t>
         </is>
       </c>
       <c r="C34" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:5A:FA</t>
+          <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F34" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G34" s="75" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="K34" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet 1320</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L34" s="75" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>регистратура - расписание</t>
         </is>
       </c>
       <c r="M34" s="75" t="inlineStr">
@@ -3428,7 +3428,11 @@
           <t>pol1</t>
         </is>
       </c>
-      <c r="N34" s="75" t="inlineStr"/>
+      <c r="N34" s="75" t="inlineStr">
+        <is>
+          <t>89681</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20.1" customHeight="1" s="70">
       <c r="A35" s="72" t="inlineStr">
@@ -3438,17 +3442,17 @@
       </c>
       <c r="B35" s="73" t="inlineStr">
         <is>
-          <t>10.67.12.77</t>
+          <t>10.67.64.103</t>
         </is>
       </c>
       <c r="C35" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:16:55:32</t>
+          <t>00:58:3F:17:6A:10</t>
         </is>
       </c>
       <c r="D35" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E35" s="75" t="inlineStr">
@@ -3463,7 +3467,7 @@
       </c>
       <c r="G35" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>FOXLINE_FLSSD256X5 DataTraveler_3.0</t>
         </is>
       </c>
       <c r="H35" s="75" t="inlineStr">
@@ -3493,7 +3497,7 @@
       </c>
       <c r="M35" s="75" t="inlineStr">
         <is>
-          <t>жирургия онкология 3 этаж</t>
+          <t>хирургия онкология 3 этаж</t>
         </is>
       </c>
       <c r="N35" s="75" t="inlineStr">
@@ -3530,193 +3534,199 @@
       </c>
       <c r="F36" s="75" t="inlineStr">
         <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G36" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H36" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I36" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J36" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K36" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet 1320</t>
+        </is>
+      </c>
+      <c r="L36" s="75" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="M36" s="75" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N36" s="75" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20.1" customHeight="1" s="70">
+      <c r="A37" s="72" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B37" s="73" t="inlineStr">
+        <is>
+          <t>10.67.12.77</t>
+        </is>
+      </c>
+      <c r="C37" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:16:55:32</t>
+        </is>
+      </c>
+      <c r="D37" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQB365MC</t>
+        </is>
+      </c>
+      <c r="E37" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F37" s="75" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G37" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H37" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I37" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J37" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K37" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro MFP 4103</t>
+        </is>
+      </c>
+      <c r="L37" s="75" t="inlineStr">
+        <is>
+          <t>ординаторская</t>
+        </is>
+      </c>
+      <c r="M37" s="75" t="inlineStr">
+        <is>
+          <t>жирургия онкология 3 этаж</t>
+        </is>
+      </c>
+      <c r="N37" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20.1" customHeight="1" s="70">
+      <c r="A38" s="72" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>10.67.64.73</t>
+        </is>
+      </c>
+      <c r="C38" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:5A:FA</t>
+        </is>
+      </c>
+      <c r="D38" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E38" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F38" s="75" t="inlineStr">
+        <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G36" s="75" t="inlineStr">
+      <c r="G38" s="75" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H36" s="75" t="inlineStr">
+      <c r="H38" s="75" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I36" s="75" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J36" s="75" t="inlineStr">
+      <c r="J38" s="75" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K36" s="75" t="inlineStr">
+      <c r="K38" s="75" t="inlineStr">
         <is>
           <t>HP LaserJet 1320</t>
         </is>
       </c>
-      <c r="L36" s="75" t="inlineStr">
+      <c r="L38" s="75" t="inlineStr">
         <is>
           <t>828</t>
         </is>
       </c>
-      <c r="M36" s="75" t="inlineStr">
+      <c r="M38" s="75" t="inlineStr">
         <is>
           <t>pol1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20.1" customHeight="1" s="70">
-      <c r="A37" s="66" t="inlineStr">
-        <is>
-          <t>29.07.2026</t>
-        </is>
-      </c>
-      <c r="B37" s="63" t="inlineStr">
-        <is>
-          <t>10.67.14.168</t>
-        </is>
-      </c>
-      <c r="C37" s="64" t="inlineStr">
-        <is>
-          <t>F8:CC:6E:00:AF:29</t>
-        </is>
-      </c>
-      <c r="D37" s="65" t="inlineStr">
-        <is>
-          <t>DEPO Computers DPH110S</t>
-        </is>
-      </c>
-      <c r="E37" s="65" t="inlineStr">
-        <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
-        </is>
-      </c>
-      <c r="F37" s="65" t="inlineStr">
-        <is>
-          <t>8GB</t>
-        </is>
-      </c>
-      <c r="G37" s="65" t="inlineStr">
-        <is>
-          <t>QUMO_SSD ProductCode</t>
-        </is>
-      </c>
-      <c r="H37" s="65" t="inlineStr">
-        <is>
-          <t>SSD 120Gb</t>
-        </is>
-      </c>
-      <c r="I37" s="65" t="inlineStr">
-        <is>
-          <t>ALT 8 SP Workstation</t>
-        </is>
-      </c>
-      <c r="J37" s="65" t="inlineStr">
-        <is>
-          <t>002096</t>
-        </is>
-      </c>
-      <c r="K37" s="65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L37" s="65" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="M37" s="65" t="inlineStr">
-        <is>
-          <t>pol1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20.1" customHeight="1" s="70">
-      <c r="A38" s="66" t="inlineStr">
-        <is>
-          <t>04.08.2026</t>
-        </is>
-      </c>
-      <c r="B38" s="63" t="inlineStr">
-        <is>
-          <t>10.67.28.72</t>
-        </is>
-      </c>
-      <c r="C38" s="64" t="inlineStr">
-        <is>
-          <t>F8:CC:6E:00:5B:1A</t>
-        </is>
-      </c>
-      <c r="D38" s="65" t="inlineStr">
-        <is>
-          <t>DEPO Computers DPH110S</t>
-        </is>
-      </c>
-      <c r="E38" s="65" t="inlineStr">
-        <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
-        </is>
-      </c>
-      <c r="F38" s="65" t="inlineStr">
-        <is>
-          <t>8GB</t>
-        </is>
-      </c>
-      <c r="G38" s="65" t="inlineStr">
-        <is>
-          <t>QUMO_SSD</t>
-        </is>
-      </c>
-      <c r="H38" s="65" t="inlineStr">
-        <is>
-          <t>SSD 120Gb</t>
-        </is>
-      </c>
-      <c r="I38" s="65" t="inlineStr">
-        <is>
-          <t>ALT 8 SP Workstation</t>
-        </is>
-      </c>
-      <c r="J38" s="65" t="inlineStr">
-        <is>
-          <t>002096</t>
-        </is>
-      </c>
-      <c r="K38" s="65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L38" s="65" t="inlineStr">
-        <is>
-          <t>ord</t>
-        </is>
-      </c>
-      <c r="M38" s="65" t="inlineStr">
-        <is>
-          <t>rod-3</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20.1" customHeight="1" s="70">
       <c r="A39" s="66" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B39" s="63" t="inlineStr">
         <is>
-          <t>10.67.28.69</t>
+          <t>10.67.14.168</t>
         </is>
       </c>
       <c r="C39" s="64" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:4F:13</t>
+          <t>F8:CC:6E:00:AF:29</t>
         </is>
       </c>
       <c r="D39" s="65" t="inlineStr">
@@ -3736,7 +3746,7 @@
       </c>
       <c r="G39" s="65" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>QUMO_SSD ProductCode</t>
         </is>
       </c>
       <c r="H39" s="65" t="inlineStr">
@@ -3756,111 +3766,111 @@
       </c>
       <c r="K39" s="65" t="inlineStr">
         <is>
-          <t>Samsung SCX-4833FD</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L39" s="65" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M39" s="65" t="inlineStr">
         <is>
-          <t>det.pol</t>
+          <t>pol1</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20.1" customHeight="1" s="70">
       <c r="A40" s="66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>10.67.28.72</t>
         </is>
       </c>
       <c r="C40" s="64" t="inlineStr">
         <is>
-          <t>10:FF:E0:63:F1:98</t>
+          <t>F8:CC:6E:00:5B:1A</t>
         </is>
       </c>
       <c r="D40" s="65" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E40" s="65" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F40" s="65" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G40" s="65" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H40" s="65" t="inlineStr">
         <is>
-          <t>SSD 440Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I40" s="65" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation</t>
         </is>
       </c>
       <c r="J40" s="65" t="inlineStr">
         <is>
-          <t>WS-016-052</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K40" s="65" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L40" s="65" t="inlineStr">
         <is>
-          <t>zav</t>
+          <t>ord</t>
         </is>
       </c>
       <c r="M40" s="65" t="inlineStr">
         <is>
-          <t>pblock</t>
+          <t>rod-3</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" s="70">
       <c r="A41" s="66" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B41" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>10.67.28.69</t>
         </is>
       </c>
       <c r="C41" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>F8:CC:6E:00:4F:13</t>
         </is>
       </c>
       <c r="D41" s="65" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E41" s="65" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F41" s="65" t="inlineStr">
@@ -3870,104 +3880,104 @@
       </c>
       <c r="G41" s="65" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H41" s="65" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I41" s="65" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>ALT 8 SP Workstation</t>
         </is>
       </c>
       <c r="J41" s="65" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K41" s="65" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M426fdn</t>
+          <t>Samsung SCX-4833FD</t>
         </is>
       </c>
       <c r="L41" s="65" t="inlineStr">
         <is>
-          <t>reg.raspis</t>
+          <t>314</t>
         </is>
       </c>
       <c r="M41" s="65" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>det.pol</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" s="70">
       <c r="A42" s="66" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.77</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="C42" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:00</t>
+          <t>10:FF:E0:63:F1:98</t>
         </is>
       </c>
       <c r="D42" s="65" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Gigabyte H410M K</t>
         </is>
       </c>
       <c r="E42" s="65" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
       <c r="F42" s="65" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G42" s="65" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="H42" s="65" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>SSD 440Gb</t>
         </is>
       </c>
       <c r="I42" s="65" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J42" s="65" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-016-052</t>
         </is>
       </c>
       <c r="K42" s="65" t="inlineStr">
         <is>
-          <t>Samsung SCX-4833</t>
+          <t>HP LaserJet Pro MFP 4103</t>
         </is>
       </c>
       <c r="L42" s="65" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>zav</t>
         </is>
       </c>
       <c r="M42" s="65" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>pblock</t>
         </is>
       </c>
     </row>
@@ -3979,12 +3989,12 @@
       </c>
       <c r="B43" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.46</t>
+          <t>10.67.64.98</t>
         </is>
       </c>
       <c r="C43" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:69:FE</t>
+          <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
       <c r="D43" s="65" t="inlineStr">
@@ -4024,12 +4034,12 @@
       </c>
       <c r="K43" s="65" t="inlineStr">
         <is>
-          <t>Cups-PDF</t>
+          <t>HP LaserJet Pro M426fdn</t>
         </is>
       </c>
       <c r="L43" s="65" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>reg.raspis</t>
         </is>
       </c>
       <c r="M43" s="65" t="inlineStr">
@@ -4041,17 +4051,17 @@
     <row r="44" ht="20.1" customHeight="1" s="70">
       <c r="A44" s="66" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.67</t>
+          <t>10.67.64.77</t>
         </is>
       </c>
       <c r="C44" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:57:F8</t>
+          <t>00:58:3F:17:6A:00</t>
         </is>
       </c>
       <c r="D44" s="65" t="inlineStr">
@@ -4091,12 +4101,12 @@
       </c>
       <c r="K44" s="65" t="inlineStr">
         <is>
-          <t>HP_LaserJet_Professional_P1102</t>
+          <t>Samsung SCX-4833</t>
         </is>
       </c>
       <c r="L44" s="65" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M44" s="65" t="inlineStr">
@@ -4108,218 +4118,218 @@
     <row r="45" ht="20.1" customHeight="1" s="70">
       <c r="A45" s="66" t="inlineStr">
         <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>10.67.64.46</t>
+        </is>
+      </c>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:69:FE</t>
+        </is>
+      </c>
+      <c r="D45" s="65" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E45" s="65" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F45" s="65" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G45" s="65" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H45" s="65" t="inlineStr">
+        <is>
+          <t>SSD 256Gb</t>
+        </is>
+      </c>
+      <c r="I45" s="65" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J45" s="65" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K45" s="65" t="inlineStr">
+        <is>
+          <t>Cups-PDF</t>
+        </is>
+      </c>
+      <c r="L45" s="65" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M45" s="65" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20.1" customHeight="1" s="70">
+      <c r="A46" s="66" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>10.67.64.67</t>
+        </is>
+      </c>
+      <c r="C46" s="64" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:57:F8</t>
+        </is>
+      </c>
+      <c r="D46" s="65" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E46" s="65" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F46" s="65" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G46" s="65" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H46" s="65" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I46" s="65" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J46" s="65" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K46" s="65" t="inlineStr">
+        <is>
+          <t>HP_LaserJet_Professional_P1102</t>
+        </is>
+      </c>
+      <c r="L46" s="65" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="M46" s="65" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20.1" customHeight="1" s="70">
+      <c r="A47" s="66" t="inlineStr">
+        <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="B45" s="63" t="inlineStr">
+      <c r="B47" s="63" t="inlineStr">
         <is>
           <t>10.67.64.56</t>
         </is>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C47" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:6A</t>
         </is>
       </c>
-      <c r="D45" s="65" t="inlineStr">
+      <c r="D47" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E45" s="65" t="inlineStr">
+      <c r="E47" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F45" s="65" t="inlineStr">
+      <c r="F47" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G45" s="65" t="inlineStr">
+      <c r="G47" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H45" s="65" t="inlineStr">
+      <c r="H47" s="65" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I45" s="65" t="inlineStr">
+      <c r="I47" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J45" s="65" t="inlineStr">
+      <c r="J47" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K45" s="65" t="inlineStr">
+      <c r="K47" s="65" t="inlineStr">
         <is>
           <t>HP_LaserJet_P2055d</t>
         </is>
       </c>
-      <c r="L45" s="65" t="inlineStr">
+      <c r="L47" s="65" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="M45" s="65" t="inlineStr">
+      <c r="M47" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20.1" customHeight="1" s="70">
-      <c r="A46" s="62" t="inlineStr">
-        <is>
-          <t>29.07.2026</t>
-        </is>
-      </c>
-      <c r="B46" s="63" t="inlineStr">
-        <is>
-          <t>10.67.14.168</t>
-        </is>
-      </c>
-      <c r="C46" s="64" t="inlineStr">
-        <is>
-          <t>F8:CC:6E:00:AF:29</t>
-        </is>
-      </c>
-      <c r="D46" s="61" t="inlineStr">
-        <is>
-          <t>DEPO Computers DPH110S</t>
-        </is>
-      </c>
-      <c r="E46" s="61" t="inlineStr">
-        <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
-        </is>
-      </c>
-      <c r="F46" s="61" t="inlineStr">
-        <is>
-          <t>8GB</t>
-        </is>
-      </c>
-      <c r="G46" s="61" t="inlineStr">
-        <is>
-          <t>QUMO_SSD ProductCode</t>
-        </is>
-      </c>
-      <c r="H46" s="61" t="inlineStr">
-        <is>
-          <t>SSD 120Gb</t>
-        </is>
-      </c>
-      <c r="I46" s="61" t="inlineStr">
-        <is>
-          <t>ALT 8 SP Workstation</t>
-        </is>
-      </c>
-      <c r="J46" s="61" t="inlineStr">
-        <is>
-          <t>002096</t>
-        </is>
-      </c>
-      <c r="K46" s="61" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L46" s="61" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="M46" s="61" t="inlineStr">
-        <is>
-          <t>pol1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20.1" customHeight="1" s="70">
-      <c r="A47" s="62" t="inlineStr">
-        <is>
-          <t>04.08.2026</t>
-        </is>
-      </c>
-      <c r="B47" s="63" t="inlineStr">
-        <is>
-          <t>10.67.28.72</t>
-        </is>
-      </c>
-      <c r="C47" s="64" t="inlineStr">
-        <is>
-          <t>F8:CC:6E:00:5B:1A</t>
-        </is>
-      </c>
-      <c r="D47" s="61" t="inlineStr">
-        <is>
-          <t>DEPO Computers DPH110S</t>
-        </is>
-      </c>
-      <c r="E47" s="61" t="inlineStr">
-        <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
-        </is>
-      </c>
-      <c r="F47" s="61" t="inlineStr">
-        <is>
-          <t>8GB</t>
-        </is>
-      </c>
-      <c r="G47" s="61" t="inlineStr">
-        <is>
-          <t>QUMO_SSD</t>
-        </is>
-      </c>
-      <c r="H47" s="61" t="inlineStr">
-        <is>
-          <t>SSD 120Gb</t>
-        </is>
-      </c>
-      <c r="I47" s="61" t="inlineStr">
-        <is>
-          <t>ALT 8 SP Workstation</t>
-        </is>
-      </c>
-      <c r="J47" s="61" t="inlineStr">
-        <is>
-          <t>002096</t>
-        </is>
-      </c>
-      <c r="K47" s="61" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L47" s="61" t="inlineStr">
-        <is>
-          <t>ord</t>
-        </is>
-      </c>
-      <c r="M47" s="61" t="inlineStr">
-        <is>
-          <t>rod3</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20.1" customHeight="1" s="70">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>10.67.28.69</t>
+          <t>10.67.14.168</t>
         </is>
       </c>
       <c r="C48" s="64" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:4F:13</t>
+          <t>F8:CC:6E:00:AF:29</t>
         </is>
       </c>
       <c r="D48" s="61" t="inlineStr">
@@ -4339,7 +4349,7 @@
       </c>
       <c r="G48" s="61" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>QUMO_SSD ProductCode</t>
         </is>
       </c>
       <c r="H48" s="61" t="inlineStr">
@@ -4359,111 +4369,111 @@
       </c>
       <c r="K48" s="61" t="inlineStr">
         <is>
-          <t>samsung4833</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L48" s="61" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M48" s="61" t="inlineStr">
         <is>
-          <t>det.pol</t>
+          <t>pol1</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20.1" customHeight="1" s="70">
       <c r="A49" s="62" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B49" s="63" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>10.67.28.72</t>
         </is>
       </c>
       <c r="C49" s="64" t="inlineStr">
         <is>
-          <t>10:FF:E0:63:F1:98</t>
+          <t>F8:CC:6E:00:5B:1A</t>
         </is>
       </c>
       <c r="D49" s="61" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E49" s="61" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F49" s="61" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G49" s="61" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H49" s="61" t="inlineStr">
         <is>
-          <t>SSD 440Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I49" s="61" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation</t>
         </is>
       </c>
       <c r="J49" s="61" t="inlineStr">
         <is>
-          <t>WS-016-052</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K49" s="61" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L49" s="61" t="inlineStr">
         <is>
-          <t>zav</t>
+          <t>ord</t>
         </is>
       </c>
       <c r="M49" s="61" t="inlineStr">
         <is>
-          <t>pblock</t>
+          <t>rod3</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20.1" customHeight="1" s="70">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>10.67.28.69</t>
         </is>
       </c>
       <c r="C50" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>F8:CC:6E:00:4F:13</t>
         </is>
       </c>
       <c r="D50" s="61" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E50" s="61" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F50" s="61" t="inlineStr">
@@ -4473,2635 +4483,2769 @@
       </c>
       <c r="G50" s="61" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H50" s="61" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I50" s="61" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>ALT 8 SP Workstation</t>
         </is>
       </c>
       <c r="J50" s="61" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
-          <t>M428f</t>
+          <t>samsung4833</t>
         </is>
       </c>
       <c r="L50" s="61" t="inlineStr">
         <is>
-          <t>reg.raspis</t>
+          <t>314</t>
         </is>
       </c>
       <c r="M50" s="61" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>det.pol</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20.1" customHeight="1" s="70">
       <c r="A51" s="62" t="inlineStr">
         <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>10:FF:E0:63:F1:98</t>
+        </is>
+      </c>
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>Gigabyte H410M K</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr">
+        <is>
+          <t>Intel i3-10100 3.60GHz</t>
+        </is>
+      </c>
+      <c r="F51" s="61" t="inlineStr">
+        <is>
+          <t>16Gb</t>
+        </is>
+      </c>
+      <c r="G51" s="61" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="H51" s="61" t="inlineStr">
+        <is>
+          <t>SSD 440Gb</t>
+        </is>
+      </c>
+      <c r="I51" s="61" t="inlineStr">
+        <is>
+          <t>Windows 10 Pro</t>
+        </is>
+      </c>
+      <c r="J51" s="61" t="inlineStr">
+        <is>
+          <t>WS-016-052</t>
+        </is>
+      </c>
+      <c r="K51" s="61" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro MFP 4103</t>
+        </is>
+      </c>
+      <c r="L51" s="61" t="inlineStr">
+        <is>
+          <t>zav</t>
+        </is>
+      </c>
+      <c r="M51" s="61" t="inlineStr">
+        <is>
+          <t>pblock</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20.1" customHeight="1" s="70">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="B51" s="63" t="inlineStr">
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>10.67.64.98</t>
+        </is>
+      </c>
+      <c r="C52" s="64" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:6A:B2</t>
+        </is>
+      </c>
+      <c r="D52" s="61" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F52" s="61" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G52" s="61" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H52" s="61" t="inlineStr">
+        <is>
+          <t>SSD 256Gb</t>
+        </is>
+      </c>
+      <c r="I52" s="61" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J52" s="61" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K52" s="61" t="inlineStr">
+        <is>
+          <t>M428f</t>
+        </is>
+      </c>
+      <c r="L52" s="61" t="inlineStr">
+        <is>
+          <t>reg.raspis</t>
+        </is>
+      </c>
+      <c r="M52" s="61" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20.1" customHeight="1" s="70">
+      <c r="A53" s="62" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
         <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C51" s="64" t="inlineStr">
+      <c r="C53" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D51" s="61" t="inlineStr">
+      <c r="D53" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E51" s="61" t="inlineStr">
+      <c r="E53" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F51" s="61" t="inlineStr">
+      <c r="F53" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G51" s="61" t="inlineStr">
+      <c r="G53" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H51" s="61" t="inlineStr">
+      <c r="H53" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I51" s="61" t="inlineStr">
+      <c r="I53" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J51" s="61" t="inlineStr">
+      <c r="J53" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K51" s="61" t="inlineStr">
+      <c r="K53" s="61" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L51" s="61" t="inlineStr">
+      <c r="L53" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M51" s="61" t="inlineStr">
+      <c r="M53" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20.1" customHeight="1" s="70">
-      <c r="A52" s="59" t="n">
+    <row r="54" ht="20.1" customHeight="1" s="70">
+      <c r="A54" s="59" t="n">
         <v>46231</v>
       </c>
-      <c r="B52" s="63" t="inlineStr">
+      <c r="B54" s="63" t="inlineStr">
         <is>
           <t>10.67.2.33</t>
         </is>
       </c>
-      <c r="C52" s="64" t="inlineStr">
+      <c r="C54" s="64" t="inlineStr">
         <is>
           <t>F0-B4-D2-2C-6D-1D</t>
         </is>
       </c>
-      <c r="D52" s="61" t="inlineStr">
+      <c r="D54" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H510M H</t>
         </is>
       </c>
-      <c r="E52" s="61" t="inlineStr">
+      <c r="E54" s="61" t="inlineStr">
         <is>
           <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F52" s="61" t="inlineStr">
+      <c r="F54" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G52" s="61" t="inlineStr">
+      <c r="G54" s="61" t="inlineStr">
         <is>
           <t>KINGSTON SA400S37480G</t>
         </is>
       </c>
-      <c r="H52" s="61" t="inlineStr">
+      <c r="H54" s="61" t="inlineStr">
         <is>
           <t>SSD 480Gb</t>
         </is>
       </c>
-      <c r="I52" s="61" t="inlineStr">
+      <c r="I54" s="61" t="inlineStr">
         <is>
           <t>Windows 10 IoT Enterprise LTSC</t>
         </is>
       </c>
-      <c r="J52" s="61" t="inlineStr">
+      <c r="J54" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K52" s="61" t="inlineStr">
+      <c r="K54" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
-      <c r="L52" s="61" t="inlineStr">
+      <c r="L54" s="61" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="M52" s="61" t="inlineStr">
+      <c r="M54" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20.1" customHeight="1" s="70">
-      <c r="A53" s="58" t="n">
+    <row r="55" ht="15.75" customHeight="1" s="70">
+      <c r="A55" s="58" t="n">
         <v>46232</v>
       </c>
-      <c r="B53" s="63" t="inlineStr">
+      <c r="B55" s="63" t="inlineStr">
         <is>
           <t>10.67.14.88</t>
         </is>
       </c>
-      <c r="C53" s="64" t="inlineStr">
+      <c r="C55" s="64" t="inlineStr">
         <is>
           <t>D0-27-88-9A-7C-7C</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D55" s="61" t="inlineStr">
         <is>
           <t>Foxconn H61S</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E55" s="61" t="inlineStr">
         <is>
           <t>Intel Celeron CPU G530 2.40GHz</t>
         </is>
       </c>
-      <c r="F53" s="61" t="inlineStr">
+      <c r="F55" s="61" t="inlineStr">
         <is>
           <t>12Gb</t>
         </is>
       </c>
-      <c r="G53" s="61" t="inlineStr">
+      <c r="G55" s="61" t="inlineStr">
         <is>
           <t>WD Green</t>
         </is>
       </c>
-      <c r="H53" s="61" t="inlineStr">
+      <c r="H55" s="61" t="inlineStr">
         <is>
           <t>SSD 500Gb</t>
         </is>
       </c>
-      <c r="I53" s="61" t="inlineStr">
+      <c r="I55" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J53" s="61" t="inlineStr">
+      <c r="J55" s="61" t="inlineStr">
         <is>
           <t>WS-014-088</t>
         </is>
       </c>
-      <c r="K53" s="61" t="inlineStr">
+      <c r="K55" s="61" t="inlineStr">
         <is>
           <t>Samsung SCX-483x 5x3x Series</t>
         </is>
       </c>
-      <c r="L53" s="61" t="inlineStr">
+      <c r="L55" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M53" s="61" t="inlineStr">
+      <c r="M55" s="61" t="inlineStr">
         <is>
           <t>pol1 khl</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" s="70">
-      <c r="A54" s="57" t="n">
+    <row r="56" ht="15.75" customHeight="1" s="70">
+      <c r="A56" s="57" t="n">
         <v>46232</v>
       </c>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="B56" s="63" t="inlineStr">
         <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C54" s="64" t="inlineStr">
+      <c r="C56" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D54" s="61" t="inlineStr">
+      <c r="D56" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="E56" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F54" s="61" t="inlineStr">
+      <c r="F56" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G54" s="61" t="inlineStr">
+      <c r="G56" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H54" s="61" t="inlineStr">
+      <c r="H56" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I54" s="61" t="inlineStr">
+      <c r="I56" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J54" s="61" t="inlineStr">
+      <c r="J56" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K54" s="61" t="inlineStr">
+      <c r="K56" s="61" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L54" s="61" t="inlineStr">
+      <c r="L56" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M54" s="61" t="inlineStr">
+      <c r="M56" s="61" t="inlineStr">
         <is>
           <t>pol1 khl</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="70">
-      <c r="A55" s="56" t="n">
+    <row r="57" ht="15.75" customHeight="1" s="70">
+      <c r="A57" s="56" t="n">
         <v>46231</v>
       </c>
-      <c r="B55" s="63" t="inlineStr">
+      <c r="B57" s="63" t="inlineStr">
         <is>
           <t>10.67.24.12</t>
         </is>
       </c>
-      <c r="C55" s="64" t="inlineStr">
+      <c r="C57" s="64" t="inlineStr">
         <is>
           <t>04-D9-F5-81-FB-29</t>
         </is>
       </c>
-      <c r="D55" s="61" t="inlineStr">
+      <c r="D57" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
-      <c r="E55" s="61" t="inlineStr">
+      <c r="E57" s="61" t="inlineStr">
         <is>
           <t>AMD Ryzen 5 3400G</t>
         </is>
       </c>
-      <c r="F55" s="61" t="inlineStr">
+      <c r="F57" s="61" t="inlineStr">
         <is>
           <t>6GiB</t>
         </is>
       </c>
-      <c r="G55" s="61" t="inlineStr">
+      <c r="G57" s="61" t="inlineStr">
         <is>
           <t>WDC WD5003ABYX-01WERA1</t>
         </is>
       </c>
-      <c r="H55" s="61" t="inlineStr">
+      <c r="H57" s="61" t="inlineStr">
         <is>
           <t>500Gb</t>
         </is>
       </c>
-      <c r="I55" s="61" t="inlineStr">
+      <c r="I57" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J55" s="61" t="inlineStr">
+      <c r="J57" s="61" t="inlineStr">
         <is>
           <t>WS-024-012</t>
         </is>
       </c>
-      <c r="K55" s="61" t="inlineStr">
+      <c r="K57" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M404dn</t>
         </is>
       </c>
-      <c r="L55" s="61" t="inlineStr">
+      <c r="L57" s="61" t="inlineStr">
         <is>
           <t>disp</t>
         </is>
       </c>
-      <c r="M55" s="61" t="inlineStr">
+      <c r="M57" s="61" t="inlineStr">
         <is>
           <t>skp</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="70">
-      <c r="A56" s="55" t="n">
+    <row r="58" ht="15.75" customHeight="1" s="70">
+      <c r="A58" s="55" t="n">
         <v>46230</v>
       </c>
-      <c r="B56" s="63" t="inlineStr">
+      <c r="B58" s="63" t="inlineStr">
         <is>
           <t>10.67.28.59</t>
         </is>
       </c>
-      <c r="C56" s="64" t="inlineStr">
+      <c r="C58" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:B1:CF</t>
         </is>
       </c>
-      <c r="D56" s="61" t="inlineStr">
+      <c r="D58" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E56" s="61" t="inlineStr">
+      <c r="E58" s="61" t="inlineStr">
         <is>
           <t>Intel(R) G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F56" s="61" t="inlineStr">
+      <c r="F58" s="61" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="G56" s="61" t="inlineStr">
+      <c r="G58" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">KINGSTON_SA400S37240G </t>
         </is>
       </c>
-      <c r="H56" s="61" t="inlineStr">
+      <c r="H58" s="61" t="inlineStr">
         <is>
           <t>SSD 240Gb</t>
         </is>
       </c>
-      <c r="I56" s="61" t="inlineStr">
+      <c r="I58" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J56" s="61" t="n">
+      <c r="J58" s="61" t="n">
         <v>2096</v>
       </c>
-      <c r="K56" s="61" t="inlineStr">
+      <c r="K58" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428f-M429f</t>
         </is>
       </c>
-      <c r="L56" s="61" t="inlineStr">
+      <c r="L58" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M56" s="61" t="inlineStr">
+      <c r="M58" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="70">
-      <c r="A57" s="47" t="n">
+    <row r="59" ht="15.75" customHeight="1" s="70">
+      <c r="A59" s="47" t="n">
         <v>46225</v>
       </c>
-      <c r="B57" s="63" t="inlineStr">
+      <c r="B59" s="63" t="inlineStr">
         <is>
           <t>10.67.64.107</t>
         </is>
       </c>
-      <c r="C57" s="64" t="inlineStr">
+      <c r="C59" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:4C:F7</t>
         </is>
       </c>
-      <c r="D57" s="61" t="inlineStr">
+      <c r="D59" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E57" s="61" t="inlineStr">
+      <c r="E59" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F57" s="61" t="inlineStr">
+      <c r="F59" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G57" s="61" t="inlineStr">
+      <c r="G59" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H57" s="61" t="inlineStr">
+      <c r="H59" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I57" s="61" t="inlineStr">
+      <c r="I59" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J57" s="61" t="inlineStr">
+      <c r="J59" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K57" s="61" t="inlineStr">
+      <c r="K59" s="61" t="inlineStr">
         <is>
           <t>Pantum BP5100DN</t>
         </is>
       </c>
-      <c r="L57" s="61" t="inlineStr">
+      <c r="L59" s="61" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="M57" s="61" t="inlineStr">
+      <c r="M59" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="70">
-      <c r="A58" s="46" t="n">
+    <row r="60" ht="15.75" customHeight="1" s="70">
+      <c r="A60" s="46" t="n">
         <v>46225</v>
       </c>
-      <c r="B58" s="63" t="inlineStr">
+      <c r="B60" s="63" t="inlineStr">
         <is>
           <t>10.67.64.5</t>
         </is>
       </c>
-      <c r="C58" s="64" t="inlineStr">
+      <c r="C60" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:58:0C</t>
         </is>
       </c>
-      <c r="D58" s="61" t="inlineStr">
+      <c r="D60" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E58" s="61" t="inlineStr">
+      <c r="E60" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F58" s="61" t="inlineStr">
+      <c r="F60" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G58" s="61" t="inlineStr">
+      <c r="G60" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H58" s="61" t="inlineStr">
+      <c r="H60" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I58" s="61" t="inlineStr">
+      <c r="I60" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J58" s="61" t="inlineStr">
+      <c r="J60" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K58" s="61" t="inlineStr">
+      <c r="K60" s="61" t="inlineStr">
         <is>
           <t>HP M428</t>
         </is>
       </c>
-      <c r="L58" s="61" t="inlineStr">
+      <c r="L60" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M58" s="61" t="inlineStr">
+      <c r="M60" s="61" t="inlineStr">
         <is>
           <t>pol1-3level</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1" s="70">
-      <c r="A59" s="45" t="n">
+    <row r="61" ht="15.75" customHeight="1" s="70">
+      <c r="A61" s="45" t="n">
         <v>46226</v>
       </c>
-      <c r="B59" s="63" t="inlineStr">
+      <c r="B61" s="63" t="inlineStr">
         <is>
           <t>10.67.64.26</t>
         </is>
       </c>
-      <c r="C59" s="64" t="inlineStr">
+      <c r="C61" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
-      <c r="D59" s="61" t="inlineStr">
+      <c r="D61" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E59" s="61" t="inlineStr">
+      <c r="E61" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F59" s="61" t="inlineStr">
+      <c r="F61" s="61" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="G59" s="61" t="inlineStr">
+      <c r="G61" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H59" s="61" t="inlineStr">
+      <c r="H61" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I59" s="61" t="inlineStr">
+      <c r="I61" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J59" s="61" t="inlineStr">
+      <c r="J61" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K59" s="61" t="inlineStr">
+      <c r="K61" s="61" t="inlineStr">
         <is>
           <t>Samsung-SCX-483x-5x3x-Series</t>
         </is>
       </c>
-      <c r="L59" s="61" t="inlineStr">
+      <c r="L61" s="61" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="M59" s="61" t="inlineStr">
+      <c r="M61" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="70">
-      <c r="A60" s="44" t="n">
+    <row r="62" ht="15.75" customHeight="1" s="70">
+      <c r="A62" s="44" t="n">
         <v>46225</v>
       </c>
-      <c r="B60" s="63" t="inlineStr">
+      <c r="B62" s="63" t="inlineStr">
         <is>
           <t>10.67.64.2</t>
         </is>
       </c>
-      <c r="C60" s="64" t="inlineStr">
+      <c r="C62" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:20</t>
         </is>
       </c>
-      <c r="D60" s="61" t="inlineStr">
+      <c r="D62" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E60" s="61" t="inlineStr">
+      <c r="E62" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F60" s="61" t="inlineStr">
+      <c r="F62" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G60" s="61" t="inlineStr">
+      <c r="G62" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H60" s="61" t="inlineStr">
+      <c r="H62" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I60" s="61" t="inlineStr">
+      <c r="I62" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J60" s="61" t="inlineStr">
+      <c r="J62" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K60" s="61" t="inlineStr">
+      <c r="K62" s="61" t="inlineStr">
         <is>
           <t>HP M428</t>
         </is>
       </c>
-      <c r="L60" s="61" t="inlineStr">
+      <c r="L62" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M60" s="61" t="inlineStr">
+      <c r="M62" s="61" t="inlineStr">
         <is>
           <t>pol1-3level</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="70">
-      <c r="A61" s="43" t="n">
+    <row r="63" ht="15.75" customHeight="1" s="70">
+      <c r="A63" s="43" t="n">
         <v>46227</v>
       </c>
-      <c r="B61" s="63" t="inlineStr">
+      <c r="B63" s="63" t="inlineStr">
         <is>
           <t>10.67.28.73</t>
         </is>
       </c>
-      <c r="C61" s="64" t="inlineStr">
+      <c r="C63" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:AF:9E</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D63" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E63" s="61" t="inlineStr">
         <is>
           <t>Intel(R) G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F63" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G61" s="61" t="inlineStr">
+      <c r="G63" s="61" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H61" s="61" t="inlineStr">
+      <c r="H63" s="61" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I61" s="61" t="inlineStr">
+      <c r="I63" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J61" s="61" t="inlineStr">
+      <c r="J63" s="61" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K61" s="61" t="inlineStr">
+      <c r="K63" s="61" t="inlineStr">
         <is>
           <t>HP Laserjet M14-M17</t>
         </is>
       </c>
-      <c r="L61" s="61" t="inlineStr">
+      <c r="L63" s="61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M61" s="61" t="inlineStr">
+      <c r="M63" s="61" t="inlineStr">
         <is>
           <t>pat.anatom.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="70">
-      <c r="A62" s="40" t="n">
+    <row r="64" ht="15.75" customHeight="1" s="70">
+      <c r="A64" s="40" t="n">
         <v>46220</v>
       </c>
-      <c r="B62" s="63" t="inlineStr">
+      <c r="B64" s="63" t="inlineStr">
         <is>
           <t>10.67.12.70</t>
         </is>
       </c>
-      <c r="C62" s="64" t="inlineStr">
+      <c r="C64" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:16:57:0A</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr">
+      <c r="D64" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E64" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F62" s="61" t="inlineStr">
+      <c r="F64" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr">
+      <c r="G64" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H62" s="61" t="inlineStr">
+      <c r="H64" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I62" s="61" t="inlineStr">
+      <c r="I64" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J62" s="61" t="inlineStr">
+      <c r="J64" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K62" s="61" t="inlineStr">
+      <c r="K64" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L62" s="61" t="inlineStr">
+      <c r="L64" s="61" t="inlineStr">
         <is>
           <t>st.ses</t>
         </is>
       </c>
-      <c r="M62" s="61" t="inlineStr">
+      <c r="M64" s="61" t="inlineStr">
         <is>
           <t>h5</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1" s="70">
-      <c r="A63" s="39" t="n">
+    <row r="65">
+      <c r="A65" s="39" t="n">
         <v>46218</v>
       </c>
-      <c r="B63" s="63" t="inlineStr">
+      <c r="B65" s="63" t="inlineStr">
         <is>
           <t>10.67.12.49</t>
         </is>
       </c>
-      <c r="C63" s="64" t="inlineStr">
+      <c r="C65" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:47:D7</t>
         </is>
       </c>
-      <c r="D63" s="61" t="inlineStr">
+      <c r="D65" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E63" s="61" t="inlineStr">
+      <c r="E65" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F63" s="61" t="inlineStr">
+      <c r="F65" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G63" s="61" t="inlineStr">
+      <c r="G65" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H63" s="61" t="inlineStr">
+      <c r="H65" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I63" s="61" t="inlineStr">
+      <c r="I65" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J63" s="61" t="inlineStr">
+      <c r="J65" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K63" s="61" t="inlineStr">
+      <c r="K65" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L63" s="61" t="inlineStr">
+      <c r="L65" s="61" t="inlineStr">
         <is>
           <t>sts</t>
         </is>
       </c>
-      <c r="M63" s="61" t="inlineStr">
+      <c r="M65" s="61" t="inlineStr">
         <is>
           <t>h2</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="70">
-      <c r="A64" s="38" t="n">
+    <row r="66">
+      <c r="A66" s="38" t="n">
         <v>46218</v>
       </c>
-      <c r="B64" s="63" t="inlineStr">
+      <c r="B66" s="63" t="inlineStr">
         <is>
           <t>10.67.64.82</t>
         </is>
       </c>
-      <c r="C64" s="64" t="inlineStr">
+      <c r="C66" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:3F:87</t>
         </is>
       </c>
-      <c r="D64" s="61" t="inlineStr">
+      <c r="D66" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E64" s="61" t="inlineStr">
+      <c r="E66" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F64" s="61" t="inlineStr">
+      <c r="F66" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G64" s="61" t="inlineStr">
+      <c r="G66" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H64" s="61" t="inlineStr">
+      <c r="H66" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I64" s="61" t="inlineStr">
+      <c r="I66" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J64" s="61" t="inlineStr">
+      <c r="J66" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K64" s="61" t="inlineStr">
+      <c r="K66" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L64" s="61" t="inlineStr">
+      <c r="L66" s="61" t="inlineStr">
         <is>
           <t>433</t>
         </is>
       </c>
-      <c r="M64" s="61" t="inlineStr">
+      <c r="M66" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="37" t="n">
+    <row r="67">
+      <c r="A67" s="37" t="n">
         <v>46218</v>
       </c>
-      <c r="B65" s="63" t="inlineStr">
+      <c r="B67" s="63" t="inlineStr">
         <is>
           <t>10.67.64.52</t>
         </is>
       </c>
-      <c r="C65" s="64" t="inlineStr">
+      <c r="C67" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:59:52</t>
         </is>
       </c>
-      <c r="D65" s="61" t="inlineStr">
+      <c r="D67" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E65" s="61" t="inlineStr">
+      <c r="E67" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F65" s="61" t="inlineStr">
+      <c r="F67" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G65" s="61" t="inlineStr">
+      <c r="G67" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H65" s="61" t="inlineStr">
+      <c r="H67" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I65" s="61" t="inlineStr">
+      <c r="I67" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J65" s="61" t="inlineStr">
+      <c r="J67" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K65" s="61" t="inlineStr">
+      <c r="K67" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L65" s="61" t="inlineStr">
+      <c r="L67" s="61" t="inlineStr">
         <is>
           <t>824</t>
         </is>
       </c>
-      <c r="M65" s="61" t="inlineStr">
+      <c r="M67" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="36" t="n">
+    <row r="68">
+      <c r="A68" s="36" t="n">
         <v>46218</v>
       </c>
-      <c r="B66" s="63" t="inlineStr">
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>10.67.64.9</t>
         </is>
       </c>
-      <c r="C66" s="64" t="inlineStr">
+      <c r="C68" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:52</t>
         </is>
       </c>
-      <c r="D66" s="61" t="inlineStr">
+      <c r="D68" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E66" s="61" t="inlineStr">
+      <c r="E68" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F66" s="61" t="inlineStr">
+      <c r="F68" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G66" s="61" t="inlineStr">
+      <c r="G68" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H66" s="61" t="inlineStr">
+      <c r="H68" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I66" s="61" t="inlineStr">
+      <c r="I68" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J66" s="61" t="inlineStr">
+      <c r="J68" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K66" s="61" t="inlineStr">
+      <c r="K68" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L66" s="61" t="inlineStr">
+      <c r="L68" s="61" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M66" s="61" t="inlineStr">
+      <c r="M68" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="35" t="n">
+    <row r="69">
+      <c r="A69" s="35" t="n">
         <v>46218</v>
       </c>
-      <c r="B67" s="63" t="inlineStr">
+      <c r="B69" s="63" t="inlineStr">
         <is>
           <t>10.67.64.26</t>
         </is>
       </c>
-      <c r="C67" s="64" t="inlineStr">
+      <c r="C69" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
-      <c r="D67" s="61" t="inlineStr">
+      <c r="D69" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E67" s="61" t="inlineStr">
+      <c r="E69" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F67" s="61" t="inlineStr">
+      <c r="F69" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G67" s="61" t="inlineStr">
+      <c r="G69" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H67" s="61" t="inlineStr">
+      <c r="H69" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I67" s="61" t="inlineStr">
+      <c r="I69" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J67" s="61" t="inlineStr">
+      <c r="J69" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K67" s="61" t="inlineStr">
+      <c r="K69" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L67" s="61" t="inlineStr">
+      <c r="L69" s="61" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="M67" s="61" t="inlineStr">
+      <c r="M69" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="34" t="n">
+    <row r="70">
+      <c r="A70" s="34" t="n">
         <v>46217</v>
       </c>
-      <c r="B68" s="63" t="inlineStr">
+      <c r="B70" s="63" t="inlineStr">
         <is>
           <t>10.67.22.66</t>
         </is>
       </c>
-      <c r="C68" s="64" t="inlineStr">
+      <c r="C70" s="64" t="inlineStr">
         <is>
           <t>2C-F0-5D-9E-B2-56</t>
         </is>
       </c>
-      <c r="D68" s="61" t="inlineStr">
+      <c r="D70" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">MSI A320M-A PRO </t>
         </is>
       </c>
-      <c r="E68" s="61" t="inlineStr">
+      <c r="E70" s="61" t="inlineStr">
         <is>
           <t>AMD Ryzen 5 3400G</t>
         </is>
       </c>
-      <c r="F68" s="61" t="inlineStr">
+      <c r="F70" s="61" t="inlineStr">
         <is>
           <t>6GiB</t>
         </is>
       </c>
-      <c r="G68" s="61" t="inlineStr">
+      <c r="G70" s="61" t="inlineStr">
         <is>
           <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
-      <c r="H68" s="61" t="inlineStr">
+      <c r="H70" s="61" t="inlineStr">
         <is>
           <t>256Gb</t>
         </is>
       </c>
-      <c r="I68" s="61" t="inlineStr">
+      <c r="I70" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J68" s="61" t="inlineStr">
+      <c r="J70" s="61" t="inlineStr">
         <is>
           <t>WS-022-066</t>
         </is>
       </c>
-      <c r="K68" s="61" t="inlineStr">
+      <c r="K70" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428f-M429f</t>
         </is>
       </c>
-      <c r="L68" s="61" t="inlineStr">
+      <c r="L70" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M68" s="61" t="inlineStr">
+      <c r="M70" s="61" t="inlineStr">
         <is>
           <t>detstvo</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="33" t="n">
+    <row r="71">
+      <c r="A71" s="33" t="n">
         <v>46211</v>
       </c>
-      <c r="B69" s="63" t="inlineStr">
+      <c r="B71" s="63" t="inlineStr">
         <is>
           <t>10.67.64.88</t>
         </is>
       </c>
-      <c r="C69" s="64" t="inlineStr">
+      <c r="C71" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:72:F0</t>
         </is>
       </c>
-      <c r="D69" s="61" t="inlineStr">
+      <c r="D71" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E69" s="61" t="inlineStr">
+      <c r="E71" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F69" s="61" t="inlineStr">
+      <c r="F71" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G69" s="61" t="inlineStr">
+      <c r="G71" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H69" s="61" t="inlineStr">
+      <c r="H71" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I69" s="61" t="inlineStr">
+      <c r="I71" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J69" s="61" t="inlineStr">
+      <c r="J71" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K69" s="61" t="inlineStr">
+      <c r="K71" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L69" s="61" t="inlineStr">
+      <c r="L71" s="61" t="inlineStr">
         <is>
           <t>542</t>
         </is>
       </c>
-      <c r="M69" s="61" t="inlineStr">
+      <c r="M71" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="32" t="n">
+    <row r="72">
+      <c r="A72" s="32" t="n">
         <v>46202</v>
       </c>
-      <c r="B70" s="63" t="inlineStr">
+      <c r="B72" s="63" t="inlineStr">
         <is>
           <t>10.67.64.40</t>
         </is>
       </c>
-      <c r="C70" s="64" t="inlineStr">
+      <c r="C72" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:54:E6</t>
         </is>
       </c>
-      <c r="D70" s="61" t="inlineStr">
+      <c r="D72" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E70" s="61" t="inlineStr">
+      <c r="E72" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F70" s="61" t="inlineStr">
+      <c r="F72" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G70" s="61" t="inlineStr">
+      <c r="G72" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H70" s="61" t="inlineStr">
+      <c r="H72" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I70" s="61" t="inlineStr">
+      <c r="I72" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J70" s="61" t="inlineStr">
+      <c r="J72" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K70" s="61" t="inlineStr">
+      <c r="K72" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L70" s="61" t="inlineStr">
+      <c r="L72" s="61" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="M70" s="61" t="inlineStr">
+      <c r="M72" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="31" t="n">
+    <row r="73">
+      <c r="A73" s="31" t="n">
         <v>46199</v>
       </c>
-      <c r="B71" s="63" t="inlineStr">
+      <c r="B73" s="63" t="inlineStr">
         <is>
           <t>10.67.64.8</t>
         </is>
       </c>
-      <c r="C71" s="64" t="inlineStr">
+      <c r="C73" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:D6</t>
         </is>
       </c>
-      <c r="D71" s="61" t="inlineStr">
+      <c r="D73" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E71" s="61" t="inlineStr">
+      <c r="E73" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F71" s="61" t="inlineStr">
+      <c r="F73" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G71" s="61" t="inlineStr">
+      <c r="G73" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H71" s="61" t="inlineStr">
+      <c r="H73" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I71" s="61" t="inlineStr">
+      <c r="I73" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J71" s="61" t="inlineStr">
+      <c r="J73" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K71" s="61" t="inlineStr">
+      <c r="K73" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L71" s="61" t="inlineStr">
+      <c r="L73" s="61" t="inlineStr">
         <is>
           <t>~</t>
         </is>
       </c>
-      <c r="M71" s="61" t="inlineStr">
+      <c r="M73" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="30" t="n">
+    <row r="74">
+      <c r="A74" s="30" t="n">
         <v>46198</v>
       </c>
-      <c r="B72" s="63" t="inlineStr">
+      <c r="B74" s="63" t="inlineStr">
         <is>
           <t>10.67.22.105</t>
         </is>
       </c>
-      <c r="C72" s="64" t="inlineStr">
+      <c r="C74" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:36:6D</t>
         </is>
       </c>
-      <c r="D72" s="61" t="inlineStr">
+      <c r="D74" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E72" s="61" t="inlineStr">
+      <c r="E74" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F72" s="61" t="inlineStr">
+      <c r="F74" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G72" s="61" t="inlineStr">
+      <c r="G74" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H72" s="61" t="inlineStr">
+      <c r="H74" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I72" s="61" t="inlineStr">
+      <c r="I74" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J72" s="61" t="inlineStr">
+      <c r="J74" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K72" s="61" t="inlineStr">
+      <c r="K74" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L72" s="61" t="inlineStr">
+      <c r="L74" s="61" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="M72" s="61" t="inlineStr">
+      <c r="M74" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="n">
+    <row r="75">
+      <c r="A75" s="29" t="n">
         <v>46196</v>
       </c>
-      <c r="B73" s="63" t="inlineStr">
+      <c r="B75" s="63" t="inlineStr">
         <is>
           <t>192.168.36.31</t>
         </is>
       </c>
-      <c r="C73" s="64" t="inlineStr">
+      <c r="C75" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:1D:48</t>
         </is>
       </c>
-      <c r="D73" s="61" t="inlineStr">
+      <c r="D75" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E73" s="61" t="inlineStr">
+      <c r="E75" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F73" s="61" t="inlineStr">
+      <c r="F75" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G73" s="61" t="inlineStr">
+      <c r="G75" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H73" s="61" t="inlineStr">
+      <c r="H75" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I73" s="61" t="inlineStr">
+      <c r="I75" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J73" s="61" t="inlineStr">
+      <c r="J75" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K73" s="61" t="inlineStr">
+      <c r="K75" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L73" s="61" t="inlineStr">
+      <c r="L75" s="61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M73" s="61" t="inlineStr">
+      <c r="M75" s="61" t="inlineStr">
         <is>
           <t>stomat</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="28" t="n">
+    <row r="76">
+      <c r="A76" s="28" t="n">
         <v>46196</v>
       </c>
-      <c r="B74" s="63" t="inlineStr">
+      <c r="B76" s="63" t="inlineStr">
         <is>
           <t>192.168.36.25</t>
         </is>
       </c>
-      <c r="C74" s="64" t="inlineStr">
+      <c r="C76" s="64" t="inlineStr">
         <is>
           <t>18-C0-4D-CD-F6-5E</t>
         </is>
       </c>
-      <c r="D74" s="61" t="inlineStr">
+      <c r="D76" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M H V3</t>
         </is>
       </c>
-      <c r="E74" s="61" t="inlineStr">
+      <c r="E76" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10105 3.70GHz</t>
         </is>
       </c>
-      <c r="F74" s="61" t="inlineStr">
+      <c r="F76" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G74" s="61" t="inlineStr">
+      <c r="G76" s="61" t="inlineStr">
         <is>
           <t>Samsung SSD 870 EVO 500GB</t>
         </is>
       </c>
-      <c r="H74" s="61" t="inlineStr">
+      <c r="H76" s="61" t="inlineStr">
         <is>
           <t>465Gb</t>
         </is>
       </c>
-      <c r="I74" s="61" t="inlineStr">
+      <c r="I76" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J74" s="61" t="inlineStr">
+      <c r="J76" s="61" t="inlineStr">
         <is>
           <t>WS-036-025</t>
         </is>
       </c>
-      <c r="K74" s="61" t="inlineStr">
+      <c r="K76" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L74" s="61" t="inlineStr">
+      <c r="L76" s="61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M74" s="61" t="inlineStr">
+      <c r="M76" s="61" t="inlineStr">
         <is>
           <t>stomat</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="27" t="n">
+    <row r="77">
+      <c r="A77" s="27" t="n">
         <v>46192</v>
       </c>
-      <c r="B75" s="63" t="inlineStr">
+      <c r="B77" s="63" t="inlineStr">
         <is>
           <t>10.67.38.58</t>
         </is>
       </c>
-      <c r="C75" s="64" t="inlineStr">
+      <c r="C77" s="64" t="inlineStr">
         <is>
           <t>10-FF-E0-63-ED-A8</t>
         </is>
       </c>
-      <c r="D75" s="61" t="inlineStr">
+      <c r="D77" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M K</t>
         </is>
       </c>
-      <c r="E75" s="61" t="inlineStr">
+      <c r="E77" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F75" s="61" t="inlineStr">
+      <c r="F77" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G75" s="61" t="inlineStr">
+      <c r="G77" s="61" t="inlineStr">
         <is>
           <t>WD Blue SN5000 500GB</t>
         </is>
       </c>
-      <c r="H75" s="61" t="inlineStr">
+      <c r="H77" s="61" t="inlineStr">
         <is>
           <t>HDD 465Gb</t>
         </is>
       </c>
-      <c r="I75" s="61" t="inlineStr">
+      <c r="I77" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J75" s="61" t="inlineStr">
+      <c r="J77" s="61" t="inlineStr">
         <is>
           <t>WS-038-058</t>
         </is>
       </c>
-      <c r="K75" s="61" t="inlineStr">
+      <c r="K77" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L75" s="61" t="inlineStr">
+      <c r="L77" s="61" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="M75" s="61" t="inlineStr">
+      <c r="M77" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="26" t="n">
+    <row r="78">
+      <c r="A78" s="26" t="n">
         <v>46191</v>
       </c>
-      <c r="B76" s="63" t="inlineStr">
+      <c r="B78" s="63" t="inlineStr">
         <is>
           <t>10.67.64.98</t>
         </is>
       </c>
-      <c r="C76" s="64" t="inlineStr">
+      <c r="C78" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
-      <c r="D76" s="61" t="inlineStr">
+      <c r="D78" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E76" s="61" t="inlineStr">
+      <c r="E78" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F76" s="61" t="inlineStr">
+      <c r="F78" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G76" s="61" t="inlineStr">
+      <c r="G78" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H76" s="61" t="inlineStr">
+      <c r="H78" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I76" s="61" t="inlineStr">
+      <c r="I78" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J76" s="61" t="inlineStr">
+      <c r="J78" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K76" s="61" t="inlineStr">
+      <c r="K78" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L76" s="61" t="inlineStr">
+      <c r="L78" s="61" t="inlineStr">
         <is>
           <t>registratura</t>
         </is>
       </c>
-      <c r="M76" s="61" t="inlineStr">
+      <c r="M78" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="25" t="n">
+    <row r="79">
+      <c r="A79" s="25" t="n">
         <v>46183</v>
       </c>
-      <c r="B77" s="63" t="inlineStr">
+      <c r="B79" s="63" t="inlineStr">
         <is>
           <t>10.67.64.92</t>
         </is>
       </c>
-      <c r="C77" s="64" t="inlineStr">
+      <c r="C79" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:63:82</t>
         </is>
       </c>
-      <c r="D77" s="61" t="inlineStr">
+      <c r="D79" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E77" s="61" t="inlineStr">
+      <c r="E79" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F77" s="61" t="inlineStr">
+      <c r="F79" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G77" s="61" t="inlineStr">
+      <c r="G79" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5 OnlyDisk</t>
         </is>
       </c>
-      <c r="H77" s="61" t="inlineStr">
+      <c r="H79" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I77" s="61" t="inlineStr">
+      <c r="I79" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J77" s="61" t="inlineStr">
+      <c r="J79" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K77" s="61" t="inlineStr">
+      <c r="K79" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L77" s="61" t="inlineStr">
+      <c r="L79" s="61" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="M77" s="61" t="inlineStr">
+      <c r="M79" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="24" t="n">
+    <row r="80">
+      <c r="A80" s="24" t="n">
         <v>46183</v>
       </c>
-      <c r="B78" s="63" t="inlineStr">
+      <c r="B80" s="63" t="inlineStr">
         <is>
           <t>10.67.64.38</t>
         </is>
       </c>
-      <c r="C78" s="64" t="inlineStr">
+      <c r="C80" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:54:A4</t>
         </is>
       </c>
-      <c r="D78" s="61" t="inlineStr">
+      <c r="D80" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E78" s="61" t="inlineStr">
+      <c r="E80" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F78" s="61" t="inlineStr">
+      <c r="F80" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G78" s="61" t="inlineStr">
+      <c r="G80" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H78" s="61" t="inlineStr">
+      <c r="H80" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I78" s="61" t="inlineStr">
+      <c r="I80" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J78" s="61" t="inlineStr">
+      <c r="J80" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K78" s="61" t="inlineStr">
+      <c r="K80" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L78" s="61" t="inlineStr">
+      <c r="L80" s="61" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="M78" s="61" t="inlineStr">
+      <c r="M80" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="23" t="n">
+    <row r="81">
+      <c r="A81" s="23" t="n">
         <v>46183</v>
       </c>
-      <c r="B79" s="63" t="inlineStr">
+      <c r="B81" s="63" t="inlineStr">
         <is>
           <t>10.67.64.96</t>
         </is>
       </c>
-      <c r="C79" s="64" t="inlineStr">
+      <c r="C81" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:42:79</t>
         </is>
       </c>
-      <c r="D79" s="61" t="inlineStr">
+      <c r="D81" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E79" s="61" t="inlineStr">
+      <c r="E81" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F79" s="61" t="inlineStr">
+      <c r="F81" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G79" s="61" t="inlineStr">
+      <c r="G81" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H79" s="61" t="inlineStr">
+      <c r="H81" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I79" s="61" t="inlineStr">
+      <c r="I81" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J79" s="61" t="inlineStr">
+      <c r="J81" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K79" s="61" t="inlineStr">
+      <c r="K81" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L79" s="61" t="inlineStr">
+      <c r="L81" s="61" t="inlineStr">
         <is>
           <t>417</t>
         </is>
       </c>
-      <c r="M79" s="61" t="inlineStr">
+      <c r="M81" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="22" t="n">
+    <row r="82">
+      <c r="A82" s="22" t="n">
         <v>46181</v>
       </c>
-      <c r="B80" s="63" t="inlineStr">
+      <c r="B82" s="63" t="inlineStr">
         <is>
           <t>10.67.64.3</t>
         </is>
       </c>
-      <c r="C80" s="64" t="inlineStr">
+      <c r="C82" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:62:CA</t>
         </is>
       </c>
-      <c r="D80" s="61" t="inlineStr">
+      <c r="D82" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E80" s="61" t="inlineStr">
+      <c r="E82" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F80" s="61" t="inlineStr">
+      <c r="F82" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G80" s="61" t="inlineStr">
+      <c r="G82" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H80" s="61" t="inlineStr">
+      <c r="H82" s="61" t="inlineStr">
         <is>
           <t>238Gb</t>
         </is>
       </c>
-      <c r="I80" s="61" t="inlineStr">
+      <c r="I82" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J80" s="61" t="inlineStr">
+      <c r="J82" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K80" s="61" t="inlineStr">
+      <c r="K82" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L80" s="61" t="inlineStr">
+      <c r="L82" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M80" s="61" t="inlineStr">
+      <c r="M82" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="21" t="n">
+    <row r="83">
+      <c r="A83" s="21" t="n">
         <v>46181</v>
       </c>
-      <c r="B81" s="63" t="inlineStr">
+      <c r="B83" s="63" t="inlineStr">
         <is>
           <t>192.168.0.129</t>
         </is>
       </c>
-      <c r="C81" s="64" t="inlineStr">
+      <c r="C83" s="64" t="inlineStr">
         <is>
           <t>38-D5-47-E1-3E-C6</t>
         </is>
       </c>
-      <c r="D81" s="61" t="inlineStr">
+      <c r="D83" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK Z170-K</t>
         </is>
       </c>
-      <c r="E81" s="61" t="inlineStr">
+      <c r="E83" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i7-6700K 4.00GHz</t>
         </is>
       </c>
-      <c r="F81" s="61" t="inlineStr">
+      <c r="F83" s="61" t="inlineStr">
         <is>
           <t>32Gb</t>
         </is>
       </c>
-      <c r="G81" s="61" t="inlineStr">
+      <c r="G83" s="61" t="inlineStr">
         <is>
           <t>TOSHIBA DT01ACA100</t>
         </is>
       </c>
-      <c r="H81" s="61" t="inlineStr">
+      <c r="H83" s="61" t="inlineStr">
         <is>
           <t>931Gb</t>
         </is>
       </c>
-      <c r="I81" s="61" t="inlineStr">
+      <c r="I83" s="61" t="inlineStr">
         <is>
           <t>Windows 10 IoT Enterprise</t>
         </is>
       </c>
-      <c r="J81" s="61" t="inlineStr">
+      <c r="J83" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K81" s="61" t="inlineStr">
+      <c r="K83" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L81" s="61" t="inlineStr">
+      <c r="L83" s="61" t="inlineStr">
         <is>
           <t>my</t>
         </is>
       </c>
-      <c r="M81" s="61" t="inlineStr">
+      <c r="M83" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="20" t="n">
+    <row r="84">
+      <c r="A84" s="20" t="n">
         <v>46178</v>
       </c>
-      <c r="B82" s="63" t="inlineStr">
+      <c r="B84" s="63" t="inlineStr">
         <is>
           <t>10.67.2.8</t>
         </is>
       </c>
-      <c r="C82" s="64" t="inlineStr">
+      <c r="C84" s="64" t="inlineStr">
         <is>
           <t>58-11-22-07-4E-DF</t>
         </is>
       </c>
-      <c r="D82" s="61" t="inlineStr">
+      <c r="D84" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME H510M-K</t>
         </is>
       </c>
-      <c r="E82" s="61" t="inlineStr">
+      <c r="E84" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-10400 2.90GHz</t>
         </is>
       </c>
-      <c r="F82" s="61" t="inlineStr">
+      <c r="F84" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G82" s="61" t="inlineStr">
+      <c r="G84" s="61" t="inlineStr">
         <is>
           <t>ST500NM0011</t>
         </is>
       </c>
-      <c r="H82" s="61" t="inlineStr">
+      <c r="H84" s="61" t="inlineStr">
         <is>
           <t>SSD 465 Gb</t>
         </is>
       </c>
-      <c r="I82" s="61" t="inlineStr">
+      <c r="I84" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J82" s="61" t="inlineStr">
+      <c r="J84" s="61" t="inlineStr">
         <is>
           <t>WS-002-008</t>
         </is>
       </c>
-      <c r="K82" s="61" t="inlineStr">
+      <c r="K84" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L82" s="61" t="inlineStr">
+      <c r="L84" s="61" t="inlineStr">
         <is>
           <t>312 IGOR</t>
         </is>
       </c>
-      <c r="M82" s="61" t="inlineStr">
+      <c r="M84" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="19" t="n">
+    <row r="85">
+      <c r="A85" s="19" t="n">
         <v>46177</v>
       </c>
-      <c r="B83" s="63" t="inlineStr">
+      <c r="B85" s="63" t="inlineStr">
         <is>
           <t>10.67.2.33</t>
         </is>
       </c>
-      <c r="C83" s="64" t="inlineStr">
+      <c r="C85" s="64" t="inlineStr">
         <is>
           <t>18-C0-4D-D7-67-0E</t>
         </is>
       </c>
-      <c r="D83" s="61" t="inlineStr">
+      <c r="D85" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H510M H</t>
         </is>
       </c>
-      <c r="E83" s="61" t="inlineStr">
+      <c r="E85" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F83" s="61" t="inlineStr">
+      <c r="F85" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G83" s="61" t="inlineStr">
+      <c r="G85" s="61" t="inlineStr">
         <is>
           <t>KINGSTON SA400S37480G</t>
         </is>
       </c>
-      <c r="H83" s="61" t="inlineStr">
+      <c r="H85" s="61" t="inlineStr">
         <is>
           <t>SSD 447 Gb</t>
         </is>
       </c>
-      <c r="I83" s="61" t="inlineStr">
+      <c r="I85" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Windows 10 IoT Enterprise LTSC </t>
         </is>
       </c>
-      <c r="J83" s="61" t="inlineStr">
+      <c r="J85" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K83" s="61" t="inlineStr">
+      <c r="K85" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L83" s="61" t="inlineStr">
+      <c r="L85" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M83" s="61" t="inlineStr">
+      <c r="M85" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="18" t="n">
+    <row r="86">
+      <c r="A86" s="18" t="n">
         <v>46178</v>
       </c>
-      <c r="B84" s="63" t="inlineStr">
+      <c r="B86" s="63" t="inlineStr">
         <is>
           <t>192.168.36.34</t>
         </is>
       </c>
-      <c r="C84" s="64" t="inlineStr">
+      <c r="C86" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:37:A7</t>
         </is>
       </c>
-      <c r="D84" s="61" t="inlineStr">
+      <c r="D86" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E84" s="61" t="inlineStr">
+      <c r="E86" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) i5-9400 2.90GHz </t>
         </is>
       </c>
-      <c r="F84" s="61" t="inlineStr">
+      <c r="F86" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G84" s="61" t="inlineStr">
+      <c r="G86" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H84" s="61" t="inlineStr">
+      <c r="H86" s="61" t="inlineStr">
         <is>
           <t>SSD 256</t>
         </is>
       </c>
-      <c r="I84" s="61" t="inlineStr">
+      <c r="I86" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J84" s="61" t="inlineStr">
+      <c r="J86" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K84" s="61" t="inlineStr">
+      <c r="K86" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L84" s="61" t="inlineStr">
+      <c r="L86" s="61" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M84" s="61" t="inlineStr">
+      <c r="M86" s="61" t="inlineStr">
         <is>
           <t>stomatology</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="17" t="n">
+    <row r="87">
+      <c r="A87" s="17" t="n">
         <v>46178</v>
       </c>
-      <c r="B85" s="63" t="inlineStr">
+      <c r="B87" s="63" t="inlineStr">
         <is>
           <t>10.67.11.32</t>
         </is>
       </c>
-      <c r="C85" s="64" t="inlineStr">
+      <c r="C87" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0D:24:AD</t>
         </is>
       </c>
-      <c r="D85" s="61" t="inlineStr">
+      <c r="D87" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME B365M-C</t>
         </is>
       </c>
-      <c r="E85" s="61" t="inlineStr">
+      <c r="E87" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) i5-9400 2.90GHz </t>
         </is>
       </c>
-      <c r="F85" s="61" t="inlineStr">
+      <c r="F87" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G85" s="61" t="inlineStr">
+      <c r="G87" s="61" t="inlineStr">
         <is>
           <t>FOXLINE FLSSD256X5</t>
         </is>
       </c>
-      <c r="H85" s="61" t="inlineStr">
+      <c r="H87" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I85" s="61" t="inlineStr">
+      <c r="I87" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 10.4</t>
         </is>
       </c>
-      <c r="J85" s="61" t="inlineStr">
+      <c r="J87" s="61" t="inlineStr">
         <is>
           <t>dpk5324</t>
         </is>
       </c>
-      <c r="K85" s="61" t="inlineStr">
+      <c r="K87" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L85" s="61" t="inlineStr">
+      <c r="L87" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M85" s="61" t="inlineStr">
+      <c r="M87" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="n">
+    <row r="88">
+      <c r="A88" s="16" t="n">
         <v>46177</v>
       </c>
-      <c r="B86" s="63" t="inlineStr">
+      <c r="B88" s="63" t="inlineStr">
         <is>
           <t>192.168.0.172</t>
         </is>
       </c>
-      <c r="C86" s="64" t="inlineStr">
+      <c r="C88" s="64" t="inlineStr">
         <is>
           <t>2C:56:DC:DB:90:05</t>
         </is>
       </c>
-      <c r="D86" s="61" t="inlineStr">
+      <c r="D88" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK A68HM-K</t>
         </is>
       </c>
-      <c r="E86" s="61" t="inlineStr">
+      <c r="E88" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">AMD Athlon(tm) X2 340 </t>
         </is>
       </c>
-      <c r="F86" s="61" t="inlineStr">
+      <c r="F88" s="61" t="inlineStr">
         <is>
           <t>6Gb</t>
         </is>
       </c>
-      <c r="G86" s="61" t="inlineStr">
+      <c r="G88" s="61" t="inlineStr">
         <is>
           <t>TOSHIBA DT01ACA100</t>
         </is>
       </c>
-      <c r="H86" s="61" t="inlineStr">
+      <c r="H88" s="61" t="inlineStr">
         <is>
           <t>HDD 1000Gb</t>
         </is>
       </c>
-      <c r="I86" s="61" t="inlineStr">
+      <c r="I88" s="61" t="inlineStr">
         <is>
           <t>CentOS Stream 9</t>
         </is>
       </c>
-      <c r="J86" s="61" t="inlineStr">
+      <c r="J88" s="61" t="inlineStr">
         <is>
           <t>localhost</t>
         </is>
       </c>
-      <c r="K86" s="61" t="inlineStr">
+      <c r="K88" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L86" s="61" t="inlineStr">
+      <c r="L88" s="61" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="M86" s="61" t="inlineStr">
+      <c r="M88" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="15" t="n">
+    <row r="89">
+      <c r="A89" s="15" t="n">
         <v>46164</v>
       </c>
-      <c r="B87" s="63" t="inlineStr">
+      <c r="B89" s="63" t="inlineStr">
         <is>
           <t>10.67.40.20</t>
         </is>
       </c>
-      <c r="C87" s="64" t="inlineStr">
+      <c r="C89" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:12:36:42</t>
         </is>
       </c>
-      <c r="D87" s="61" t="inlineStr">
+      <c r="D89" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E87" s="61" t="inlineStr">
+      <c r="E89" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F87" s="61" t="inlineStr">
+      <c r="F89" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G87" s="61" t="inlineStr">
+      <c r="G89" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H87" s="61" t="inlineStr">
+      <c r="H89" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I87" s="61" t="inlineStr">
+      <c r="I89" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J87" s="61" t="inlineStr">
+      <c r="J89" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K87" s="61" t="inlineStr">
+      <c r="K89" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L87" s="61" t="inlineStr">
+      <c r="L89" s="61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M87" s="61" t="inlineStr">
+      <c r="M89" s="61" t="inlineStr">
         <is>
           <t>tuber</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="14" t="n">
+    <row r="90">
+      <c r="A90" s="14" t="n">
         <v>46164</v>
       </c>
-      <c r="B88" s="63" t="inlineStr">
+      <c r="B90" s="63" t="inlineStr">
         <is>
           <t>10.67.40.17</t>
         </is>
       </c>
-      <c r="C88" s="64" t="inlineStr">
+      <c r="C90" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:12:36:49</t>
         </is>
       </c>
-      <c r="D88" s="61" t="inlineStr">
+      <c r="D90" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E88" s="61" t="inlineStr">
+      <c r="E90" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F88" s="61" t="inlineStr">
+      <c r="F90" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G88" s="61" t="inlineStr">
+      <c r="G90" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H88" s="61" t="inlineStr">
+      <c r="H90" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I88" s="61" t="inlineStr">
+      <c r="I90" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J88" s="61" t="inlineStr">
+      <c r="J90" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K88" s="61" t="inlineStr">
+      <c r="K90" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L88" s="61" t="inlineStr">
+      <c r="L90" s="61" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M88" s="61" t="inlineStr">
+      <c r="M90" s="61" t="inlineStr">
         <is>
           <t>tuber</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
+    <row r="91">
+      <c r="A91" s="7" t="n">
         <v>46150</v>
       </c>
-      <c r="B89" s="63" t="inlineStr">
+      <c r="B91" s="63" t="inlineStr">
         <is>
           <t>10.67.64.62</t>
         </is>
       </c>
-      <c r="C89" s="64" t="inlineStr">
+      <c r="C91" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:17:59:a3</t>
         </is>
       </c>
-      <c r="D89" s="61" t="inlineStr">
+      <c r="D91" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E89" s="61" t="inlineStr">
+      <c r="E91" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F89" s="61" t="inlineStr">
+      <c r="F91" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G89" s="61" t="inlineStr">
+      <c r="G91" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H89" s="61" t="inlineStr">
+      <c r="H91" s="61" t="inlineStr">
         <is>
           <t>256 GB/238 GiB</t>
         </is>
       </c>
-      <c r="I89" s="61" t="inlineStr">
+      <c r="I91" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J89" s="61" t="inlineStr">
+      <c r="J91" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K89" s="61" t="inlineStr">
+      <c r="K91" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L89" s="61" t="inlineStr">
+      <c r="L91" s="61" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="M89" s="61" t="inlineStr">
+      <c r="M91" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="7" t="n">
+    <row r="92">
+      <c r="A92" s="7" t="n">
         <v>46148</v>
       </c>
-      <c r="B90" s="63" t="inlineStr">
+      <c r="B92" s="63" t="inlineStr">
         <is>
           <t>192.168.0.139</t>
         </is>
       </c>
-      <c r="C90" s="64" t="inlineStr">
+      <c r="C92" s="64" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="D90" s="61" t="inlineStr">
+      <c r="D92" s="61" t="inlineStr">
         <is>
           <t>ASRock J3355M</t>
         </is>
       </c>
-      <c r="E90" s="61" t="inlineStr">
+      <c r="E92" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) J3355 2.00GHz </t>
         </is>
       </c>
-      <c r="F90" s="61" t="inlineStr">
+      <c r="F92" s="61" t="inlineStr">
         <is>
           <t>6Gb</t>
         </is>
       </c>
-      <c r="G90" s="61" t="inlineStr">
+      <c r="G92" s="61" t="inlineStr">
         <is>
           <t>WDC WD5000BPVT-2</t>
         </is>
       </c>
-      <c r="H90" s="61" t="inlineStr">
+      <c r="H92" s="61" t="inlineStr">
         <is>
           <t>500 GB/466 GiB</t>
         </is>
       </c>
-      <c r="I90" s="61" t="inlineStr">
+      <c r="I92" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 8.2</t>
         </is>
       </c>
-      <c r="J90" s="61" t="inlineStr">
+      <c r="J92" s="61" t="inlineStr">
         <is>
           <t>home-comp</t>
         </is>
       </c>
-      <c r="K90" s="61" t="inlineStr">
+      <c r="K92" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L90" s="61" t="inlineStr">
+      <c r="L92" s="61" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="M90" s="61" t="inlineStr">
+      <c r="M92" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>

--- a/base/list-points.xlsx
+++ b/base/list-points.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:XFD92"/>
+  <dimension ref="A1:XFD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" customWidth="1" style="70" min="1" max="1"/>
@@ -1721,72 +1721,72 @@
     <row r="11" ht="18" customHeight="1" s="70">
       <c r="A11" s="72" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B11" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.161</t>
+          <t>10.67.12.58</t>
         </is>
       </c>
       <c r="C11" s="74" t="inlineStr">
         <is>
-          <t>18-C0-4D-CD-F2-E9</t>
+          <t>00:58:3F:16:57:0B</t>
         </is>
       </c>
       <c r="D11" s="75" t="inlineStr">
         <is>
-          <t>Gigabyte H410M H V3</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E11" s="75" t="inlineStr">
         <is>
-          <t>Intel Core i3-10105 CPU 3.70GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F11" s="75" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G11" s="75" t="inlineStr">
         <is>
-          <t>Samsung SSD 870 EVO 500GB</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H11" s="75" t="inlineStr">
         <is>
-          <t>SSD-500Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I11" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J11" s="75" t="inlineStr">
         <is>
-          <t>WS-014-161</t>
+          <t>comp-core-i7-8700t-1051a2</t>
         </is>
       </c>
       <c r="K11" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP_LaserJet_1018</t>
         </is>
       </c>
       <c r="L11" s="75" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>старшая сестра</t>
         </is>
       </c>
       <c r="M11" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>хирургия 2 этаж</t>
         </is>
       </c>
       <c r="N11" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89601</t>
         </is>
       </c>
     </row>
@@ -1798,57 +1798,57 @@
       </c>
       <c r="B12" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.6</t>
+          <t>10.67.14.161</t>
         </is>
       </c>
       <c r="C12" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:59:32</t>
+          <t>18-C0-4D-CD-F2-E9</t>
         </is>
       </c>
       <c r="D12" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Gigabyte H410M H V3</t>
         </is>
       </c>
       <c r="E12" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel Core i3-10105 CPU 3.70GHz</t>
         </is>
       </c>
       <c r="F12" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G12" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>Samsung SSD 870 EVO 500GB</t>
         </is>
       </c>
       <c r="H12" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>SSD-500Gb</t>
         </is>
       </c>
       <c r="I12" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J12" s="75" t="inlineStr">
         <is>
-          <t>comp-core-i7-8700t-1051a2</t>
+          <t>WS-014-161</t>
         </is>
       </c>
       <c r="K12" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M404dn</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L12" s="75" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>510</t>
         </is>
       </c>
       <c r="M12" s="75" t="inlineStr">
@@ -1865,27 +1865,27 @@
     <row r="13" ht="20.1" customHeight="1" s="70">
       <c r="A13" s="72" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B13" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.77</t>
+          <t>10.67.64.6</t>
         </is>
       </c>
       <c r="C13" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B4:DD</t>
+          <t>00:58:3F:17:59:32</t>
         </is>
       </c>
       <c r="D13" s="75" t="inlineStr">
         <is>
-          <t>DEPO Computers DPH110S</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E13" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i3-9100 3.60GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F13" s="75" t="inlineStr">
@@ -1895,32 +1895,32 @@
       </c>
       <c r="G13" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H13" s="75" t="inlineStr">
         <is>
-          <t>SSD 240Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I13" s="75" t="inlineStr">
         <is>
-          <t>ALT 8 SP Workstation (cliff)</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J13" s="75" t="inlineStr">
         <is>
-          <t>comp-pentium-gold-002096</t>
+          <t>comp-core-i7-8700t-1051a2</t>
         </is>
       </c>
       <c r="K13" s="75" t="inlineStr">
         <is>
-          <t>hp402</t>
+          <t>HP LaserJet Pro M404dn</t>
         </is>
       </c>
       <c r="L13" s="75" t="inlineStr">
         <is>
-          <t>регистратура 2 окно</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M13" s="75" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="N13" s="75" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B14" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.59</t>
+          <t>10.67.28.77</t>
         </is>
       </c>
       <c r="C14" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B1:CF</t>
+          <t>F8:CC:6E:00:B4:DD</t>
         </is>
       </c>
       <c r="D14" s="75" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E14" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
+          <t>Intel(R) i3-9100 3.60GHz</t>
         </is>
       </c>
       <c r="F14" s="75" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G14" s="75" t="inlineStr">
         <is>
-          <t>KINGSTON_SA400S37240G</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H14" s="75" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="K14" s="75" t="inlineStr">
         <is>
-          <t>M428</t>
+          <t>hp402</t>
         </is>
       </c>
       <c r="L14" s="75" t="inlineStr">
         <is>
-          <t>регистратура 3 окно</t>
+          <t>регистратура 2 окно</t>
         </is>
       </c>
       <c r="M14" s="75" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="N14" s="75" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>78535</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B15" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.61</t>
+          <t>10.67.28.59</t>
         </is>
       </c>
       <c r="C15" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:A5:45</t>
+          <t>F8:CC:6E:00:B1:CF</t>
         </is>
       </c>
       <c r="D15" s="75" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="G15" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>KINGSTON_SA400S37240G</t>
         </is>
       </c>
       <c r="H15" s="75" t="inlineStr">
         <is>
-          <t>SSD 120Gb</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I15" s="75" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="K15" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>M428</t>
         </is>
       </c>
       <c r="L15" s="75" t="inlineStr">
         <is>
-          <t>регистратура 1 окно</t>
+          <t>регистратура 3 окно</t>
         </is>
       </c>
       <c r="M15" s="75" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="N15" s="75" t="inlineStr">
         <is>
-          <t>88541</t>
+          <t>88546</t>
         </is>
       </c>
     </row>
@@ -2086,47 +2086,47 @@
       </c>
       <c r="B16" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.141</t>
+          <t>10.67.28.61</t>
         </is>
       </c>
       <c r="C16" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-74</t>
+          <t>F8:CC:6E:00:A5:45</t>
         </is>
       </c>
       <c r="D16" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star International Co., Ltd.  A320M-A PRO (MS-7C51)</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E16" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F16" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G16" s="75" t="inlineStr">
         <is>
-          <t>Smartbuy SSD 256GB</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H16" s="75" t="inlineStr">
         <is>
-          <t>SSD-256Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I16" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J16" s="75" t="inlineStr">
         <is>
-          <t>WS-14-141</t>
+          <t>comp-pentium-gold-002096</t>
         </is>
       </c>
       <c r="K16" s="75" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="L16" s="75" t="inlineStr">
         <is>
-          <t>регистратура 2 окно</t>
+          <t>регистратура 1 окно</t>
         </is>
       </c>
       <c r="M16" s="75" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="N16" s="75" t="inlineStr">
         <is>
-          <t>88746</t>
+          <t>88541</t>
         </is>
       </c>
     </row>
@@ -2158,17 +2158,17 @@
       </c>
       <c r="B17" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.130</t>
+          <t>10.67.14.141</t>
         </is>
       </c>
       <c r="C17" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-36</t>
+          <t>2C-F0-5D-9E-B2-74</t>
         </is>
       </c>
       <c r="D17" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME A320M-A</t>
+          <t>Micro-Star International Co., Ltd.  A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E17" s="75" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="G17" s="75" t="inlineStr">
         <is>
-          <t>ST1000DM010-2EP102</t>
+          <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
       <c r="H17" s="75" t="inlineStr">
         <is>
-          <t>HDD-1Tb</t>
+          <t>SSD-256Gb</t>
         </is>
       </c>
       <c r="I17" s="75" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="J17" s="75" t="inlineStr">
         <is>
-          <t>DESKTOP-MQADVRK</t>
+          <t>WS-14-141</t>
         </is>
       </c>
       <c r="K17" s="75" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L17" s="75" t="inlineStr">
         <is>
-          <t>регистратура 3 окно</t>
+          <t>регистратура 2 окно</t>
         </is>
       </c>
       <c r="M17" s="75" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="N17" s="75" t="inlineStr">
         <is>
-          <t>114130</t>
+          <t>88746</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="B18" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.132 / 192.168.56.1</t>
+          <t>10.67.14.130</t>
         </is>
       </c>
       <c r="C18" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-2A / 0A-00-27-00-00-07</t>
+          <t>04-D9-F5-81-FB-36</t>
         </is>
       </c>
       <c r="D18" s="75" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="J18" s="75" t="inlineStr">
         <is>
-          <t>WS-014-132</t>
+          <t>DESKTOP-MQADVRK</t>
         </is>
       </c>
       <c r="K18" s="75" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L18" s="75" t="inlineStr">
         <is>
-          <t>регистратура 1 окно</t>
+          <t>регистратура 3 окно</t>
         </is>
       </c>
       <c r="M18" s="75" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="N18" s="75" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>114130</t>
         </is>
       </c>
     </row>
@@ -2302,89 +2302,89 @@
       </c>
       <c r="B19" s="73" t="inlineStr">
         <is>
-          <t>10.67.38.49</t>
+          <t>10.67.14.132 / 192.168.56.1</t>
         </is>
       </c>
       <c r="C19" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:12:1D:31</t>
+          <t>04-D9-F5-81-FB-2A / 0A-00-27-00-00-07</t>
         </is>
       </c>
       <c r="D19" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E19" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F19" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G19" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H19" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I19" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J19" s="75" t="inlineStr">
         <is>
-          <t>comp-core-i7-8700t-1051a2</t>
+          <t>WS-014-132</t>
         </is>
       </c>
       <c r="K19" s="75" t="inlineStr">
         <is>
-          <t>HP_LaserJet_MFP_M28-M31</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L19" s="75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>регистратура 1 окно</t>
         </is>
       </c>
       <c r="M19" s="75" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N19" s="75" t="inlineStr">
         <is>
-          <t>89591</t>
+          <t>114132</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="70">
       <c r="A20" s="72" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B20" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.26</t>
+          <t>10.67.38.49</t>
         </is>
       </c>
       <c r="C20" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:76:0C</t>
+          <t>00:58:3F:12:1D:31</t>
         </is>
       </c>
       <c r="D20" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E20" s="75" t="inlineStr">
@@ -2414,44 +2414,44 @@
       </c>
       <c r="J20" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>comp-core-i7-8700t-1051a2</t>
         </is>
       </c>
       <c r="K20" s="75" t="inlineStr">
         <is>
-          <t>Samsung-SCX-483x-5x3x-Series</t>
+          <t>HP_LaserJet_MFP_M28-M31</t>
         </is>
       </c>
       <c r="L20" s="75" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M20" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="N20" s="75" t="inlineStr">
         <is>
-          <t>91036</t>
+          <t>89591</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="70">
       <c r="A21" s="72" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B21" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.88</t>
+          <t>10.67.64.26</t>
         </is>
       </c>
       <c r="C21" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:72:F0</t>
+          <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
       <c r="D21" s="75" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="K21" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>Samsung-SCX-483x-5x3x-Series</t>
         </is>
       </c>
       <c r="L21" s="75" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M21" s="75" t="inlineStr">
@@ -2506,24 +2506,24 @@
       </c>
       <c r="N21" s="75" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>91036</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20.1" customHeight="1" s="70">
       <c r="A22" s="72" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B22" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.66</t>
+          <t>10.67.64.88</t>
         </is>
       </c>
       <c r="C22" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:64:28</t>
+          <t>00:58:3F:17:72:F0</t>
         </is>
       </c>
       <c r="D22" s="75" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="K22" s="75" t="inlineStr">
         <is>
-          <t>Samsung-SCX-3400-Series</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L22" s="75" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>542</t>
         </is>
       </c>
       <c r="M22" s="75" t="inlineStr">
@@ -2578,29 +2578,29 @@
       </c>
       <c r="N22" s="75" t="inlineStr">
         <is>
-          <t>89722</t>
+          <t>89588</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="70">
       <c r="A23" s="72" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B23" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.82</t>
+          <t>10.67.64.66</t>
         </is>
       </c>
       <c r="C23" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:0F:3F:87</t>
+          <t>00:58:3F:17:64:28</t>
         </is>
       </c>
       <c r="D23" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E23" s="75" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="K23" s="75" t="inlineStr">
         <is>
-          <t>HP_LaserJet_Professional_P1102</t>
+          <t>Samsung-SCX-3400-Series</t>
         </is>
       </c>
       <c r="L23" s="75" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M23" s="75" t="inlineStr">
@@ -2650,29 +2650,29 @@
       </c>
       <c r="N23" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89722</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="70">
       <c r="A24" s="72" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B24" s="73" t="inlineStr">
         <is>
-          <t>10.67.11.32</t>
+          <t>10.67.64.82</t>
         </is>
       </c>
       <c r="C24" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:0D:24:AD</t>
+          <t>00:58:3F:0F:3F:87</t>
         </is>
       </c>
       <c r="D24" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME B365M-C</t>
+          <t>Aquarius AQB365MC</t>
         </is>
       </c>
       <c r="E24" s="75" t="inlineStr">
@@ -2687,37 +2687,37 @@
       </c>
       <c r="G24" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE FLSSD256X5</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I24" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 10.4</t>
+          <t>ALT Workstation 9.0</t>
         </is>
       </c>
       <c r="J24" s="75" t="inlineStr">
         <is>
-          <t>dpk5324</t>
+          <t>1051a2</t>
         </is>
       </c>
       <c r="K24" s="75" t="inlineStr">
         <is>
-          <t>POScentre</t>
+          <t>HP_LaserJet_Professional_P1102</t>
         </is>
       </c>
       <c r="L24" s="75" t="inlineStr">
         <is>
-          <t>312-3211</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M24" s="75" t="inlineStr">
         <is>
-          <t>uprav</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N24" s="75" t="inlineStr">
@@ -2729,72 +2729,72 @@
     <row r="25" ht="20.1" customHeight="1" s="70">
       <c r="A25" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B25" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.74</t>
+          <t>10.67.11.32</t>
         </is>
       </c>
       <c r="C25" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:B1:92</t>
+          <t>00:58:3F:0D:24:AD</t>
         </is>
       </c>
       <c r="D25" s="75" t="inlineStr">
         <is>
-          <t>DEPO Computers DPH110S</t>
+          <t>ASUSTeK PRIME B365M-C</t>
         </is>
       </c>
       <c r="E25" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i3-9100 3.60GHz</t>
+          <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
       <c r="F25" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G25" s="75" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>FOXLINE FLSSD256X5</t>
         </is>
       </c>
       <c r="H25" s="75" t="inlineStr">
         <is>
-          <t>SSD 240Gb</t>
+          <t>SSD 256Gb</t>
         </is>
       </c>
       <c r="I25" s="75" t="inlineStr">
         <is>
-          <t>ALT 8 SP Workstation (cliff)</t>
+          <t>ALT Workstation 10.4</t>
         </is>
       </c>
       <c r="J25" s="75" t="inlineStr">
         <is>
-          <t>002096</t>
+          <t>dpk5324</t>
         </is>
       </c>
       <c r="K25" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>POScentre</t>
         </is>
       </c>
       <c r="L25" s="75" t="inlineStr">
         <is>
-          <t>регистратура 4 окно</t>
+          <t>312-3211</t>
         </is>
       </c>
       <c r="M25" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>uprav</t>
         </is>
       </c>
       <c r="N25" s="75" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="B26" s="73" t="inlineStr">
         <is>
-          <t>10.67.28.57</t>
+          <t>10.67.28.74</t>
         </is>
       </c>
       <c r="C26" s="74" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:A2:9E</t>
+          <t>F8:CC:6E:00:B1:92</t>
         </is>
       </c>
       <c r="D26" s="75" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="E26" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
+          <t>Intel(R) i3-9100 3.60GHz</t>
         </is>
       </c>
       <c r="F26" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>8Gb</t>
         </is>
       </c>
       <c r="G26" s="75" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="H26" s="75" t="inlineStr">
         <is>
-          <t>SSD 120Gb</t>
+          <t>SSD 240Gb</t>
         </is>
       </c>
       <c r="I26" s="75" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L26" s="75" t="inlineStr">
         <is>
-          <t>регистратура 5 окно</t>
+          <t>регистратура 4 окно</t>
         </is>
       </c>
       <c r="M26" s="75" t="inlineStr">
@@ -2866,117 +2866,121 @@
       </c>
       <c r="N26" s="75" t="inlineStr">
         <is>
-          <t>88536</t>
+          <t>88520</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20.1" customHeight="1" s="70">
       <c r="A27" s="72" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B27" s="73" t="inlineStr">
         <is>
-          <t>10.67.40.22</t>
+          <t>10.67.28.57</t>
         </is>
       </c>
       <c r="C27" s="74" t="inlineStr">
         <is>
-          <t>70-85-C2-0F-89-20</t>
+          <t>F8:CC:6E:00:A2:9E</t>
         </is>
       </c>
       <c r="D27" s="75" t="inlineStr">
         <is>
-          <t>ASRock H81M-VG4 R3.0</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E27" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-4160 3.60GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F27" s="75" t="inlineStr">
         <is>
-          <t>4Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G27" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H27" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I27" s="75" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation (cliff)</t>
         </is>
       </c>
       <c r="J27" s="75" t="inlineStr">
         <is>
-          <t>WS-040-022</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K27" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet MFP M129-M134 PCLmS</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L27" s="75" t="inlineStr">
         <is>
-          <t>заведующая</t>
+          <t>регистратура 5 окно</t>
         </is>
       </c>
       <c r="M27" s="75" t="inlineStr">
         <is>
-          <t>туберкулёз</t>
-        </is>
-      </c>
-      <c r="N27" s="75" t="inlineStr"/>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N27" s="75" t="inlineStr">
+        <is>
+          <t>88536</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="70">
       <c r="A28" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B28" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.145</t>
+          <t>10.67.40.22</t>
         </is>
       </c>
       <c r="C28" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-EA</t>
+          <t>70-85-C2-0F-89-20</t>
         </is>
       </c>
       <c r="D28" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star A320M-A PRO (MS-7C51)</t>
+          <t>ASRock H81M-VG4 R3.0</t>
         </is>
       </c>
       <c r="E28" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel i3-4160 3.60GHz</t>
         </is>
       </c>
       <c r="F28" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>4Gb</t>
         </is>
       </c>
       <c r="G28" s="75" t="inlineStr">
         <is>
-          <t>Smartbuy SSD 256GB</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H28" s="75" t="inlineStr">
         <is>
-          <t>SSD-256Gb</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I28" s="75" t="inlineStr">
@@ -2986,29 +2990,25 @@
       </c>
       <c r="J28" s="75" t="inlineStr">
         <is>
-          <t>WS-014-145</t>
+          <t>WS-040-022</t>
         </is>
       </c>
       <c r="K28" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP LaserJet MFP M129-M134 PCLmS</t>
         </is>
       </c>
       <c r="L28" s="75" t="inlineStr">
         <is>
-          <t>регистратура - 6 окно</t>
+          <t>заведующая</t>
         </is>
       </c>
       <c r="M28" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
-        </is>
-      </c>
-      <c r="N28" s="75" t="inlineStr">
-        <is>
-          <t>88749</t>
-        </is>
-      </c>
+          <t>туберкулёз</t>
+        </is>
+      </c>
+      <c r="N28" s="75" t="inlineStr"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" s="70">
       <c r="A29" s="72" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B29" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.146</t>
+          <t>10.67.14.145</t>
         </is>
       </c>
       <c r="C29" s="74" t="inlineStr">
         <is>
-          <t>2C-F0-5D-9E-B2-5D</t>
+          <t>2C-F0-5D-9E-B2-EA</t>
         </is>
       </c>
       <c r="D29" s="75" t="inlineStr">
         <is>
-          <t>Micro-Star  A320M-A PRO (MS-7C51)</t>
+          <t>Micro-Star A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E29" s="75" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J29" s="75" t="inlineStr">
         <is>
-          <t>WS-014-146</t>
+          <t>WS-014-145</t>
         </is>
       </c>
       <c r="K29" s="75" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L29" s="75" t="inlineStr">
         <is>
-          <t>регистратура 5 окно</t>
+          <t>регистратура - 6 окно</t>
         </is>
       </c>
       <c r="M29" s="75" t="inlineStr">
@@ -3078,49 +3078,49 @@
       </c>
       <c r="N29" s="75" t="inlineStr">
         <is>
-          <t>88745</t>
+          <t>88749</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20.1" customHeight="1" s="70">
       <c r="A30" s="72" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B30" s="73" t="inlineStr">
         <is>
-          <t>10.67.40.24</t>
+          <t>10.67.14.146</t>
         </is>
       </c>
       <c r="C30" s="74" t="inlineStr">
         <is>
-          <t>10-FF-E0-28-EC-18</t>
+          <t>2C-F0-5D-9E-B2-5D</t>
         </is>
       </c>
       <c r="D30" s="75" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>Micro-Star  A320M-A PRO (MS-7C51)</t>
         </is>
       </c>
       <c r="E30" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F30" s="75" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G30" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>SSD-256Gb</t>
         </is>
       </c>
       <c r="I30" s="75" t="inlineStr">
@@ -3130,65 +3130,69 @@
       </c>
       <c r="J30" s="75" t="inlineStr">
         <is>
-          <t>WS-040-024</t>
+          <t>WS-014-146</t>
         </is>
       </c>
       <c r="K30" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Professional M1214nfh MFP</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L30" s="75" t="inlineStr">
         <is>
-          <t>9 заведующая</t>
+          <t>регистратура 5 окно</t>
         </is>
       </c>
       <c r="M30" s="75" t="inlineStr">
         <is>
-          <t>туберкулёз</t>
-        </is>
-      </c>
-      <c r="N30" s="75" t="inlineStr"/>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N30" s="75" t="inlineStr">
+        <is>
+          <t>88745</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20.1" customHeight="1" s="70">
       <c r="A31" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B31" s="73" t="inlineStr">
         <is>
-          <t>10.67.14.133</t>
+          <t>10.67.40.24</t>
         </is>
       </c>
       <c r="C31" s="74" t="inlineStr">
         <is>
-          <t>04-D9-F5-81-FB-2B</t>
+          <t>10-FF-E0-28-EC-18</t>
         </is>
       </c>
       <c r="D31" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME A320M-A</t>
+          <t>Gigabyte H410M K</t>
         </is>
       </c>
       <c r="E31" s="75" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
+          <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
       <c r="F31" s="75" t="inlineStr">
         <is>
-          <t>6Gb</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G31" s="75" t="inlineStr">
         <is>
-          <t>ST1000DM010-2EP102</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H31" s="75" t="inlineStr">
         <is>
-          <t>HDD-1Tb</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I31" s="75" t="inlineStr">
@@ -3198,69 +3202,65 @@
       </c>
       <c r="J31" s="75" t="inlineStr">
         <is>
-          <t>WS-014-133</t>
+          <t>WS-040-024</t>
         </is>
       </c>
       <c r="K31" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>HP LaserJet Professional M1214nfh MFP</t>
         </is>
       </c>
       <c r="L31" s="75" t="inlineStr">
         <is>
-          <t>регитратура 4 окно</t>
+          <t>9 заведующая</t>
         </is>
       </c>
       <c r="M31" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
-        </is>
-      </c>
-      <c r="N31" s="75" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+          <t>туберкулёз</t>
+        </is>
+      </c>
+      <c r="N31" s="75" t="inlineStr"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" s="70">
       <c r="A32" s="72" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B32" s="73" t="inlineStr">
         <is>
-          <t>192.168.56.1</t>
+          <t>10.67.14.133</t>
         </is>
       </c>
       <c r="C32" s="74" t="inlineStr">
         <is>
-          <t>04-42-1A-0F-29-A3</t>
+          <t>04-D9-F5-81-FB-2B</t>
         </is>
       </c>
       <c r="D32" s="75" t="inlineStr">
         <is>
-          <t>ASUSTeK PRIME H510M-R</t>
+          <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
       <c r="E32" s="75" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>AMD Ryzen 5 3400G with Radeon Vega Graphics</t>
         </is>
       </c>
       <c r="F32" s="75" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>6Gb</t>
         </is>
       </c>
       <c r="G32" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>ST1000DM010-2EP102</t>
         </is>
       </c>
       <c r="H32" s="75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>HDD-1Tb</t>
         </is>
       </c>
       <c r="I32" s="75" t="inlineStr">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="J32" s="75" t="inlineStr">
         <is>
-          <t>WS-014-0198</t>
+          <t>WS-014-133</t>
         </is>
       </c>
       <c r="K32" s="75" t="inlineStr">
         <is>
-          <t>HP Color LaserJet Pro MFP 4303</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L32" s="75" t="inlineStr">
         <is>
-          <t>Кирилл Николаевич приемная</t>
+          <t>регитратура 4 окно</t>
         </is>
       </c>
       <c r="M32" s="75" t="inlineStr">
@@ -3288,67 +3288,71 @@
           <t>pol1</t>
         </is>
       </c>
-      <c r="N32" s="75" t="inlineStr"/>
+      <c r="N32" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="70">
       <c r="A33" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B33" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.87</t>
+          <t>192.168.56.1</t>
         </is>
       </c>
       <c r="C33" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:72:20</t>
+          <t>04-42-1A-0F-29-A3</t>
         </is>
       </c>
       <c r="D33" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>ASUSTeK PRIME H510M-R</t>
         </is>
       </c>
       <c r="E33" s="75" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
       <c r="F33" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G33" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H33" s="75" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I33" s="75" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J33" s="75" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-014-0198</t>
         </is>
       </c>
       <c r="K33" s="75" t="inlineStr">
         <is>
-          <t>M428</t>
+          <t>HP Color LaserJet Pro MFP 4303</t>
         </is>
       </c>
       <c r="L33" s="75" t="inlineStr">
         <is>
-          <t>регистратура - 6 окно</t>
+          <t>Кирилл Николаевич приемная</t>
         </is>
       </c>
       <c r="M33" s="75" t="inlineStr">
@@ -3356,11 +3360,7 @@
           <t>pol1</t>
         </is>
       </c>
-      <c r="N33" s="75" t="inlineStr">
-        <is>
-          <t>89636</t>
-        </is>
-      </c>
+      <c r="N33" s="75" t="inlineStr"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" s="70">
       <c r="A34" s="72" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B34" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>10.67.64.87</t>
         </is>
       </c>
       <c r="C34" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>00:58:3F:17:72:20</t>
         </is>
       </c>
       <c r="D34" s="75" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F34" s="75" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>8Gb</t>
         </is>
       </c>
       <c r="G34" s="75" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="K34" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M428fdw</t>
+          <t>M428</t>
         </is>
       </c>
       <c r="L34" s="75" t="inlineStr">
         <is>
-          <t>регистратура - расписание</t>
+          <t>регистратура - 6 окно</t>
         </is>
       </c>
       <c r="M34" s="75" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="N34" s="75" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>89636</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="B35" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.103</t>
+          <t>10.67.64.98</t>
         </is>
       </c>
       <c r="C35" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:10</t>
+          <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
       <c r="D35" s="75" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="F35" s="75" t="inlineStr">
         <is>
-          <t>8Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G35" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5 DataTraveler_3.0</t>
+          <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
       <c r="H35" s="75" t="inlineStr">
@@ -3487,39 +3487,39 @@
       </c>
       <c r="K35" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
       <c r="L35" s="75" t="inlineStr">
         <is>
-          <t>ординаторская</t>
+          <t>регистратура - расписание</t>
         </is>
       </c>
       <c r="M35" s="75" t="inlineStr">
         <is>
-          <t>хирургия онкология 3 этаж</t>
+          <t>pol1</t>
         </is>
       </c>
       <c r="N35" s="75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>89681</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20.1" customHeight="1" s="70">
       <c r="A36" s="72" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B36" s="73" t="inlineStr">
         <is>
-          <t>10.67.64.73</t>
+          <t>10.67.64.103</t>
         </is>
       </c>
       <c r="C36" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:17:5A:FA</t>
+          <t>00:58:3F:17:6A:10</t>
         </is>
       </c>
       <c r="D36" s="75" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="G36" s="75" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>FOXLINE_FLSSD256X5 DataTraveler_3.0</t>
         </is>
       </c>
       <c r="H36" s="75" t="inlineStr">
@@ -3559,40 +3559,44 @@
       </c>
       <c r="K36" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet 1320</t>
+          <t>HP LaserJet Pro MFP 4103</t>
         </is>
       </c>
       <c r="L36" s="75" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>ординаторская</t>
         </is>
       </c>
       <c r="M36" s="75" t="inlineStr">
         <is>
-          <t>pol1</t>
-        </is>
-      </c>
-      <c r="N36" s="75" t="inlineStr"/>
+          <t>хирургия онкология 3 этаж</t>
+        </is>
+      </c>
+      <c r="N36" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20.1" customHeight="1" s="70">
       <c r="A37" s="72" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B37" s="73" t="inlineStr">
         <is>
-          <t>10.67.12.77</t>
+          <t>10.67.64.73</t>
         </is>
       </c>
       <c r="C37" s="74" t="inlineStr">
         <is>
-          <t>00:58:3F:16:55:32</t>
+          <t>00:58:3F:17:5A:FA</t>
         </is>
       </c>
       <c r="D37" s="75" t="inlineStr">
         <is>
-          <t>Aquarius AQB365MC</t>
+          <t>Aquarius AQH310CM</t>
         </is>
       </c>
       <c r="E37" s="75" t="inlineStr">
@@ -3627,154 +3631,155 @@
       </c>
       <c r="K37" s="75" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>HP LaserJet 1320</t>
         </is>
       </c>
       <c r="L37" s="75" t="inlineStr">
         <is>
-          <t>ординаторская</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M37" s="75" t="inlineStr">
         <is>
-          <t>жирургия онкология 3 этаж</t>
-        </is>
-      </c>
-      <c r="N37" s="75" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+          <t>pol1</t>
+        </is>
+      </c>
+      <c r="N37" s="75" t="inlineStr"/>
     </row>
     <row r="38" ht="20.1" customHeight="1" s="70">
       <c r="A38" s="72" t="inlineStr">
         <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>10.67.12.77</t>
+        </is>
+      </c>
+      <c r="C38" s="74" t="inlineStr">
+        <is>
+          <t>00:58:3F:16:55:32</t>
+        </is>
+      </c>
+      <c r="D38" s="75" t="inlineStr">
+        <is>
+          <t>Aquarius AQB365MC</t>
+        </is>
+      </c>
+      <c r="E38" s="75" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F38" s="75" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G38" s="75" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H38" s="75" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I38" s="75" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J38" s="75" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K38" s="75" t="inlineStr">
+        <is>
+          <t>HP LaserJet Pro MFP 4103</t>
+        </is>
+      </c>
+      <c r="L38" s="75" t="inlineStr">
+        <is>
+          <t>ординаторская</t>
+        </is>
+      </c>
+      <c r="M38" s="75" t="inlineStr">
+        <is>
+          <t>жирургия онкология 3 этаж</t>
+        </is>
+      </c>
+      <c r="N38" s="75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20.1" customHeight="1" s="70">
+      <c r="A39" s="72" t="inlineStr">
+        <is>
           <t>24.08.2026</t>
         </is>
       </c>
-      <c r="B38" s="73" t="inlineStr">
+      <c r="B39" s="73" t="inlineStr">
         <is>
           <t>10.67.64.73</t>
         </is>
       </c>
-      <c r="C38" s="74" t="inlineStr">
+      <c r="C39" s="74" t="inlineStr">
         <is>
           <t>00:58:3F:17:5A:FA</t>
         </is>
       </c>
-      <c r="D38" s="75" t="inlineStr">
+      <c r="D39" s="75" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E38" s="75" t="inlineStr">
+      <c r="E39" s="75" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F38" s="75" t="inlineStr">
+      <c r="F39" s="75" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G38" s="75" t="inlineStr">
+      <c r="G39" s="75" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H38" s="75" t="inlineStr">
+      <c r="H39" s="75" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I38" s="75" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J38" s="75" t="inlineStr">
+      <c r="J39" s="75" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K38" s="75" t="inlineStr">
+      <c r="K39" s="75" t="inlineStr">
         <is>
           <t>HP LaserJet 1320</t>
         </is>
       </c>
-      <c r="L38" s="75" t="inlineStr">
+      <c r="L39" s="75" t="inlineStr">
         <is>
           <t>828</t>
         </is>
       </c>
-      <c r="M38" s="75" t="inlineStr">
-        <is>
-          <t>pol1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20.1" customHeight="1" s="70">
-      <c r="A39" s="66" t="inlineStr">
-        <is>
-          <t>29.07.2026</t>
-        </is>
-      </c>
-      <c r="B39" s="63" t="inlineStr">
-        <is>
-          <t>10.67.14.168</t>
-        </is>
-      </c>
-      <c r="C39" s="64" t="inlineStr">
-        <is>
-          <t>F8:CC:6E:00:AF:29</t>
-        </is>
-      </c>
-      <c r="D39" s="65" t="inlineStr">
-        <is>
-          <t>DEPO Computers DPH110S</t>
-        </is>
-      </c>
-      <c r="E39" s="65" t="inlineStr">
-        <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
-        </is>
-      </c>
-      <c r="F39" s="65" t="inlineStr">
-        <is>
-          <t>8GB</t>
-        </is>
-      </c>
-      <c r="G39" s="65" t="inlineStr">
-        <is>
-          <t>QUMO_SSD ProductCode</t>
-        </is>
-      </c>
-      <c r="H39" s="65" t="inlineStr">
-        <is>
-          <t>SSD 120Gb</t>
-        </is>
-      </c>
-      <c r="I39" s="65" t="inlineStr">
-        <is>
-          <t>ALT 8 SP Workstation</t>
-        </is>
-      </c>
-      <c r="J39" s="65" t="inlineStr">
-        <is>
-          <t>002096</t>
-        </is>
-      </c>
-      <c r="K39" s="65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L39" s="65" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="M39" s="65" t="inlineStr">
+      <c r="M39" s="75" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
@@ -3783,17 +3788,17 @@
     <row r="40" ht="20.1" customHeight="1" s="70">
       <c r="A40" s="66" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>10.67.28.72</t>
+          <t>10.67.14.168</t>
         </is>
       </c>
       <c r="C40" s="64" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:5B:1A</t>
+          <t>F8:CC:6E:00:AF:29</t>
         </is>
       </c>
       <c r="D40" s="65" t="inlineStr">
@@ -3813,7 +3818,7 @@
       </c>
       <c r="G40" s="65" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>QUMO_SSD ProductCode</t>
         </is>
       </c>
       <c r="H40" s="65" t="inlineStr">
@@ -3838,29 +3843,29 @@
       </c>
       <c r="L40" s="65" t="inlineStr">
         <is>
-          <t>ord</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M40" s="65" t="inlineStr">
         <is>
-          <t>rod-3</t>
+          <t>pol1</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" s="70">
       <c r="A41" s="66" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B41" s="63" t="inlineStr">
         <is>
-          <t>10.67.28.69</t>
+          <t>10.67.28.72</t>
         </is>
       </c>
       <c r="C41" s="64" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:4F:13</t>
+          <t>F8:CC:6E:00:5B:1A</t>
         </is>
       </c>
       <c r="D41" s="65" t="inlineStr">
@@ -3900,168 +3905,168 @@
       </c>
       <c r="K41" s="65" t="inlineStr">
         <is>
-          <t>Samsung SCX-4833FD</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L41" s="65" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>ord</t>
         </is>
       </c>
       <c r="M41" s="65" t="inlineStr">
         <is>
-          <t>det.pol</t>
+          <t>rod-3</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20.1" customHeight="1" s="70">
       <c r="A42" s="66" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>10.67.28.69</t>
         </is>
       </c>
       <c r="C42" s="64" t="inlineStr">
         <is>
-          <t>10:FF:E0:63:F1:98</t>
+          <t>F8:CC:6E:00:4F:13</t>
         </is>
       </c>
       <c r="D42" s="65" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E42" s="65" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F42" s="65" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G42" s="65" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H42" s="65" t="inlineStr">
         <is>
-          <t>SSD 440Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I42" s="65" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation</t>
         </is>
       </c>
       <c r="J42" s="65" t="inlineStr">
         <is>
-          <t>WS-016-052</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K42" s="65" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>Samsung SCX-4833FD</t>
         </is>
       </c>
       <c r="L42" s="65" t="inlineStr">
         <is>
-          <t>zav</t>
+          <t>314</t>
         </is>
       </c>
       <c r="M42" s="65" t="inlineStr">
         <is>
-          <t>pblock</t>
+          <t>det.pol</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20.1" customHeight="1" s="70">
       <c r="A43" s="66" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B43" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="C43" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>10:FF:E0:63:F1:98</t>
         </is>
       </c>
       <c r="D43" s="65" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Gigabyte H410M K</t>
         </is>
       </c>
       <c r="E43" s="65" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
       <c r="F43" s="65" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G43" s="65" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="H43" s="65" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 440Gb</t>
         </is>
       </c>
       <c r="I43" s="65" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J43" s="65" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-016-052</t>
         </is>
       </c>
       <c r="K43" s="65" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro M426fdn</t>
+          <t>HP LaserJet Pro MFP 4103</t>
         </is>
       </c>
       <c r="L43" s="65" t="inlineStr">
         <is>
-          <t>reg.raspis</t>
+          <t>zav</t>
         </is>
       </c>
       <c r="M43" s="65" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>pblock</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20.1" customHeight="1" s="70">
       <c r="A44" s="66" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.77</t>
+          <t>10.67.64.98</t>
         </is>
       </c>
       <c r="C44" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:00</t>
+          <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
       <c r="D44" s="65" t="inlineStr">
@@ -4086,7 +4091,7 @@
       </c>
       <c r="H44" s="65" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>SSD 256Gb</t>
         </is>
       </c>
       <c r="I44" s="65" t="inlineStr">
@@ -4101,12 +4106,12 @@
       </c>
       <c r="K44" s="65" t="inlineStr">
         <is>
-          <t>Samsung SCX-4833</t>
+          <t>HP LaserJet Pro M426fdn</t>
         </is>
       </c>
       <c r="L44" s="65" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>reg.raspis</t>
         </is>
       </c>
       <c r="M44" s="65" t="inlineStr">
@@ -4118,17 +4123,17 @@
     <row r="45" ht="20.1" customHeight="1" s="70">
       <c r="A45" s="66" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B45" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.46</t>
+          <t>10.67.64.77</t>
         </is>
       </c>
       <c r="C45" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:69:FE</t>
+          <t>00:58:3F:17:6A:00</t>
         </is>
       </c>
       <c r="D45" s="65" t="inlineStr">
@@ -4153,7 +4158,7 @@
       </c>
       <c r="H45" s="65" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 260Gb</t>
         </is>
       </c>
       <c r="I45" s="65" t="inlineStr">
@@ -4168,12 +4173,12 @@
       </c>
       <c r="K45" s="65" t="inlineStr">
         <is>
-          <t>Cups-PDF</t>
+          <t>Samsung SCX-4833</t>
         </is>
       </c>
       <c r="L45" s="65" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M45" s="65" t="inlineStr">
@@ -4185,17 +4190,17 @@
     <row r="46" ht="20.1" customHeight="1" s="70">
       <c r="A46" s="66" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.67</t>
+          <t>10.67.64.46</t>
         </is>
       </c>
       <c r="C46" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:57:F8</t>
+          <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
       <c r="D46" s="65" t="inlineStr">
@@ -4220,7 +4225,7 @@
       </c>
       <c r="H46" s="65" t="inlineStr">
         <is>
-          <t>SSD 260Gb</t>
+          <t>SSD 256Gb</t>
         </is>
       </c>
       <c r="I46" s="65" t="inlineStr">
@@ -4235,12 +4240,12 @@
       </c>
       <c r="K46" s="65" t="inlineStr">
         <is>
-          <t>HP_LaserJet_Professional_P1102</t>
+          <t>Cups-PDF</t>
         </is>
       </c>
       <c r="L46" s="65" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M46" s="65" t="inlineStr">
@@ -4252,132 +4257,132 @@
     <row r="47" ht="20.1" customHeight="1" s="70">
       <c r="A47" s="66" t="inlineStr">
         <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>10.67.64.67</t>
+        </is>
+      </c>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:57:F8</t>
+        </is>
+      </c>
+      <c r="D47" s="65" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E47" s="65" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F47" s="65" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G47" s="65" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H47" s="65" t="inlineStr">
+        <is>
+          <t>SSD 260Gb</t>
+        </is>
+      </c>
+      <c r="I47" s="65" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J47" s="65" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K47" s="65" t="inlineStr">
+        <is>
+          <t>HP_LaserJet_Professional_P1102</t>
+        </is>
+      </c>
+      <c r="L47" s="65" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="M47" s="65" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20.1" customHeight="1" s="70">
+      <c r="A48" s="66" t="inlineStr">
+        <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="B47" s="63" t="inlineStr">
+      <c r="B48" s="63" t="inlineStr">
         <is>
           <t>10.67.64.56</t>
         </is>
       </c>
-      <c r="C47" s="64" t="inlineStr">
+      <c r="C48" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:6A</t>
         </is>
       </c>
-      <c r="D47" s="65" t="inlineStr">
+      <c r="D48" s="65" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E47" s="65" t="inlineStr">
+      <c r="E48" s="65" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F47" s="65" t="inlineStr">
+      <c r="F48" s="65" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G47" s="65" t="inlineStr">
+      <c r="G48" s="65" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H47" s="65" t="inlineStr">
+      <c r="H48" s="65" t="inlineStr">
         <is>
           <t>SSD 260Gb</t>
         </is>
       </c>
-      <c r="I47" s="65" t="inlineStr">
+      <c r="I48" s="65" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J47" s="65" t="inlineStr">
+      <c r="J48" s="65" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K47" s="65" t="inlineStr">
+      <c r="K48" s="65" t="inlineStr">
         <is>
           <t>HP_LaserJet_P2055d</t>
         </is>
       </c>
-      <c r="L47" s="65" t="inlineStr">
+      <c r="L48" s="65" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="M47" s="65" t="inlineStr">
-        <is>
-          <t>pol1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20.1" customHeight="1" s="70">
-      <c r="A48" s="62" t="inlineStr">
-        <is>
-          <t>29.07.2026</t>
-        </is>
-      </c>
-      <c r="B48" s="63" t="inlineStr">
-        <is>
-          <t>10.67.14.168</t>
-        </is>
-      </c>
-      <c r="C48" s="64" t="inlineStr">
-        <is>
-          <t>F8:CC:6E:00:AF:29</t>
-        </is>
-      </c>
-      <c r="D48" s="61" t="inlineStr">
-        <is>
-          <t>DEPO Computers DPH110S</t>
-        </is>
-      </c>
-      <c r="E48" s="61" t="inlineStr">
-        <is>
-          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
-        </is>
-      </c>
-      <c r="F48" s="61" t="inlineStr">
-        <is>
-          <t>8GB</t>
-        </is>
-      </c>
-      <c r="G48" s="61" t="inlineStr">
-        <is>
-          <t>QUMO_SSD ProductCode</t>
-        </is>
-      </c>
-      <c r="H48" s="61" t="inlineStr">
-        <is>
-          <t>SSD 120Gb</t>
-        </is>
-      </c>
-      <c r="I48" s="61" t="inlineStr">
-        <is>
-          <t>ALT 8 SP Workstation</t>
-        </is>
-      </c>
-      <c r="J48" s="61" t="inlineStr">
-        <is>
-          <t>002096</t>
-        </is>
-      </c>
-      <c r="K48" s="61" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L48" s="61" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="M48" s="61" t="inlineStr">
+      <c r="M48" s="65" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
@@ -4386,17 +4391,17 @@
     <row r="49" ht="20.1" customHeight="1" s="70">
       <c r="A49" s="62" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B49" s="63" t="inlineStr">
         <is>
-          <t>10.67.28.72</t>
+          <t>10.67.14.168</t>
         </is>
       </c>
       <c r="C49" s="64" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:5B:1A</t>
+          <t>F8:CC:6E:00:AF:29</t>
         </is>
       </c>
       <c r="D49" s="61" t="inlineStr">
@@ -4416,7 +4421,7 @@
       </c>
       <c r="G49" s="61" t="inlineStr">
         <is>
-          <t>QUMO_SSD</t>
+          <t>QUMO_SSD ProductCode</t>
         </is>
       </c>
       <c r="H49" s="61" t="inlineStr">
@@ -4441,29 +4446,29 @@
       </c>
       <c r="L49" s="61" t="inlineStr">
         <is>
-          <t>ord</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M49" s="61" t="inlineStr">
         <is>
-          <t>rod3</t>
+          <t>pol1</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20.1" customHeight="1" s="70">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>10.67.28.69</t>
+          <t>10.67.28.72</t>
         </is>
       </c>
       <c r="C50" s="64" t="inlineStr">
         <is>
-          <t>F8:CC:6E:00:4F:13</t>
+          <t>F8:CC:6E:00:5B:1A</t>
         </is>
       </c>
       <c r="D50" s="61" t="inlineStr">
@@ -4503,151 +4508,151 @@
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
-          <t>samsung4833</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L50" s="61" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>ord</t>
         </is>
       </c>
       <c r="M50" s="61" t="inlineStr">
         <is>
-          <t>det.pol</t>
+          <t>rod3</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20.1" customHeight="1" s="70">
       <c r="A51" s="62" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B51" s="63" t="inlineStr">
         <is>
-          <t>127.0.0.1</t>
+          <t>10.67.28.69</t>
         </is>
       </c>
       <c r="C51" s="64" t="inlineStr">
         <is>
-          <t>10:FF:E0:63:F1:98</t>
+          <t>F8:CC:6E:00:4F:13</t>
         </is>
       </c>
       <c r="D51" s="61" t="inlineStr">
         <is>
-          <t>Gigabyte H410M K</t>
+          <t>DEPO Computers DPH110S</t>
         </is>
       </c>
       <c r="E51" s="61" t="inlineStr">
         <is>
-          <t>Intel i3-10100 3.60GHz</t>
+          <t>Intel(R) Pentium(R) Gold G5420 3.80GHz</t>
         </is>
       </c>
       <c r="F51" s="61" t="inlineStr">
         <is>
-          <t>16Gb</t>
+          <t>8GB</t>
         </is>
       </c>
       <c r="G51" s="61" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>QUMO_SSD</t>
         </is>
       </c>
       <c r="H51" s="61" t="inlineStr">
         <is>
-          <t>SSD 440Gb</t>
+          <t>SSD 120Gb</t>
         </is>
       </c>
       <c r="I51" s="61" t="inlineStr">
         <is>
-          <t>Windows 10 Pro</t>
+          <t>ALT 8 SP Workstation</t>
         </is>
       </c>
       <c r="J51" s="61" t="inlineStr">
         <is>
-          <t>WS-016-052</t>
+          <t>002096</t>
         </is>
       </c>
       <c r="K51" s="61" t="inlineStr">
         <is>
-          <t>HP LaserJet Pro MFP 4103</t>
+          <t>samsung4833</t>
         </is>
       </c>
       <c r="L51" s="61" t="inlineStr">
         <is>
-          <t>zav</t>
+          <t>314</t>
         </is>
       </c>
       <c r="M51" s="61" t="inlineStr">
         <is>
-          <t>pblock</t>
+          <t>det.pol</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20.1" customHeight="1" s="70">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>10.67.64.98</t>
+          <t>127.0.0.1</t>
         </is>
       </c>
       <c r="C52" s="64" t="inlineStr">
         <is>
-          <t>00:58:3F:17:6A:B2</t>
+          <t>10:FF:E0:63:F1:98</t>
         </is>
       </c>
       <c r="D52" s="61" t="inlineStr">
         <is>
-          <t>Aquarius AQH310CM</t>
+          <t>Gigabyte H410M K</t>
         </is>
       </c>
       <c r="E52" s="61" t="inlineStr">
         <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
+          <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
       <c r="F52" s="61" t="inlineStr">
         <is>
-          <t>8GB</t>
+          <t>16Gb</t>
         </is>
       </c>
       <c r="G52" s="61" t="inlineStr">
         <is>
-          <t>FOXLINE_FLSSD256X5</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
         <is>
-          <t>SSD 256Gb</t>
+          <t>SSD 440Gb</t>
         </is>
       </c>
       <c r="I52" s="61" t="inlineStr">
         <is>
-          <t>ALT Workstation 9.0</t>
+          <t>Windows 10 Pro</t>
         </is>
       </c>
       <c r="J52" s="61" t="inlineStr">
         <is>
-          <t>1051a2</t>
+          <t>WS-016-052</t>
         </is>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
-          <t>M428f</t>
+          <t>HP LaserJet Pro MFP 4103</t>
         </is>
       </c>
       <c r="L52" s="61" t="inlineStr">
         <is>
-          <t>reg.raspis</t>
+          <t>zav</t>
         </is>
       </c>
       <c r="M52" s="61" t="inlineStr">
         <is>
-          <t>pol1</t>
+          <t>pblock</t>
         </is>
       </c>
     </row>
@@ -4659,2593 +4664,2660 @@
       </c>
       <c r="B53" s="63" t="inlineStr">
         <is>
+          <t>10.67.64.98</t>
+        </is>
+      </c>
+      <c r="C53" s="64" t="inlineStr">
+        <is>
+          <t>00:58:3F:17:6A:B2</t>
+        </is>
+      </c>
+      <c r="D53" s="61" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F53" s="61" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="G53" s="61" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H53" s="61" t="inlineStr">
+        <is>
+          <t>SSD 256Gb</t>
+        </is>
+      </c>
+      <c r="I53" s="61" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J53" s="61" t="inlineStr">
+        <is>
+          <t>1051a2</t>
+        </is>
+      </c>
+      <c r="K53" s="61" t="inlineStr">
+        <is>
+          <t>M428f</t>
+        </is>
+      </c>
+      <c r="L53" s="61" t="inlineStr">
+        <is>
+          <t>reg.raspis</t>
+        </is>
+      </c>
+      <c r="M53" s="61" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20.1" customHeight="1" s="70">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C53" s="64" t="inlineStr">
+      <c r="C54" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D54" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E54" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F53" s="61" t="inlineStr">
+      <c r="F54" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G53" s="61" t="inlineStr">
+      <c r="G54" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H53" s="61" t="inlineStr">
+      <c r="H54" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I53" s="61" t="inlineStr">
+      <c r="I54" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J53" s="61" t="inlineStr">
+      <c r="J54" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K53" s="61" t="inlineStr">
+      <c r="K54" s="61" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L53" s="61" t="inlineStr">
+      <c r="L54" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M53" s="61" t="inlineStr">
+      <c r="M54" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" s="70">
-      <c r="A54" s="59" t="n">
+    <row r="55" ht="15.75" customHeight="1" s="70">
+      <c r="A55" s="59" t="n">
         <v>46231</v>
       </c>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="B55" s="63" t="inlineStr">
         <is>
           <t>10.67.2.33</t>
         </is>
       </c>
-      <c r="C54" s="64" t="inlineStr">
+      <c r="C55" s="64" t="inlineStr">
         <is>
           <t>F0-B4-D2-2C-6D-1D</t>
         </is>
       </c>
-      <c r="D54" s="61" t="inlineStr">
+      <c r="D55" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H510M H</t>
         </is>
       </c>
-      <c r="E54" s="61" t="inlineStr">
+      <c r="E55" s="61" t="inlineStr">
         <is>
           <t>Intel i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F54" s="61" t="inlineStr">
+      <c r="F55" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G54" s="61" t="inlineStr">
+      <c r="G55" s="61" t="inlineStr">
         <is>
           <t>KINGSTON SA400S37480G</t>
         </is>
       </c>
-      <c r="H54" s="61" t="inlineStr">
+      <c r="H55" s="61" t="inlineStr">
         <is>
           <t>SSD 480Gb</t>
         </is>
       </c>
-      <c r="I54" s="61" t="inlineStr">
+      <c r="I55" s="61" t="inlineStr">
         <is>
           <t>Windows 10 IoT Enterprise LTSC</t>
         </is>
       </c>
-      <c r="J54" s="61" t="inlineStr">
+      <c r="J55" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K54" s="61" t="inlineStr">
+      <c r="K55" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428fdw</t>
         </is>
       </c>
-      <c r="L54" s="61" t="inlineStr">
+      <c r="L55" s="61" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="M54" s="61" t="inlineStr">
+      <c r="M55" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="70">
-      <c r="A55" s="58" t="n">
+    <row r="56" ht="15.75" customHeight="1" s="70">
+      <c r="A56" s="58" t="n">
         <v>46232</v>
       </c>
-      <c r="B55" s="63" t="inlineStr">
+      <c r="B56" s="63" t="inlineStr">
         <is>
           <t>10.67.14.88</t>
         </is>
       </c>
-      <c r="C55" s="64" t="inlineStr">
+      <c r="C56" s="64" t="inlineStr">
         <is>
           <t>D0-27-88-9A-7C-7C</t>
         </is>
       </c>
-      <c r="D55" s="61" t="inlineStr">
+      <c r="D56" s="61" t="inlineStr">
         <is>
           <t>Foxconn H61S</t>
         </is>
       </c>
-      <c r="E55" s="61" t="inlineStr">
+      <c r="E56" s="61" t="inlineStr">
         <is>
           <t>Intel Celeron CPU G530 2.40GHz</t>
         </is>
       </c>
-      <c r="F55" s="61" t="inlineStr">
+      <c r="F56" s="61" t="inlineStr">
         <is>
           <t>12Gb</t>
         </is>
       </c>
-      <c r="G55" s="61" t="inlineStr">
+      <c r="G56" s="61" t="inlineStr">
         <is>
           <t>WD Green</t>
         </is>
       </c>
-      <c r="H55" s="61" t="inlineStr">
+      <c r="H56" s="61" t="inlineStr">
         <is>
           <t>SSD 500Gb</t>
         </is>
       </c>
-      <c r="I55" s="61" t="inlineStr">
+      <c r="I56" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J55" s="61" t="inlineStr">
+      <c r="J56" s="61" t="inlineStr">
         <is>
           <t>WS-014-088</t>
         </is>
       </c>
-      <c r="K55" s="61" t="inlineStr">
+      <c r="K56" s="61" t="inlineStr">
         <is>
           <t>Samsung SCX-483x 5x3x Series</t>
         </is>
       </c>
-      <c r="L55" s="61" t="inlineStr">
+      <c r="L56" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M55" s="61" t="inlineStr">
+      <c r="M56" s="61" t="inlineStr">
         <is>
           <t>pol1 khl</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="70">
-      <c r="A56" s="57" t="n">
+    <row r="57" ht="15.75" customHeight="1" s="70">
+      <c r="A57" s="57" t="n">
         <v>46232</v>
       </c>
-      <c r="B56" s="63" t="inlineStr">
+      <c r="B57" s="63" t="inlineStr">
         <is>
           <t>10.67.64.46</t>
         </is>
       </c>
-      <c r="C56" s="64" t="inlineStr">
+      <c r="C57" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:69:FE</t>
         </is>
       </c>
-      <c r="D56" s="61" t="inlineStr">
+      <c r="D57" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E56" s="61" t="inlineStr">
+      <c r="E57" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F56" s="61" t="inlineStr">
+      <c r="F57" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G56" s="61" t="inlineStr">
+      <c r="G57" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H56" s="61" t="inlineStr">
+      <c r="H57" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I56" s="61" t="inlineStr">
+      <c r="I57" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J56" s="61" t="inlineStr">
+      <c r="J57" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K56" s="61" t="inlineStr">
+      <c r="K57" s="61" t="inlineStr">
         <is>
           <t>Cups-PDF</t>
         </is>
       </c>
-      <c r="L56" s="61" t="inlineStr">
+      <c r="L57" s="61" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="M56" s="61" t="inlineStr">
+      <c r="M57" s="61" t="inlineStr">
         <is>
           <t>pol1 khl</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="70">
-      <c r="A57" s="56" t="n">
+    <row r="58" ht="15.75" customHeight="1" s="70">
+      <c r="A58" s="56" t="n">
         <v>46231</v>
       </c>
-      <c r="B57" s="63" t="inlineStr">
+      <c r="B58" s="63" t="inlineStr">
         <is>
           <t>10.67.24.12</t>
         </is>
       </c>
-      <c r="C57" s="64" t="inlineStr">
+      <c r="C58" s="64" t="inlineStr">
         <is>
           <t>04-D9-F5-81-FB-29</t>
         </is>
       </c>
-      <c r="D57" s="61" t="inlineStr">
+      <c r="D58" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME A320M-A</t>
         </is>
       </c>
-      <c r="E57" s="61" t="inlineStr">
+      <c r="E58" s="61" t="inlineStr">
         <is>
           <t>AMD Ryzen 5 3400G</t>
         </is>
       </c>
-      <c r="F57" s="61" t="inlineStr">
+      <c r="F58" s="61" t="inlineStr">
         <is>
           <t>6GiB</t>
         </is>
       </c>
-      <c r="G57" s="61" t="inlineStr">
+      <c r="G58" s="61" t="inlineStr">
         <is>
           <t>WDC WD5003ABYX-01WERA1</t>
         </is>
       </c>
-      <c r="H57" s="61" t="inlineStr">
+      <c r="H58" s="61" t="inlineStr">
         <is>
           <t>500Gb</t>
         </is>
       </c>
-      <c r="I57" s="61" t="inlineStr">
+      <c r="I58" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J57" s="61" t="inlineStr">
+      <c r="J58" s="61" t="inlineStr">
         <is>
           <t>WS-024-012</t>
         </is>
       </c>
-      <c r="K57" s="61" t="inlineStr">
+      <c r="K58" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M404dn</t>
         </is>
       </c>
-      <c r="L57" s="61" t="inlineStr">
+      <c r="L58" s="61" t="inlineStr">
         <is>
           <t>disp</t>
         </is>
       </c>
-      <c r="M57" s="61" t="inlineStr">
+      <c r="M58" s="61" t="inlineStr">
         <is>
           <t>skp</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="70">
-      <c r="A58" s="55" t="n">
+    <row r="59" ht="15.75" customHeight="1" s="70">
+      <c r="A59" s="55" t="n">
         <v>46230</v>
       </c>
-      <c r="B58" s="63" t="inlineStr">
+      <c r="B59" s="63" t="inlineStr">
         <is>
           <t>10.67.28.59</t>
         </is>
       </c>
-      <c r="C58" s="64" t="inlineStr">
+      <c r="C59" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:B1:CF</t>
         </is>
       </c>
-      <c r="D58" s="61" t="inlineStr">
+      <c r="D59" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E58" s="61" t="inlineStr">
+      <c r="E59" s="61" t="inlineStr">
         <is>
           <t>Intel(R) G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F58" s="61" t="inlineStr">
+      <c r="F59" s="61" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="G58" s="61" t="inlineStr">
+      <c r="G59" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">KINGSTON_SA400S37240G </t>
         </is>
       </c>
-      <c r="H58" s="61" t="inlineStr">
+      <c r="H59" s="61" t="inlineStr">
         <is>
           <t>SSD 240Gb</t>
         </is>
       </c>
-      <c r="I58" s="61" t="inlineStr">
+      <c r="I59" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J58" s="61" t="n">
+      <c r="J59" s="61" t="n">
         <v>2096</v>
       </c>
-      <c r="K58" s="61" t="inlineStr">
+      <c r="K59" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428f-M429f</t>
         </is>
       </c>
-      <c r="L58" s="61" t="inlineStr">
+      <c r="L59" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M58" s="61" t="inlineStr">
+      <c r="M59" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1" s="70">
-      <c r="A59" s="47" t="n">
+    <row r="60" ht="15.75" customHeight="1" s="70">
+      <c r="A60" s="47" t="n">
         <v>46225</v>
       </c>
-      <c r="B59" s="63" t="inlineStr">
+      <c r="B60" s="63" t="inlineStr">
         <is>
           <t>10.67.64.107</t>
         </is>
       </c>
-      <c r="C59" s="64" t="inlineStr">
+      <c r="C60" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:4C:F7</t>
         </is>
       </c>
-      <c r="D59" s="61" t="inlineStr">
+      <c r="D60" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E59" s="61" t="inlineStr">
+      <c r="E60" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F59" s="61" t="inlineStr">
+      <c r="F60" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G59" s="61" t="inlineStr">
+      <c r="G60" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H59" s="61" t="inlineStr">
+      <c r="H60" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I59" s="61" t="inlineStr">
+      <c r="I60" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J59" s="61" t="inlineStr">
+      <c r="J60" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K59" s="61" t="inlineStr">
+      <c r="K60" s="61" t="inlineStr">
         <is>
           <t>Pantum BP5100DN</t>
         </is>
       </c>
-      <c r="L59" s="61" t="inlineStr">
+      <c r="L60" s="61" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="M59" s="61" t="inlineStr">
+      <c r="M60" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="70">
-      <c r="A60" s="46" t="n">
+    <row r="61" ht="15.75" customHeight="1" s="70">
+      <c r="A61" s="46" t="n">
         <v>46225</v>
       </c>
-      <c r="B60" s="63" t="inlineStr">
+      <c r="B61" s="63" t="inlineStr">
         <is>
           <t>10.67.64.5</t>
         </is>
       </c>
-      <c r="C60" s="64" t="inlineStr">
+      <c r="C61" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:58:0C</t>
         </is>
       </c>
-      <c r="D60" s="61" t="inlineStr">
+      <c r="D61" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E60" s="61" t="inlineStr">
+      <c r="E61" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F60" s="61" t="inlineStr">
+      <c r="F61" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G60" s="61" t="inlineStr">
+      <c r="G61" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H60" s="61" t="inlineStr">
+      <c r="H61" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I60" s="61" t="inlineStr">
+      <c r="I61" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J60" s="61" t="inlineStr">
+      <c r="J61" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K60" s="61" t="inlineStr">
+      <c r="K61" s="61" t="inlineStr">
         <is>
           <t>HP M428</t>
         </is>
       </c>
-      <c r="L60" s="61" t="inlineStr">
+      <c r="L61" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M60" s="61" t="inlineStr">
+      <c r="M61" s="61" t="inlineStr">
         <is>
           <t>pol1-3level</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="70">
-      <c r="A61" s="45" t="n">
+    <row r="62" ht="15.75" customHeight="1" s="70">
+      <c r="A62" s="45" t="n">
         <v>46226</v>
       </c>
-      <c r="B61" s="63" t="inlineStr">
+      <c r="B62" s="63" t="inlineStr">
         <is>
           <t>10.67.64.26</t>
         </is>
       </c>
-      <c r="C61" s="64" t="inlineStr">
+      <c r="C62" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D62" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E62" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F62" s="61" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="G61" s="61" t="inlineStr">
+      <c r="G62" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H61" s="61" t="inlineStr">
+      <c r="H62" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I61" s="61" t="inlineStr">
+      <c r="I62" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J61" s="61" t="inlineStr">
+      <c r="J62" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K61" s="61" t="inlineStr">
+      <c r="K62" s="61" t="inlineStr">
         <is>
           <t>Samsung-SCX-483x-5x3x-Series</t>
         </is>
       </c>
-      <c r="L61" s="61" t="inlineStr">
+      <c r="L62" s="61" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="M61" s="61" t="inlineStr">
+      <c r="M62" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="70">
-      <c r="A62" s="44" t="n">
+    <row r="63" ht="15.75" customHeight="1" s="70">
+      <c r="A63" s="44" t="n">
         <v>46225</v>
       </c>
-      <c r="B62" s="63" t="inlineStr">
+      <c r="B63" s="63" t="inlineStr">
         <is>
           <t>10.67.64.2</t>
         </is>
       </c>
-      <c r="C62" s="64" t="inlineStr">
+      <c r="C63" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:20</t>
         </is>
       </c>
-      <c r="D62" s="61" t="inlineStr">
+      <c r="D63" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E62" s="61" t="inlineStr">
+      <c r="E63" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F62" s="61" t="inlineStr">
+      <c r="F63" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G62" s="61" t="inlineStr">
+      <c r="G63" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H62" s="61" t="inlineStr">
+      <c r="H63" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I62" s="61" t="inlineStr">
+      <c r="I63" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J62" s="61" t="inlineStr">
+      <c r="J63" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K62" s="61" t="inlineStr">
+      <c r="K63" s="61" t="inlineStr">
         <is>
           <t>HP M428</t>
         </is>
       </c>
-      <c r="L62" s="61" t="inlineStr">
+      <c r="L63" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M62" s="61" t="inlineStr">
+      <c r="M63" s="61" t="inlineStr">
         <is>
           <t>pol1-3level</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1" s="70">
-      <c r="A63" s="43" t="n">
+    <row r="64" ht="15.75" customHeight="1" s="70">
+      <c r="A64" s="43" t="n">
         <v>46227</v>
       </c>
-      <c r="B63" s="63" t="inlineStr">
+      <c r="B64" s="63" t="inlineStr">
         <is>
           <t>10.67.28.73</t>
         </is>
       </c>
-      <c r="C63" s="64" t="inlineStr">
+      <c r="C64" s="64" t="inlineStr">
         <is>
           <t>F8:CC:6E:00:AF:9E</t>
         </is>
       </c>
-      <c r="D63" s="61" t="inlineStr">
+      <c r="D64" s="61" t="inlineStr">
         <is>
           <t>DEPO Computers DPH110S</t>
         </is>
       </c>
-      <c r="E63" s="61" t="inlineStr">
+      <c r="E64" s="61" t="inlineStr">
         <is>
           <t>Intel(R) G5420 3.80GHz</t>
         </is>
       </c>
-      <c r="F63" s="61" t="inlineStr">
+      <c r="F64" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G63" s="61" t="inlineStr">
+      <c r="G64" s="61" t="inlineStr">
         <is>
           <t>QUMO_SSD</t>
         </is>
       </c>
-      <c r="H63" s="61" t="inlineStr">
+      <c r="H64" s="61" t="inlineStr">
         <is>
           <t>SSD 120Gb</t>
         </is>
       </c>
-      <c r="I63" s="61" t="inlineStr">
+      <c r="I64" s="61" t="inlineStr">
         <is>
           <t>ALT 8 SP Workstation</t>
         </is>
       </c>
-      <c r="J63" s="61" t="inlineStr">
+      <c r="J64" s="61" t="inlineStr">
         <is>
           <t>002096</t>
         </is>
       </c>
-      <c r="K63" s="61" t="inlineStr">
+      <c r="K64" s="61" t="inlineStr">
         <is>
           <t>HP Laserjet M14-M17</t>
         </is>
       </c>
-      <c r="L63" s="61" t="inlineStr">
+      <c r="L64" s="61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M63" s="61" t="inlineStr">
+      <c r="M64" s="61" t="inlineStr">
         <is>
           <t>pat.anatom.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="70">
-      <c r="A64" s="40" t="n">
+    <row r="65">
+      <c r="A65" s="40" t="n">
         <v>46220</v>
       </c>
-      <c r="B64" s="63" t="inlineStr">
+      <c r="B65" s="63" t="inlineStr">
         <is>
           <t>10.67.12.70</t>
         </is>
       </c>
-      <c r="C64" s="64" t="inlineStr">
+      <c r="C65" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:16:57:0A</t>
         </is>
       </c>
-      <c r="D64" s="61" t="inlineStr">
+      <c r="D65" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E64" s="61" t="inlineStr">
+      <c r="E65" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F64" s="61" t="inlineStr">
+      <c r="F65" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G64" s="61" t="inlineStr">
+      <c r="G65" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H64" s="61" t="inlineStr">
+      <c r="H65" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I64" s="61" t="inlineStr">
+      <c r="I65" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J64" s="61" t="inlineStr">
+      <c r="J65" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K64" s="61" t="inlineStr">
+      <c r="K65" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L64" s="61" t="inlineStr">
+      <c r="L65" s="61" t="inlineStr">
         <is>
           <t>st.ses</t>
         </is>
       </c>
-      <c r="M64" s="61" t="inlineStr">
+      <c r="M65" s="61" t="inlineStr">
         <is>
           <t>h5</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="39" t="n">
+    <row r="66">
+      <c r="A66" s="39" t="n">
         <v>46218</v>
       </c>
-      <c r="B65" s="63" t="inlineStr">
+      <c r="B66" s="63" t="inlineStr">
         <is>
           <t>10.67.12.49</t>
         </is>
       </c>
-      <c r="C65" s="64" t="inlineStr">
+      <c r="C66" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:47:D7</t>
         </is>
       </c>
-      <c r="D65" s="61" t="inlineStr">
+      <c r="D66" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E65" s="61" t="inlineStr">
+      <c r="E66" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F65" s="61" t="inlineStr">
+      <c r="F66" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G65" s="61" t="inlineStr">
+      <c r="G66" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H65" s="61" t="inlineStr">
+      <c r="H66" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I65" s="61" t="inlineStr">
+      <c r="I66" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J65" s="61" t="inlineStr">
+      <c r="J66" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K65" s="61" t="inlineStr">
+      <c r="K66" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L65" s="61" t="inlineStr">
+      <c r="L66" s="61" t="inlineStr">
         <is>
           <t>sts</t>
         </is>
       </c>
-      <c r="M65" s="61" t="inlineStr">
+      <c r="M66" s="61" t="inlineStr">
         <is>
           <t>h2</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="38" t="n">
+    <row r="67">
+      <c r="A67" s="38" t="n">
         <v>46218</v>
       </c>
-      <c r="B66" s="63" t="inlineStr">
+      <c r="B67" s="63" t="inlineStr">
         <is>
           <t>10.67.64.82</t>
         </is>
       </c>
-      <c r="C66" s="64" t="inlineStr">
+      <c r="C67" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:3F:87</t>
         </is>
       </c>
-      <c r="D66" s="61" t="inlineStr">
+      <c r="D67" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E66" s="61" t="inlineStr">
+      <c r="E67" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F66" s="61" t="inlineStr">
+      <c r="F67" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G66" s="61" t="inlineStr">
+      <c r="G67" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H66" s="61" t="inlineStr">
+      <c r="H67" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I66" s="61" t="inlineStr">
+      <c r="I67" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J66" s="61" t="inlineStr">
+      <c r="J67" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K66" s="61" t="inlineStr">
+      <c r="K67" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L66" s="61" t="inlineStr">
+      <c r="L67" s="61" t="inlineStr">
         <is>
           <t>433</t>
         </is>
       </c>
-      <c r="M66" s="61" t="inlineStr">
+      <c r="M67" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="37" t="n">
+    <row r="68">
+      <c r="A68" s="37" t="n">
         <v>46218</v>
       </c>
-      <c r="B67" s="63" t="inlineStr">
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>10.67.64.52</t>
         </is>
       </c>
-      <c r="C67" s="64" t="inlineStr">
+      <c r="C68" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:59:52</t>
         </is>
       </c>
-      <c r="D67" s="61" t="inlineStr">
+      <c r="D68" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E67" s="61" t="inlineStr">
+      <c r="E68" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F67" s="61" t="inlineStr">
+      <c r="F68" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G67" s="61" t="inlineStr">
+      <c r="G68" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H67" s="61" t="inlineStr">
+      <c r="H68" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I67" s="61" t="inlineStr">
+      <c r="I68" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J67" s="61" t="inlineStr">
+      <c r="J68" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K67" s="61" t="inlineStr">
+      <c r="K68" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L67" s="61" t="inlineStr">
+      <c r="L68" s="61" t="inlineStr">
         <is>
           <t>824</t>
         </is>
       </c>
-      <c r="M67" s="61" t="inlineStr">
+      <c r="M68" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="36" t="n">
+    <row r="69">
+      <c r="A69" s="36" t="n">
         <v>46218</v>
       </c>
-      <c r="B68" s="63" t="inlineStr">
+      <c r="B69" s="63" t="inlineStr">
         <is>
           <t>10.67.64.9</t>
         </is>
       </c>
-      <c r="C68" s="64" t="inlineStr">
+      <c r="C69" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:52</t>
         </is>
       </c>
-      <c r="D68" s="61" t="inlineStr">
+      <c r="D69" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E68" s="61" t="inlineStr">
+      <c r="E69" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F68" s="61" t="inlineStr">
+      <c r="F69" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G68" s="61" t="inlineStr">
+      <c r="G69" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H68" s="61" t="inlineStr">
+      <c r="H69" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I68" s="61" t="inlineStr">
+      <c r="I69" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J68" s="61" t="inlineStr">
+      <c r="J69" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K68" s="61" t="inlineStr">
+      <c r="K69" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L68" s="61" t="inlineStr">
+      <c r="L69" s="61" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M68" s="61" t="inlineStr">
+      <c r="M69" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="35" t="n">
+    <row r="70">
+      <c r="A70" s="35" t="n">
         <v>46218</v>
       </c>
-      <c r="B69" s="63" t="inlineStr">
+      <c r="B70" s="63" t="inlineStr">
         <is>
           <t>10.67.64.26</t>
         </is>
       </c>
-      <c r="C69" s="64" t="inlineStr">
+      <c r="C70" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:76:0C</t>
         </is>
       </c>
-      <c r="D69" s="61" t="inlineStr">
+      <c r="D70" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E69" s="61" t="inlineStr">
+      <c r="E70" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F69" s="61" t="inlineStr">
+      <c r="F70" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G69" s="61" t="inlineStr">
+      <c r="G70" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H69" s="61" t="inlineStr">
+      <c r="H70" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I69" s="61" t="inlineStr">
+      <c r="I70" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J69" s="61" t="inlineStr">
+      <c r="J70" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K69" s="61" t="inlineStr">
+      <c r="K70" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L69" s="61" t="inlineStr">
+      <c r="L70" s="61" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="M69" s="61" t="inlineStr">
+      <c r="M70" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="34" t="n">
+    <row r="71">
+      <c r="A71" s="34" t="n">
         <v>46217</v>
       </c>
-      <c r="B70" s="63" t="inlineStr">
+      <c r="B71" s="63" t="inlineStr">
         <is>
           <t>10.67.22.66</t>
         </is>
       </c>
-      <c r="C70" s="64" t="inlineStr">
+      <c r="C71" s="64" t="inlineStr">
         <is>
           <t>2C-F0-5D-9E-B2-56</t>
         </is>
       </c>
-      <c r="D70" s="61" t="inlineStr">
+      <c r="D71" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">MSI A320M-A PRO </t>
         </is>
       </c>
-      <c r="E70" s="61" t="inlineStr">
+      <c r="E71" s="61" t="inlineStr">
         <is>
           <t>AMD Ryzen 5 3400G</t>
         </is>
       </c>
-      <c r="F70" s="61" t="inlineStr">
+      <c r="F71" s="61" t="inlineStr">
         <is>
           <t>6GiB</t>
         </is>
       </c>
-      <c r="G70" s="61" t="inlineStr">
+      <c r="G71" s="61" t="inlineStr">
         <is>
           <t>Smartbuy SSD 256GB</t>
         </is>
       </c>
-      <c r="H70" s="61" t="inlineStr">
+      <c r="H71" s="61" t="inlineStr">
         <is>
           <t>256Gb</t>
         </is>
       </c>
-      <c r="I70" s="61" t="inlineStr">
+      <c r="I71" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J70" s="61" t="inlineStr">
+      <c r="J71" s="61" t="inlineStr">
         <is>
           <t>WS-022-066</t>
         </is>
       </c>
-      <c r="K70" s="61" t="inlineStr">
+      <c r="K71" s="61" t="inlineStr">
         <is>
           <t>HP LaserJet Pro M428f-M429f</t>
         </is>
       </c>
-      <c r="L70" s="61" t="inlineStr">
+      <c r="L71" s="61" t="inlineStr">
         <is>
           <t>registr</t>
         </is>
       </c>
-      <c r="M70" s="61" t="inlineStr">
+      <c r="M71" s="61" t="inlineStr">
         <is>
           <t>detstvo</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="33" t="n">
+    <row r="72">
+      <c r="A72" s="33" t="n">
         <v>46211</v>
       </c>
-      <c r="B71" s="63" t="inlineStr">
+      <c r="B72" s="63" t="inlineStr">
         <is>
           <t>10.67.64.88</t>
         </is>
       </c>
-      <c r="C71" s="64" t="inlineStr">
+      <c r="C72" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:72:F0</t>
         </is>
       </c>
-      <c r="D71" s="61" t="inlineStr">
+      <c r="D72" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E71" s="61" t="inlineStr">
+      <c r="E72" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F71" s="61" t="inlineStr">
+      <c r="F72" s="61" t="inlineStr">
         <is>
           <t>8GB</t>
         </is>
       </c>
-      <c r="G71" s="61" t="inlineStr">
+      <c r="G72" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H71" s="61" t="inlineStr">
+      <c r="H72" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I71" s="61" t="inlineStr">
+      <c r="I72" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J71" s="61" t="inlineStr">
+      <c r="J72" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K71" s="61" t="inlineStr">
+      <c r="K72" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L71" s="61" t="inlineStr">
+      <c r="L72" s="61" t="inlineStr">
         <is>
           <t>542</t>
         </is>
       </c>
-      <c r="M71" s="61" t="inlineStr">
+      <c r="M72" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="32" t="n">
+    <row r="73">
+      <c r="A73" s="32" t="n">
         <v>46202</v>
       </c>
-      <c r="B72" s="63" t="inlineStr">
+      <c r="B73" s="63" t="inlineStr">
         <is>
           <t>10.67.64.40</t>
         </is>
       </c>
-      <c r="C72" s="64" t="inlineStr">
+      <c r="C73" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:54:E6</t>
         </is>
       </c>
-      <c r="D72" s="61" t="inlineStr">
+      <c r="D73" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E72" s="61" t="inlineStr">
+      <c r="E73" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F72" s="61" t="inlineStr">
+      <c r="F73" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G72" s="61" t="inlineStr">
+      <c r="G73" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H72" s="61" t="inlineStr">
+      <c r="H73" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I72" s="61" t="inlineStr">
+      <c r="I73" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J72" s="61" t="inlineStr">
+      <c r="J73" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K72" s="61" t="inlineStr">
+      <c r="K73" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L72" s="61" t="inlineStr">
+      <c r="L73" s="61" t="inlineStr">
         <is>
           <t>530</t>
         </is>
       </c>
-      <c r="M72" s="61" t="inlineStr">
+      <c r="M73" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="31" t="n">
+    <row r="74">
+      <c r="A74" s="31" t="n">
         <v>46199</v>
       </c>
-      <c r="B73" s="63" t="inlineStr">
+      <c r="B74" s="63" t="inlineStr">
         <is>
           <t>10.67.64.8</t>
         </is>
       </c>
-      <c r="C73" s="64" t="inlineStr">
+      <c r="C74" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:57:D6</t>
         </is>
       </c>
-      <c r="D73" s="61" t="inlineStr">
+      <c r="D74" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E73" s="61" t="inlineStr">
+      <c r="E74" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F73" s="61" t="inlineStr">
+      <c r="F74" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G73" s="61" t="inlineStr">
+      <c r="G74" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H73" s="61" t="inlineStr">
+      <c r="H74" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I73" s="61" t="inlineStr">
+      <c r="I74" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J73" s="61" t="inlineStr">
+      <c r="J74" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K73" s="61" t="inlineStr">
+      <c r="K74" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L73" s="61" t="inlineStr">
+      <c r="L74" s="61" t="inlineStr">
         <is>
           <t>~</t>
         </is>
       </c>
-      <c r="M73" s="61" t="inlineStr">
+      <c r="M74" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="n">
+    <row r="75">
+      <c r="A75" s="30" t="n">
         <v>46198</v>
       </c>
-      <c r="B74" s="63" t="inlineStr">
+      <c r="B75" s="63" t="inlineStr">
         <is>
           <t>10.67.22.105</t>
         </is>
       </c>
-      <c r="C74" s="64" t="inlineStr">
+      <c r="C75" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:36:6D</t>
         </is>
       </c>
-      <c r="D74" s="61" t="inlineStr">
+      <c r="D75" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E74" s="61" t="inlineStr">
+      <c r="E75" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F74" s="61" t="inlineStr">
+      <c r="F75" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G74" s="61" t="inlineStr">
+      <c r="G75" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H74" s="61" t="inlineStr">
+      <c r="H75" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I74" s="61" t="inlineStr">
+      <c r="I75" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J74" s="61" t="inlineStr">
+      <c r="J75" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K74" s="61" t="inlineStr">
+      <c r="K75" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L74" s="61" t="inlineStr">
+      <c r="L75" s="61" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="M74" s="61" t="inlineStr">
+      <c r="M75" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="n">
+    <row r="76">
+      <c r="A76" s="29" t="n">
         <v>46196</v>
       </c>
-      <c r="B75" s="63" t="inlineStr">
+      <c r="B76" s="63" t="inlineStr">
         <is>
           <t>192.168.36.31</t>
         </is>
       </c>
-      <c r="C75" s="64" t="inlineStr">
+      <c r="C76" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:1D:48</t>
         </is>
       </c>
-      <c r="D75" s="61" t="inlineStr">
+      <c r="D76" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E75" s="61" t="inlineStr">
+      <c r="E76" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F75" s="61" t="inlineStr">
+      <c r="F76" s="61" t="inlineStr">
         <is>
           <t>9Gb</t>
         </is>
       </c>
-      <c r="G75" s="61" t="inlineStr">
+      <c r="G76" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H75" s="61" t="inlineStr">
+      <c r="H76" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I75" s="61" t="inlineStr">
+      <c r="I76" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J75" s="61" t="inlineStr">
+      <c r="J76" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K75" s="61" t="inlineStr">
+      <c r="K76" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L75" s="61" t="inlineStr">
+      <c r="L76" s="61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M75" s="61" t="inlineStr">
+      <c r="M76" s="61" t="inlineStr">
         <is>
           <t>stomat</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="n">
+    <row r="77">
+      <c r="A77" s="28" t="n">
         <v>46196</v>
       </c>
-      <c r="B76" s="63" t="inlineStr">
+      <c r="B77" s="63" t="inlineStr">
         <is>
           <t>192.168.36.25</t>
         </is>
       </c>
-      <c r="C76" s="64" t="inlineStr">
+      <c r="C77" s="64" t="inlineStr">
         <is>
           <t>18-C0-4D-CD-F6-5E</t>
         </is>
       </c>
-      <c r="D76" s="61" t="inlineStr">
+      <c r="D77" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M H V3</t>
         </is>
       </c>
-      <c r="E76" s="61" t="inlineStr">
+      <c r="E77" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10105 3.70GHz</t>
         </is>
       </c>
-      <c r="F76" s="61" t="inlineStr">
+      <c r="F77" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G76" s="61" t="inlineStr">
+      <c r="G77" s="61" t="inlineStr">
         <is>
           <t>Samsung SSD 870 EVO 500GB</t>
         </is>
       </c>
-      <c r="H76" s="61" t="inlineStr">
+      <c r="H77" s="61" t="inlineStr">
         <is>
           <t>465Gb</t>
         </is>
       </c>
-      <c r="I76" s="61" t="inlineStr">
+      <c r="I77" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J76" s="61" t="inlineStr">
+      <c r="J77" s="61" t="inlineStr">
         <is>
           <t>WS-036-025</t>
         </is>
       </c>
-      <c r="K76" s="61" t="inlineStr">
+      <c r="K77" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L76" s="61" t="inlineStr">
+      <c r="L77" s="61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M76" s="61" t="inlineStr">
+      <c r="M77" s="61" t="inlineStr">
         <is>
           <t>stomat</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="27" t="n">
+    <row r="78">
+      <c r="A78" s="27" t="n">
         <v>46192</v>
       </c>
-      <c r="B77" s="63" t="inlineStr">
+      <c r="B78" s="63" t="inlineStr">
         <is>
           <t>10.67.38.58</t>
         </is>
       </c>
-      <c r="C77" s="64" t="inlineStr">
+      <c r="C78" s="64" t="inlineStr">
         <is>
           <t>10-FF-E0-63-ED-A8</t>
         </is>
       </c>
-      <c r="D77" s="61" t="inlineStr">
+      <c r="D78" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H410M K</t>
         </is>
       </c>
-      <c r="E77" s="61" t="inlineStr">
+      <c r="E78" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F77" s="61" t="inlineStr">
+      <c r="F78" s="61" t="inlineStr">
         <is>
           <t>16Gb</t>
         </is>
       </c>
-      <c r="G77" s="61" t="inlineStr">
+      <c r="G78" s="61" t="inlineStr">
         <is>
           <t>WD Blue SN5000 500GB</t>
         </is>
       </c>
-      <c r="H77" s="61" t="inlineStr">
+      <c r="H78" s="61" t="inlineStr">
         <is>
           <t>HDD 465Gb</t>
         </is>
       </c>
-      <c r="I77" s="61" t="inlineStr">
+      <c r="I78" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J77" s="61" t="inlineStr">
+      <c r="J78" s="61" t="inlineStr">
         <is>
           <t>WS-038-058</t>
         </is>
       </c>
-      <c r="K77" s="61" t="inlineStr">
+      <c r="K78" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L77" s="61" t="inlineStr">
+      <c r="L78" s="61" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="M77" s="61" t="inlineStr">
+      <c r="M78" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="26" t="n">
+    <row r="79">
+      <c r="A79" s="26" t="n">
         <v>46191</v>
       </c>
-      <c r="B78" s="63" t="inlineStr">
+      <c r="B79" s="63" t="inlineStr">
         <is>
           <t>10.67.64.98</t>
         </is>
       </c>
-      <c r="C78" s="64" t="inlineStr">
+      <c r="C79" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:6A:B2</t>
         </is>
       </c>
-      <c r="D78" s="61" t="inlineStr">
+      <c r="D79" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E78" s="61" t="inlineStr">
+      <c r="E79" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F78" s="61" t="inlineStr">
+      <c r="F79" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G78" s="61" t="inlineStr">
+      <c r="G79" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H78" s="61" t="inlineStr">
+      <c r="H79" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I78" s="61" t="inlineStr">
+      <c r="I79" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J78" s="61" t="inlineStr">
+      <c r="J79" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K78" s="61" t="inlineStr">
+      <c r="K79" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L78" s="61" t="inlineStr">
+      <c r="L79" s="61" t="inlineStr">
         <is>
           <t>registratura</t>
         </is>
       </c>
-      <c r="M78" s="61" t="inlineStr">
+      <c r="M79" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="25" t="n">
+    <row r="80">
+      <c r="A80" s="25" t="n">
         <v>46183</v>
       </c>
-      <c r="B79" s="63" t="inlineStr">
+      <c r="B80" s="63" t="inlineStr">
         <is>
           <t>10.67.64.92</t>
         </is>
       </c>
-      <c r="C79" s="64" t="inlineStr">
+      <c r="C80" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:63:82</t>
         </is>
       </c>
-      <c r="D79" s="61" t="inlineStr">
+      <c r="D80" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E79" s="61" t="inlineStr">
+      <c r="E80" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F79" s="61" t="inlineStr">
+      <c r="F80" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G79" s="61" t="inlineStr">
+      <c r="G80" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5 OnlyDisk</t>
         </is>
       </c>
-      <c r="H79" s="61" t="inlineStr">
+      <c r="H80" s="61" t="inlineStr">
         <is>
           <t>SSD 238Gb</t>
         </is>
       </c>
-      <c r="I79" s="61" t="inlineStr">
+      <c r="I80" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J79" s="61" t="inlineStr">
+      <c r="J80" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K79" s="61" t="inlineStr">
+      <c r="K80" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L79" s="61" t="inlineStr">
+      <c r="L80" s="61" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="M79" s="61" t="inlineStr">
+      <c r="M80" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="24" t="n">
+    <row r="81">
+      <c r="A81" s="24" t="n">
         <v>46183</v>
       </c>
-      <c r="B80" s="63" t="inlineStr">
+      <c r="B81" s="63" t="inlineStr">
         <is>
           <t>10.67.64.38</t>
         </is>
       </c>
-      <c r="C80" s="64" t="inlineStr">
+      <c r="C81" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:54:A4</t>
         </is>
       </c>
-      <c r="D80" s="61" t="inlineStr">
+      <c r="D81" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E80" s="61" t="inlineStr">
+      <c r="E81" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F80" s="61" t="inlineStr">
+      <c r="F81" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G80" s="61" t="inlineStr">
+      <c r="G81" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H80" s="61" t="inlineStr">
+      <c r="H81" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I80" s="61" t="inlineStr">
+      <c r="I81" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J80" s="61" t="inlineStr">
+      <c r="J81" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K80" s="61" t="inlineStr">
+      <c r="K81" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L80" s="61" t="inlineStr">
+      <c r="L81" s="61" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="M80" s="61" t="inlineStr">
+      <c r="M81" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="23" t="n">
+    <row r="82">
+      <c r="A82" s="23" t="n">
         <v>46183</v>
       </c>
-      <c r="B81" s="63" t="inlineStr">
+      <c r="B82" s="63" t="inlineStr">
         <is>
           <t>10.67.64.96</t>
         </is>
       </c>
-      <c r="C81" s="64" t="inlineStr">
+      <c r="C82" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0F:42:79</t>
         </is>
       </c>
-      <c r="D81" s="61" t="inlineStr">
+      <c r="D82" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E81" s="61" t="inlineStr">
+      <c r="E82" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F81" s="61" t="inlineStr">
+      <c r="F82" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G81" s="61" t="inlineStr">
+      <c r="G82" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H81" s="61" t="inlineStr">
+      <c r="H82" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I81" s="61" t="inlineStr">
+      <c r="I82" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J81" s="61" t="inlineStr">
+      <c r="J82" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K81" s="61" t="inlineStr">
+      <c r="K82" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L81" s="61" t="inlineStr">
+      <c r="L82" s="61" t="inlineStr">
         <is>
           <t>417</t>
         </is>
       </c>
-      <c r="M81" s="61" t="inlineStr">
+      <c r="M82" s="61" t="inlineStr">
         <is>
           <t>pol1</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="22" t="n">
+    <row r="83">
+      <c r="A83" s="22" t="n">
         <v>46181</v>
       </c>
-      <c r="B82" s="63" t="inlineStr">
+      <c r="B83" s="63" t="inlineStr">
         <is>
           <t>10.67.64.3</t>
         </is>
       </c>
-      <c r="C82" s="64" t="inlineStr">
+      <c r="C83" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:17:62:CA</t>
         </is>
       </c>
-      <c r="D82" s="61" t="inlineStr">
+      <c r="D83" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQH310CM</t>
         </is>
       </c>
-      <c r="E82" s="61" t="inlineStr">
+      <c r="E83" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F82" s="61" t="inlineStr">
+      <c r="F83" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G82" s="61" t="inlineStr">
+      <c r="G83" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H82" s="61" t="inlineStr">
+      <c r="H83" s="61" t="inlineStr">
         <is>
           <t>238Gb</t>
         </is>
       </c>
-      <c r="I82" s="61" t="inlineStr">
+      <c r="I83" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J82" s="61" t="inlineStr">
+      <c r="J83" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K82" s="61" t="inlineStr">
+      <c r="K83" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L82" s="61" t="inlineStr">
+      <c r="L83" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M82" s="61" t="inlineStr">
+      <c r="M83" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="21" t="n">
+    <row r="84">
+      <c r="A84" s="21" t="n">
         <v>46181</v>
       </c>
-      <c r="B83" s="63" t="inlineStr">
+      <c r="B84" s="63" t="inlineStr">
         <is>
           <t>192.168.0.129</t>
         </is>
       </c>
-      <c r="C83" s="64" t="inlineStr">
+      <c r="C84" s="64" t="inlineStr">
         <is>
           <t>38-D5-47-E1-3E-C6</t>
         </is>
       </c>
-      <c r="D83" s="61" t="inlineStr">
+      <c r="D84" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK Z170-K</t>
         </is>
       </c>
-      <c r="E83" s="61" t="inlineStr">
+      <c r="E84" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i7-6700K 4.00GHz</t>
         </is>
       </c>
-      <c r="F83" s="61" t="inlineStr">
+      <c r="F84" s="61" t="inlineStr">
         <is>
           <t>32Gb</t>
         </is>
       </c>
-      <c r="G83" s="61" t="inlineStr">
+      <c r="G84" s="61" t="inlineStr">
         <is>
           <t>TOSHIBA DT01ACA100</t>
         </is>
       </c>
-      <c r="H83" s="61" t="inlineStr">
+      <c r="H84" s="61" t="inlineStr">
         <is>
           <t>931Gb</t>
         </is>
       </c>
-      <c r="I83" s="61" t="inlineStr">
+      <c r="I84" s="61" t="inlineStr">
         <is>
           <t>Windows 10 IoT Enterprise</t>
         </is>
       </c>
-      <c r="J83" s="61" t="inlineStr">
+      <c r="J84" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K83" s="61" t="inlineStr">
+      <c r="K84" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L83" s="61" t="inlineStr">
+      <c r="L84" s="61" t="inlineStr">
         <is>
           <t>my</t>
         </is>
       </c>
-      <c r="M83" s="61" t="inlineStr">
+      <c r="M84" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="20" t="n">
+    <row r="85">
+      <c r="A85" s="20" t="n">
         <v>46178</v>
       </c>
-      <c r="B84" s="63" t="inlineStr">
+      <c r="B85" s="63" t="inlineStr">
         <is>
           <t>10.67.2.8</t>
         </is>
       </c>
-      <c r="C84" s="64" t="inlineStr">
+      <c r="C85" s="64" t="inlineStr">
         <is>
           <t>58-11-22-07-4E-DF</t>
         </is>
       </c>
-      <c r="D84" s="61" t="inlineStr">
+      <c r="D85" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME H510M-K</t>
         </is>
       </c>
-      <c r="E84" s="61" t="inlineStr">
+      <c r="E85" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-10400 2.90GHz</t>
         </is>
       </c>
-      <c r="F84" s="61" t="inlineStr">
+      <c r="F85" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G84" s="61" t="inlineStr">
+      <c r="G85" s="61" t="inlineStr">
         <is>
           <t>ST500NM0011</t>
         </is>
       </c>
-      <c r="H84" s="61" t="inlineStr">
+      <c r="H85" s="61" t="inlineStr">
         <is>
           <t>SSD 465 Gb</t>
         </is>
       </c>
-      <c r="I84" s="61" t="inlineStr">
+      <c r="I85" s="61" t="inlineStr">
         <is>
           <t>Windows 10 Pro</t>
         </is>
       </c>
-      <c r="J84" s="61" t="inlineStr">
+      <c r="J85" s="61" t="inlineStr">
         <is>
           <t>WS-002-008</t>
         </is>
       </c>
-      <c r="K84" s="61" t="inlineStr">
+      <c r="K85" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L84" s="61" t="inlineStr">
+      <c r="L85" s="61" t="inlineStr">
         <is>
           <t>312 IGOR</t>
         </is>
       </c>
-      <c r="M84" s="61" t="inlineStr">
+      <c r="M85" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="19" t="n">
+    <row r="86">
+      <c r="A86" s="19" t="n">
         <v>46177</v>
       </c>
-      <c r="B85" s="63" t="inlineStr">
+      <c r="B86" s="63" t="inlineStr">
         <is>
           <t>10.67.2.33</t>
         </is>
       </c>
-      <c r="C85" s="64" t="inlineStr">
+      <c r="C86" s="64" t="inlineStr">
         <is>
           <t>18-C0-4D-D7-67-0E</t>
         </is>
       </c>
-      <c r="D85" s="61" t="inlineStr">
+      <c r="D86" s="61" t="inlineStr">
         <is>
           <t>Gigabyte H510M H</t>
         </is>
       </c>
-      <c r="E85" s="61" t="inlineStr">
+      <c r="E86" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i3-10100 3.60GHz</t>
         </is>
       </c>
-      <c r="F85" s="61" t="inlineStr">
+      <c r="F86" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G85" s="61" t="inlineStr">
+      <c r="G86" s="61" t="inlineStr">
         <is>
           <t>KINGSTON SA400S37480G</t>
         </is>
       </c>
-      <c r="H85" s="61" t="inlineStr">
+      <c r="H86" s="61" t="inlineStr">
         <is>
           <t>SSD 447 Gb</t>
         </is>
       </c>
-      <c r="I85" s="61" t="inlineStr">
+      <c r="I86" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Windows 10 IoT Enterprise LTSC </t>
         </is>
       </c>
-      <c r="J85" s="61" t="inlineStr">
+      <c r="J86" s="61" t="inlineStr">
         <is>
           <t>KOMPUTER</t>
         </is>
       </c>
-      <c r="K85" s="61" t="inlineStr">
+      <c r="K86" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L85" s="61" t="inlineStr">
+      <c r="L86" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M85" s="61" t="inlineStr">
+      <c r="M86" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="18" t="n">
+    <row r="87">
+      <c r="A87" s="18" t="n">
         <v>46178</v>
       </c>
-      <c r="B86" s="63" t="inlineStr">
+      <c r="B87" s="63" t="inlineStr">
         <is>
           <t>192.168.36.34</t>
         </is>
       </c>
-      <c r="C86" s="64" t="inlineStr">
+      <c r="C87" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:12:37:A7</t>
         </is>
       </c>
-      <c r="D86" s="61" t="inlineStr">
+      <c r="D87" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E86" s="61" t="inlineStr">
+      <c r="E87" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) i5-9400 2.90GHz </t>
         </is>
       </c>
-      <c r="F86" s="61" t="inlineStr">
+      <c r="F87" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G86" s="61" t="inlineStr">
+      <c r="G87" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H86" s="61" t="inlineStr">
+      <c r="H87" s="61" t="inlineStr">
         <is>
           <t>SSD 256</t>
         </is>
       </c>
-      <c r="I86" s="61" t="inlineStr">
+      <c r="I87" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J86" s="61" t="inlineStr">
+      <c r="J87" s="61" t="inlineStr">
         <is>
           <t>1051a2</t>
         </is>
       </c>
-      <c r="K86" s="61" t="inlineStr">
+      <c r="K87" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L86" s="61" t="inlineStr">
+      <c r="L87" s="61" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M86" s="61" t="inlineStr">
+      <c r="M87" s="61" t="inlineStr">
         <is>
           <t>stomatology</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="17" t="n">
+    <row r="88">
+      <c r="A88" s="17" t="n">
         <v>46178</v>
       </c>
-      <c r="B87" s="63" t="inlineStr">
+      <c r="B88" s="63" t="inlineStr">
         <is>
           <t>10.67.11.32</t>
         </is>
       </c>
-      <c r="C87" s="64" t="inlineStr">
+      <c r="C88" s="64" t="inlineStr">
         <is>
           <t>00:58:3F:0D:24:AD</t>
         </is>
       </c>
-      <c r="D87" s="61" t="inlineStr">
+      <c r="D88" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK PRIME B365M-C</t>
         </is>
       </c>
-      <c r="E87" s="61" t="inlineStr">
+      <c r="E88" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) i5-9400 2.90GHz </t>
         </is>
       </c>
-      <c r="F87" s="61" t="inlineStr">
+      <c r="F88" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G87" s="61" t="inlineStr">
+      <c r="G88" s="61" t="inlineStr">
         <is>
           <t>FOXLINE FLSSD256X5</t>
         </is>
       </c>
-      <c r="H87" s="61" t="inlineStr">
+      <c r="H88" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I87" s="61" t="inlineStr">
+      <c r="I88" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 10.4</t>
         </is>
       </c>
-      <c r="J87" s="61" t="inlineStr">
+      <c r="J88" s="61" t="inlineStr">
         <is>
           <t>dpk5324</t>
         </is>
       </c>
-      <c r="K87" s="61" t="inlineStr">
+      <c r="K88" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L87" s="61" t="inlineStr">
+      <c r="L88" s="61" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="M87" s="61" t="inlineStr">
+      <c r="M88" s="61" t="inlineStr">
         <is>
           <t>uprav</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="16" t="n">
+    <row r="89">
+      <c r="A89" s="16" t="n">
         <v>46177</v>
       </c>
-      <c r="B88" s="63" t="inlineStr">
+      <c r="B89" s="63" t="inlineStr">
         <is>
           <t>192.168.0.172</t>
         </is>
       </c>
-      <c r="C88" s="64" t="inlineStr">
+      <c r="C89" s="64" t="inlineStr">
         <is>
           <t>2C:56:DC:DB:90:05</t>
         </is>
       </c>
-      <c r="D88" s="61" t="inlineStr">
+      <c r="D89" s="61" t="inlineStr">
         <is>
           <t>ASUSTeK A68HM-K</t>
         </is>
       </c>
-      <c r="E88" s="61" t="inlineStr">
+      <c r="E89" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">AMD Athlon(tm) X2 340 </t>
         </is>
       </c>
-      <c r="F88" s="61" t="inlineStr">
+      <c r="F89" s="61" t="inlineStr">
         <is>
           <t>6Gb</t>
         </is>
       </c>
-      <c r="G88" s="61" t="inlineStr">
+      <c r="G89" s="61" t="inlineStr">
         <is>
           <t>TOSHIBA DT01ACA100</t>
         </is>
       </c>
-      <c r="H88" s="61" t="inlineStr">
+      <c r="H89" s="61" t="inlineStr">
         <is>
           <t>HDD 1000Gb</t>
         </is>
       </c>
-      <c r="I88" s="61" t="inlineStr">
+      <c r="I89" s="61" t="inlineStr">
         <is>
           <t>CentOS Stream 9</t>
         </is>
       </c>
-      <c r="J88" s="61" t="inlineStr">
+      <c r="J89" s="61" t="inlineStr">
         <is>
           <t>localhost</t>
         </is>
       </c>
-      <c r="K88" s="61" t="inlineStr">
+      <c r="K89" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L88" s="61" t="inlineStr">
+      <c r="L89" s="61" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="M88" s="61" t="inlineStr">
+      <c r="M89" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="15" t="n">
+    <row r="90">
+      <c r="A90" s="15" t="n">
         <v>46164</v>
       </c>
-      <c r="B89" s="63" t="inlineStr">
+      <c r="B90" s="63" t="inlineStr">
         <is>
           <t>10.67.40.20</t>
         </is>
       </c>
-      <c r="C89" s="64" t="inlineStr">
+      <c r="C90" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:12:36:42</t>
         </is>
       </c>
-      <c r="D89" s="61" t="inlineStr">
+      <c r="D90" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E89" s="61" t="inlineStr">
+      <c r="E90" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F89" s="61" t="inlineStr">
+      <c r="F90" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G89" s="61" t="inlineStr">
+      <c r="G90" s="61" t="inlineStr">
         <is>
           <t>FOXLINE_FLSSD256X5</t>
         </is>
       </c>
-      <c r="H89" s="61" t="inlineStr">
+      <c r="H90" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I89" s="61" t="inlineStr">
+      <c r="I90" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J89" s="61" t="inlineStr">
+      <c r="J90" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K89" s="61" t="inlineStr">
+      <c r="K90" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L89" s="61" t="inlineStr">
+      <c r="L90" s="61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M89" s="61" t="inlineStr">
+      <c r="M90" s="61" t="inlineStr">
         <is>
           <t>tuber</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="14" t="n">
+    <row r="91">
+      <c r="A91" s="14" t="n">
         <v>46164</v>
       </c>
-      <c r="B90" s="63" t="inlineStr">
+      <c r="B91" s="63" t="inlineStr">
         <is>
           <t>10.67.40.17</t>
         </is>
       </c>
-      <c r="C90" s="64" t="inlineStr">
+      <c r="C91" s="64" t="inlineStr">
         <is>
           <t>00:58:3f:12:36:49</t>
         </is>
       </c>
-      <c r="D90" s="61" t="inlineStr">
+      <c r="D91" s="61" t="inlineStr">
         <is>
           <t>Aquarius AQB365MC</t>
         </is>
       </c>
-      <c r="E90" s="61" t="inlineStr">
+      <c r="E91" s="61" t="inlineStr">
         <is>
           <t>Intel(R) i5-9400 2.90GHz</t>
         </is>
       </c>
-      <c r="F90" s="61" t="inlineStr">
+      <c r="F91" s="61" t="inlineStr">
         <is>
           <t>8Gb</t>
         </is>
       </c>
-      <c r="G90" s="61" t="inlineStr">
+      <c r="G91" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">FOXLINE_FLSSD256X5 </t>
         </is>
       </c>
-      <c r="H90" s="61" t="inlineStr">
+      <c r="H91" s="61" t="inlineStr">
         <is>
           <t>SSD 256Gb</t>
         </is>
       </c>
-      <c r="I90" s="61" t="inlineStr">
+      <c r="I91" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 9.0</t>
         </is>
       </c>
-      <c r="J90" s="61" t="inlineStr">
+      <c r="J91" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K90" s="61" t="inlineStr">
+      <c r="K91" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L90" s="61" t="inlineStr">
+      <c r="L91" s="61" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M90" s="61" t="inlineStr">
+      <c r="M91" s="61" t="inlineStr">
         <is>
           <t>tuber</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n">
-        <v>46150</v>
-      </c>
-      <c r="B91" s="63" t="inlineStr">
-        <is>
-          <t>10.67.64.62</t>
-        </is>
-      </c>
-      <c r="C91" s="64" t="inlineStr">
-        <is>
-          <t>00:58:3f:17:59:a3</t>
-        </is>
-      </c>
-      <c r="D91" s="61" t="inlineStr">
-        <is>
-          <t>Aquarius AQH310CM</t>
-        </is>
-      </c>
-      <c r="E91" s="61" t="inlineStr">
-        <is>
-          <t>Intel(R) i5-9400 2.90GHz</t>
-        </is>
-      </c>
-      <c r="F91" s="61" t="inlineStr">
-        <is>
-          <t>8Gb</t>
-        </is>
-      </c>
-      <c r="G91" s="61" t="inlineStr">
-        <is>
-          <t>FOXLINE_FLSSD256X5</t>
-        </is>
-      </c>
-      <c r="H91" s="61" t="inlineStr">
-        <is>
-          <t>256 GB/238 GiB</t>
-        </is>
-      </c>
-      <c r="I91" s="61" t="inlineStr">
-        <is>
-          <t>ALT Workstation 9.0</t>
-        </is>
-      </c>
-      <c r="J91" s="61" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="K91" s="61" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L91" s="61" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="M91" s="61" t="inlineStr">
-        <is>
-          <t>pol1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B92" s="63" t="inlineStr">
+        <is>
+          <t>10.67.64.62</t>
+        </is>
+      </c>
+      <c r="C92" s="64" t="inlineStr">
+        <is>
+          <t>00:58:3f:17:59:a3</t>
+        </is>
+      </c>
+      <c r="D92" s="61" t="inlineStr">
+        <is>
+          <t>Aquarius AQH310CM</t>
+        </is>
+      </c>
+      <c r="E92" s="61" t="inlineStr">
+        <is>
+          <t>Intel(R) i5-9400 2.90GHz</t>
+        </is>
+      </c>
+      <c r="F92" s="61" t="inlineStr">
+        <is>
+          <t>8Gb</t>
+        </is>
+      </c>
+      <c r="G92" s="61" t="inlineStr">
+        <is>
+          <t>FOXLINE_FLSSD256X5</t>
+        </is>
+      </c>
+      <c r="H92" s="61" t="inlineStr">
+        <is>
+          <t>256 GB/238 GiB</t>
+        </is>
+      </c>
+      <c r="I92" s="61" t="inlineStr">
+        <is>
+          <t>ALT Workstation 9.0</t>
+        </is>
+      </c>
+      <c r="J92" s="61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K92" s="61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L92" s="61" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="M92" s="61" t="inlineStr">
+        <is>
+          <t>pol1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
         <v>46148</v>
       </c>
-      <c r="B92" s="63" t="inlineStr">
+      <c r="B93" s="63" t="inlineStr">
         <is>
           <t>192.168.0.139</t>
         </is>
       </c>
-      <c r="C92" s="64" t="inlineStr">
+      <c r="C93" s="64" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="D92" s="61" t="inlineStr">
+      <c r="D93" s="61" t="inlineStr">
         <is>
           <t>ASRock J3355M</t>
         </is>
       </c>
-      <c r="E92" s="61" t="inlineStr">
+      <c r="E93" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">Intel(R) J3355 2.00GHz </t>
         </is>
       </c>
-      <c r="F92" s="61" t="inlineStr">
+      <c r="F93" s="61" t="inlineStr">
         <is>
           <t>6Gb</t>
         </is>
       </c>
-      <c r="G92" s="61" t="inlineStr">
+      <c r="G93" s="61" t="inlineStr">
         <is>
           <t>WDC WD5000BPVT-2</t>
         </is>
       </c>
-      <c r="H92" s="61" t="inlineStr">
+      <c r="H93" s="61" t="inlineStr">
         <is>
           <t>500 GB/466 GiB</t>
         </is>
       </c>
-      <c r="I92" s="61" t="inlineStr">
+      <c r="I93" s="61" t="inlineStr">
         <is>
           <t>ALT Workstation 8.2</t>
         </is>
       </c>
-      <c r="J92" s="61" t="inlineStr">
+      <c r="J93" s="61" t="inlineStr">
         <is>
           <t>home-comp</t>
         </is>
       </c>
-      <c r="K92" s="61" t="inlineStr">
+      <c r="K93" s="61" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L92" s="61" t="inlineStr">
+      <c r="L93" s="61" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
-      <c r="M92" s="61" t="inlineStr">
+      <c r="M93" s="61" t="inlineStr">
         <is>
           <t>home</t>
         </is>
